--- a/occultation-manager/python/NorthAmerica_AstReportForm_V5.6.12r_Template.xlsx
+++ b/occultation-manager/python/NorthAmerica_AstReportForm_V5.6.12r_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve\Documents\_Steve\Astronomy\IOTA\Reports\mpReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="13_ncr:1_{9EA8FC22-946C-4214-9D68-CC0F7796F0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDC3EB53-2346-421C-9033-DEBAC694F5EB}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{9EA8FC22-946C-4214-9D68-CC0F7796F0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AB946FF-F9DD-4E4D-A0B8-9B937D142827}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -583,7 +583,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="634">
   <si>
     <t>Important Reminders and Tips for the New Report Form (Revised 12-12-2018)</t>
   </si>
@@ -1671,6 +1671,12 @@
   </si>
   <si>
     <t>{{STARTED_OBSERVING_HOURS}}</t>
+  </si>
+  <si>
+    <t>{{STARTED_OBSERVING_MINUTES}}</t>
+  </si>
+  <si>
+    <t>{{STARTED_OBSERVING_SECONDS}}</t>
   </si>
   <si>
     <t>Enter Confidence Level Error Bars In Boxes Below</t>
@@ -4025,6 +4031,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4034,16 +4043,13 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -4240,6 +4246,9 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
@@ -4279,81 +4288,84 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="20" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4385,12 +4397,6 @@
     </xf>
     <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
@@ -8680,21 +8686,21 @@
     </row>
     <row r="149" spans="1:16" ht="18">
       <c r="A149" s="156"/>
-      <c r="B149" s="226"/>
-      <c r="C149" s="226"/>
-      <c r="D149" s="226"/>
-      <c r="E149" s="226"/>
-      <c r="F149" s="226"/>
-      <c r="G149" s="226"/>
-      <c r="H149" s="226"/>
-      <c r="I149" s="226"/>
-      <c r="J149" s="226"/>
-      <c r="K149" s="226"/>
-      <c r="L149" s="226"/>
-      <c r="M149" s="226"/>
-      <c r="N149" s="226"/>
-      <c r="O149" s="226"/>
-      <c r="P149" s="226"/>
+      <c r="B149" s="227"/>
+      <c r="C149" s="227"/>
+      <c r="D149" s="227"/>
+      <c r="E149" s="227"/>
+      <c r="F149" s="227"/>
+      <c r="G149" s="227"/>
+      <c r="H149" s="227"/>
+      <c r="I149" s="227"/>
+      <c r="J149" s="227"/>
+      <c r="K149" s="227"/>
+      <c r="L149" s="227"/>
+      <c r="M149" s="227"/>
+      <c r="N149" s="227"/>
+      <c r="O149" s="227"/>
+      <c r="P149" s="227"/>
     </row>
     <row r="150" spans="1:16" ht="18">
       <c r="A150" s="65" t="s">
@@ -9162,49 +9168,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="27.95" customHeight="1">
-      <c r="A1" s="307" t="s">
+      <c r="A1" s="301" t="s">
         <v>179</v>
       </c>
-      <c r="B1" s="307"/>
-      <c r="C1" s="307"/>
-      <c r="D1" s="307"/>
-      <c r="E1" s="308"/>
-      <c r="F1" s="308"/>
-      <c r="G1" s="314" t="s">
+      <c r="B1" s="301"/>
+      <c r="C1" s="301"/>
+      <c r="D1" s="301"/>
+      <c r="E1" s="302"/>
+      <c r="F1" s="302"/>
+      <c r="G1" s="308" t="s">
         <v>180</v>
       </c>
-      <c r="H1" s="315"/>
-      <c r="I1" s="315"/>
-      <c r="J1" s="315"/>
-      <c r="K1" s="315"/>
-      <c r="L1" s="315"/>
-      <c r="M1" s="315"/>
-      <c r="N1" s="315"/>
-      <c r="O1" s="315"/>
-      <c r="P1" s="315"/>
-      <c r="Q1" s="315"/>
-      <c r="R1" s="315"/>
-      <c r="S1" s="315"/>
-      <c r="T1" s="315"/>
-      <c r="U1" s="315"/>
-      <c r="V1" s="315"/>
-      <c r="W1" s="227"/>
-      <c r="X1" s="227"/>
-      <c r="Y1" s="227"/>
-      <c r="Z1" s="227"/>
+      <c r="H1" s="309"/>
+      <c r="I1" s="309"/>
+      <c r="J1" s="309"/>
+      <c r="K1" s="309"/>
+      <c r="L1" s="309"/>
+      <c r="M1" s="309"/>
+      <c r="N1" s="309"/>
+      <c r="O1" s="309"/>
+      <c r="P1" s="309"/>
+      <c r="Q1" s="309"/>
+      <c r="R1" s="309"/>
+      <c r="S1" s="309"/>
+      <c r="T1" s="309"/>
+      <c r="U1" s="309"/>
+      <c r="V1" s="309"/>
+      <c r="W1" s="226"/>
+      <c r="X1" s="226"/>
+      <c r="Y1" s="226"/>
+      <c r="Z1" s="226"/>
       <c r="AA1" s="246"/>
-      <c r="AB1" s="227"/>
-      <c r="AC1" s="227"/>
+      <c r="AB1" s="226"/>
+      <c r="AC1" s="226"/>
     </row>
     <row r="2" spans="1:29" ht="18" customHeight="1">
-      <c r="A2" s="309" t="s">
+      <c r="A2" s="303" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="309"/>
-      <c r="C2" s="309"/>
-      <c r="D2" s="309"/>
-      <c r="E2" s="310"/>
-      <c r="F2" s="310"/>
+      <c r="B2" s="303"/>
+      <c r="C2" s="303"/>
+      <c r="D2" s="303"/>
+      <c r="E2" s="304"/>
+      <c r="F2" s="304"/>
       <c r="G2" s="220"/>
       <c r="H2" s="220"/>
       <c r="I2" s="220"/>
@@ -9226,20 +9232,20 @@
       <c r="W2" s="81"/>
       <c r="X2" s="81"/>
       <c r="Y2" s="81"/>
-      <c r="Z2" s="322" t="s">
+      <c r="Z2" s="324" t="s">
         <v>183</v>
       </c>
-      <c r="AA2" s="322"/>
-      <c r="AB2" s="322"/>
-      <c r="AC2" s="322"/>
+      <c r="AA2" s="324"/>
+      <c r="AB2" s="324"/>
+      <c r="AC2" s="324"/>
     </row>
     <row r="3" spans="1:29" ht="14.1" customHeight="1">
-      <c r="A3" s="311"/>
-      <c r="B3" s="311"/>
-      <c r="C3" s="311"/>
-      <c r="D3" s="311"/>
-      <c r="E3" s="311"/>
-      <c r="F3" s="311"/>
+      <c r="A3" s="305"/>
+      <c r="B3" s="305"/>
+      <c r="C3" s="305"/>
+      <c r="D3" s="305"/>
+      <c r="E3" s="305"/>
+      <c r="F3" s="305"/>
       <c r="G3" s="220"/>
       <c r="H3" s="220"/>
       <c r="I3" s="220"/>
@@ -9252,9 +9258,9 @@
       <c r="P3" s="220"/>
       <c r="Q3" s="220"/>
       <c r="R3" s="220"/>
-      <c r="S3" s="227"/>
-      <c r="T3" s="227"/>
-      <c r="U3" s="227"/>
+      <c r="S3" s="226"/>
+      <c r="T3" s="226"/>
+      <c r="U3" s="226"/>
       <c r="V3" s="81"/>
       <c r="W3" s="81"/>
       <c r="X3" s="81"/>
@@ -9283,9 +9289,9 @@
       <c r="P4" s="220"/>
       <c r="Q4" s="220"/>
       <c r="R4" s="220"/>
-      <c r="S4" s="227"/>
-      <c r="T4" s="227"/>
-      <c r="U4" s="227"/>
+      <c r="S4" s="226"/>
+      <c r="T4" s="226"/>
+      <c r="U4" s="226"/>
       <c r="V4" s="81"/>
       <c r="W4" s="81"/>
       <c r="X4" s="81"/>
@@ -9303,47 +9309,47 @@
     </row>
     <row r="5" spans="1:29" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="81"/>
-      <c r="B5" s="291" t="s">
+      <c r="B5" s="292" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="318"/>
-      <c r="D5" s="319" t="s">
+      <c r="C5" s="312"/>
+      <c r="D5" s="313" t="s">
         <v>188</v>
       </c>
-      <c r="E5" s="319"/>
-      <c r="F5" s="227"/>
-      <c r="G5" s="227"/>
-      <c r="H5" s="291" t="s">
+      <c r="E5" s="313"/>
+      <c r="F5" s="226"/>
+      <c r="G5" s="226"/>
+      <c r="H5" s="292" t="s">
         <v>189</v>
       </c>
-      <c r="I5" s="291"/>
-      <c r="J5" s="291"/>
-      <c r="K5" s="303" t="s">
+      <c r="I5" s="292"/>
+      <c r="J5" s="292"/>
+      <c r="K5" s="314" t="s">
         <v>190</v>
       </c>
-      <c r="L5" s="303"/>
+      <c r="L5" s="314"/>
       <c r="M5" s="220"/>
-      <c r="N5" s="291" t="s">
+      <c r="N5" s="292" t="s">
         <v>191</v>
       </c>
-      <c r="O5" s="291"/>
-      <c r="P5" s="313" t="s">
+      <c r="O5" s="292"/>
+      <c r="P5" s="307" t="s">
         <v>192</v>
       </c>
-      <c r="Q5" s="313"/>
-      <c r="R5" s="313"/>
-      <c r="S5" s="222"/>
-      <c r="T5" s="316" t="s">
+      <c r="Q5" s="307"/>
+      <c r="R5" s="307"/>
+      <c r="S5" s="223"/>
+      <c r="T5" s="310" t="s">
         <v>193</v>
       </c>
-      <c r="U5" s="317"/>
-      <c r="V5" s="317"/>
-      <c r="W5" s="317"/>
-      <c r="X5" s="317"/>
+      <c r="U5" s="311"/>
+      <c r="V5" s="311"/>
+      <c r="W5" s="311"/>
+      <c r="X5" s="311"/>
       <c r="Y5" s="161" t="s">
         <v>194</v>
       </c>
-      <c r="Z5" s="222" t="s">
+      <c r="Z5" s="223" t="s">
         <v>195</v>
       </c>
       <c r="AA5" s="162" t="s">
@@ -9358,91 +9364,91 @@
     </row>
     <row r="6" spans="1:29" ht="12" customHeight="1">
       <c r="A6" s="81"/>
-      <c r="B6" s="227"/>
-      <c r="C6" s="227"/>
-      <c r="D6" s="227"/>
-      <c r="E6" s="227"/>
-      <c r="F6" s="227"/>
-      <c r="G6" s="227"/>
-      <c r="H6" s="227"/>
-      <c r="I6" s="227"/>
-      <c r="J6" s="227"/>
-      <c r="K6" s="227"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
+      <c r="D6" s="226"/>
+      <c r="E6" s="226"/>
+      <c r="F6" s="226"/>
+      <c r="G6" s="226"/>
+      <c r="H6" s="226"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="226"/>
+      <c r="K6" s="226"/>
       <c r="L6" s="165"/>
       <c r="M6" s="165"/>
       <c r="N6" s="160"/>
-      <c r="O6" s="227"/>
-      <c r="P6" s="227"/>
-      <c r="Q6" s="227"/>
-      <c r="R6" s="227"/>
-      <c r="S6" s="312" t="s">
+      <c r="O6" s="226"/>
+      <c r="P6" s="226"/>
+      <c r="Q6" s="226"/>
+      <c r="R6" s="226"/>
+      <c r="S6" s="306" t="s">
         <v>198</v>
       </c>
-      <c r="T6" s="312"/>
-      <c r="U6" s="312"/>
-      <c r="V6" s="312"/>
+      <c r="T6" s="306"/>
+      <c r="U6" s="306"/>
+      <c r="V6" s="306"/>
       <c r="W6" s="81"/>
-      <c r="X6" s="312" t="s">
+      <c r="X6" s="306" t="s">
         <v>199</v>
       </c>
-      <c r="Y6" s="312"/>
-      <c r="Z6" s="312"/>
-      <c r="AA6" s="312"/>
-      <c r="AB6" s="312"/>
-      <c r="AC6" s="312"/>
+      <c r="Y6" s="306"/>
+      <c r="Z6" s="306"/>
+      <c r="AA6" s="306"/>
+      <c r="AB6" s="306"/>
+      <c r="AC6" s="306"/>
     </row>
     <row r="7" spans="1:29" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="291" t="s">
+      <c r="A7" s="292" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="292"/>
-      <c r="C7" s="292"/>
+      <c r="B7" s="293"/>
+      <c r="C7" s="293"/>
       <c r="D7" s="166" t="s">
         <v>201</v>
       </c>
-      <c r="E7" s="290" t="s">
+      <c r="E7" s="291" t="s">
         <v>202</v>
       </c>
-      <c r="F7" s="290"/>
+      <c r="F7" s="291"/>
       <c r="G7" s="167"/>
-      <c r="H7" s="320" t="s">
+      <c r="H7" s="317" t="s">
         <v>203</v>
       </c>
-      <c r="I7" s="321"/>
-      <c r="J7" s="321"/>
-      <c r="K7" s="290" t="s">
+      <c r="I7" s="318"/>
+      <c r="J7" s="318"/>
+      <c r="K7" s="291" t="s">
         <v>204</v>
       </c>
-      <c r="L7" s="290"/>
-      <c r="M7" s="290"/>
-      <c r="N7" s="290"/>
-      <c r="O7" s="290"/>
-      <c r="P7" s="291" t="s">
+      <c r="L7" s="291"/>
+      <c r="M7" s="291"/>
+      <c r="N7" s="291"/>
+      <c r="O7" s="291"/>
+      <c r="P7" s="292" t="s">
         <v>205</v>
       </c>
-      <c r="Q7" s="291"/>
-      <c r="R7" s="291"/>
-      <c r="S7" s="303" t="s">
+      <c r="Q7" s="292"/>
+      <c r="R7" s="292"/>
+      <c r="S7" s="314" t="s">
         <v>206</v>
       </c>
-      <c r="T7" s="304"/>
-      <c r="U7" s="304"/>
-      <c r="V7" s="304"/>
-      <c r="W7" s="227"/>
-      <c r="X7" s="289" t="s">
+      <c r="T7" s="321"/>
+      <c r="U7" s="321"/>
+      <c r="V7" s="321"/>
+      <c r="W7" s="226"/>
+      <c r="X7" s="290" t="s">
         <v>207</v>
       </c>
-      <c r="Y7" s="289"/>
-      <c r="Z7" s="289"/>
-      <c r="AA7" s="289"/>
-      <c r="AB7" s="289"/>
-      <c r="AC7" s="289"/>
+      <c r="Y7" s="290"/>
+      <c r="Z7" s="290"/>
+      <c r="AA7" s="290"/>
+      <c r="AB7" s="290"/>
+      <c r="AC7" s="290"/>
     </row>
     <row r="8" spans="1:29" ht="15.95" customHeight="1">
       <c r="A8" s="81"/>
-      <c r="B8" s="227"/>
-      <c r="C8" s="227"/>
-      <c r="D8" s="227"/>
+      <c r="B8" s="226"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="226"/>
       <c r="E8" s="278" t="s">
         <v>208</v>
       </c>
@@ -9456,13 +9462,13 @@
       <c r="M8" s="278"/>
       <c r="N8" s="278"/>
       <c r="O8" s="278"/>
-      <c r="P8" s="223" t="s">
+      <c r="P8" s="224" t="s">
         <v>209</v>
       </c>
-      <c r="Q8" s="227"/>
-      <c r="R8" s="227"/>
-      <c r="S8" s="227"/>
-      <c r="T8" s="227"/>
+      <c r="Q8" s="226"/>
+      <c r="R8" s="226"/>
+      <c r="S8" s="226"/>
+      <c r="T8" s="226"/>
       <c r="U8" s="81"/>
       <c r="V8" s="81"/>
       <c r="W8" s="81"/>
@@ -9479,58 +9485,58 @@
       </c>
       <c r="B9" s="268"/>
       <c r="C9" s="268"/>
-      <c r="D9" s="289" t="s">
+      <c r="D9" s="290" t="s">
         <v>211</v>
       </c>
-      <c r="E9" s="289"/>
-      <c r="F9" s="289"/>
-      <c r="G9" s="289"/>
-      <c r="H9" s="289"/>
-      <c r="I9" s="289"/>
-      <c r="J9" s="289"/>
-      <c r="K9" s="289"/>
-      <c r="L9" s="289"/>
-      <c r="M9" s="289"/>
-      <c r="N9" s="289"/>
-      <c r="O9" s="289"/>
+      <c r="E9" s="290"/>
+      <c r="F9" s="290"/>
+      <c r="G9" s="290"/>
+      <c r="H9" s="290"/>
+      <c r="I9" s="290"/>
+      <c r="J9" s="290"/>
+      <c r="K9" s="290"/>
+      <c r="L9" s="290"/>
+      <c r="M9" s="290"/>
+      <c r="N9" s="290"/>
+      <c r="O9" s="290"/>
       <c r="P9" s="277" t="s">
         <v>212</v>
       </c>
       <c r="Q9" s="259"/>
       <c r="R9" s="259"/>
-      <c r="S9" s="299" t="s">
+      <c r="S9" s="300" t="s">
         <v>213</v>
       </c>
-      <c r="T9" s="289"/>
-      <c r="U9" s="289"/>
-      <c r="V9" s="289"/>
-      <c r="W9" s="289"/>
-      <c r="X9" s="289"/>
-      <c r="Y9" s="289"/>
-      <c r="Z9" s="289"/>
-      <c r="AA9" s="289"/>
-      <c r="AB9" s="289"/>
-      <c r="AC9" s="289"/>
+      <c r="T9" s="290"/>
+      <c r="U9" s="290"/>
+      <c r="V9" s="290"/>
+      <c r="W9" s="290"/>
+      <c r="X9" s="290"/>
+      <c r="Y9" s="290"/>
+      <c r="Z9" s="290"/>
+      <c r="AA9" s="290"/>
+      <c r="AB9" s="290"/>
+      <c r="AC9" s="290"/>
     </row>
     <row r="10" spans="1:29" ht="3.95" customHeight="1">
       <c r="A10" s="81"/>
-      <c r="B10" s="227"/>
-      <c r="C10" s="227"/>
+      <c r="B10" s="226"/>
+      <c r="C10" s="226"/>
       <c r="D10" s="231"/>
-      <c r="E10" s="295"/>
-      <c r="F10" s="295"/>
-      <c r="G10" s="295"/>
-      <c r="H10" s="295"/>
-      <c r="I10" s="295"/>
-      <c r="J10" s="295"/>
-      <c r="K10" s="295"/>
-      <c r="L10" s="295"/>
-      <c r="M10" s="295"/>
-      <c r="N10" s="295"/>
-      <c r="O10" s="295"/>
-      <c r="P10" s="227"/>
-      <c r="Q10" s="227"/>
-      <c r="R10" s="227"/>
+      <c r="E10" s="296"/>
+      <c r="F10" s="296"/>
+      <c r="G10" s="296"/>
+      <c r="H10" s="296"/>
+      <c r="I10" s="296"/>
+      <c r="J10" s="296"/>
+      <c r="K10" s="296"/>
+      <c r="L10" s="296"/>
+      <c r="M10" s="296"/>
+      <c r="N10" s="296"/>
+      <c r="O10" s="296"/>
+      <c r="P10" s="226"/>
+      <c r="Q10" s="226"/>
+      <c r="R10" s="226"/>
       <c r="S10" s="231"/>
       <c r="T10" s="228"/>
       <c r="U10" s="231"/>
@@ -9544,50 +9550,50 @@
       <c r="AC10" s="231"/>
     </row>
     <row r="11" spans="1:29" ht="15.95" customHeight="1">
-      <c r="A11" s="293" t="s">
+      <c r="A11" s="294" t="s">
         <v>214</v>
       </c>
-      <c r="B11" s="293"/>
-      <c r="C11" s="293"/>
-      <c r="D11" s="296" t="s">
+      <c r="B11" s="294"/>
+      <c r="C11" s="294"/>
+      <c r="D11" s="297" t="s">
         <v>215</v>
       </c>
-      <c r="E11" s="296"/>
-      <c r="F11" s="296"/>
-      <c r="G11" s="296"/>
-      <c r="H11" s="296"/>
-      <c r="I11" s="296"/>
-      <c r="J11" s="296"/>
-      <c r="K11" s="296"/>
-      <c r="L11" s="296"/>
-      <c r="M11" s="296"/>
-      <c r="N11" s="296"/>
-      <c r="O11" s="296"/>
-      <c r="P11" s="293" t="s">
+      <c r="E11" s="297"/>
+      <c r="F11" s="297"/>
+      <c r="G11" s="297"/>
+      <c r="H11" s="297"/>
+      <c r="I11" s="297"/>
+      <c r="J11" s="297"/>
+      <c r="K11" s="297"/>
+      <c r="L11" s="297"/>
+      <c r="M11" s="297"/>
+      <c r="N11" s="297"/>
+      <c r="O11" s="297"/>
+      <c r="P11" s="294" t="s">
         <v>216</v>
       </c>
-      <c r="Q11" s="293"/>
-      <c r="R11" s="293"/>
-      <c r="S11" s="300" t="s">
+      <c r="Q11" s="294"/>
+      <c r="R11" s="294"/>
+      <c r="S11" s="323" t="s">
         <v>217</v>
       </c>
-      <c r="T11" s="300"/>
-      <c r="U11" s="300"/>
-      <c r="V11" s="300"/>
-      <c r="W11" s="300"/>
-      <c r="X11" s="300"/>
-      <c r="Y11" s="300"/>
-      <c r="Z11" s="300"/>
-      <c r="AA11" s="300"/>
-      <c r="AB11" s="300"/>
-      <c r="AC11" s="300"/>
+      <c r="T11" s="323"/>
+      <c r="U11" s="323"/>
+      <c r="V11" s="323"/>
+      <c r="W11" s="323"/>
+      <c r="X11" s="323"/>
+      <c r="Y11" s="323"/>
+      <c r="Z11" s="323"/>
+      <c r="AA11" s="323"/>
+      <c r="AB11" s="323"/>
+      <c r="AC11" s="323"/>
     </row>
     <row r="12" spans="1:29" ht="3.95" customHeight="1">
       <c r="A12" s="132"/>
       <c r="B12" s="133"/>
       <c r="C12" s="133"/>
       <c r="D12" s="231"/>
-      <c r="E12" s="295"/>
+      <c r="E12" s="296"/>
       <c r="F12" s="256"/>
       <c r="G12" s="256"/>
       <c r="H12" s="256"/>
@@ -9614,49 +9620,49 @@
       <c r="AC12" s="231"/>
     </row>
     <row r="13" spans="1:29" ht="15.95" customHeight="1">
-      <c r="A13" s="293" t="s">
+      <c r="A13" s="294" t="s">
         <v>218</v>
       </c>
-      <c r="B13" s="293"/>
-      <c r="C13" s="293"/>
-      <c r="D13" s="296" t="s">
+      <c r="B13" s="294"/>
+      <c r="C13" s="294"/>
+      <c r="D13" s="297" t="s">
         <v>219</v>
       </c>
-      <c r="E13" s="296"/>
-      <c r="F13" s="296"/>
-      <c r="G13" s="296"/>
-      <c r="H13" s="296"/>
-      <c r="I13" s="296"/>
-      <c r="J13" s="296"/>
-      <c r="K13" s="296"/>
-      <c r="L13" s="296"/>
-      <c r="M13" s="296"/>
-      <c r="N13" s="296"/>
-      <c r="O13" s="296"/>
-      <c r="P13" s="293" t="s">
+      <c r="E13" s="297"/>
+      <c r="F13" s="297"/>
+      <c r="G13" s="297"/>
+      <c r="H13" s="297"/>
+      <c r="I13" s="297"/>
+      <c r="J13" s="297"/>
+      <c r="K13" s="297"/>
+      <c r="L13" s="297"/>
+      <c r="M13" s="297"/>
+      <c r="N13" s="297"/>
+      <c r="O13" s="297"/>
+      <c r="P13" s="294" t="s">
         <v>220</v>
       </c>
-      <c r="Q13" s="293"/>
-      <c r="R13" s="293"/>
-      <c r="S13" s="296" t="s">
+      <c r="Q13" s="294"/>
+      <c r="R13" s="294"/>
+      <c r="S13" s="297" t="s">
         <v>221</v>
       </c>
-      <c r="T13" s="296"/>
-      <c r="U13" s="296"/>
-      <c r="V13" s="296"/>
-      <c r="W13" s="296"/>
-      <c r="X13" s="296"/>
-      <c r="Y13" s="296"/>
-      <c r="Z13" s="296"/>
-      <c r="AA13" s="296"/>
-      <c r="AB13" s="296"/>
-      <c r="AC13" s="296"/>
+      <c r="T13" s="297"/>
+      <c r="U13" s="297"/>
+      <c r="V13" s="297"/>
+      <c r="W13" s="297"/>
+      <c r="X13" s="297"/>
+      <c r="Y13" s="297"/>
+      <c r="Z13" s="297"/>
+      <c r="AA13" s="297"/>
+      <c r="AB13" s="297"/>
+      <c r="AC13" s="297"/>
     </row>
     <row r="14" spans="1:29" ht="15.95" customHeight="1">
       <c r="A14" s="81"/>
       <c r="B14" s="160"/>
       <c r="C14" s="160"/>
-      <c r="D14" s="227"/>
+      <c r="D14" s="226"/>
       <c r="E14" s="257"/>
       <c r="F14" s="257"/>
       <c r="G14" s="257"/>
@@ -9668,11 +9674,11 @@
       <c r="M14" s="257"/>
       <c r="N14" s="257"/>
       <c r="O14" s="257"/>
-      <c r="P14" s="227"/>
-      <c r="Q14" s="227"/>
-      <c r="R14" s="227"/>
-      <c r="S14" s="227"/>
-      <c r="T14" s="227"/>
+      <c r="P14" s="226"/>
+      <c r="Q14" s="226"/>
+      <c r="R14" s="226"/>
+      <c r="S14" s="226"/>
+      <c r="T14" s="226"/>
       <c r="U14" s="81"/>
       <c r="V14" s="81"/>
       <c r="W14" s="81"/>
@@ -9706,13 +9712,13 @@
       <c r="P15" s="274"/>
       <c r="Q15" s="274"/>
       <c r="R15" s="274"/>
-      <c r="S15" s="297" t="s">
+      <c r="S15" s="298" t="s">
         <v>224</v>
       </c>
-      <c r="T15" s="297"/>
-      <c r="U15" s="297"/>
-      <c r="V15" s="297"/>
-      <c r="W15" s="297"/>
+      <c r="T15" s="298"/>
+      <c r="U15" s="298"/>
+      <c r="V15" s="298"/>
+      <c r="W15" s="298"/>
       <c r="X15" s="256"/>
       <c r="Y15" s="256"/>
       <c r="Z15" s="256"/>
@@ -9724,23 +9730,23 @@
       <c r="A16" s="81"/>
       <c r="B16" s="160"/>
       <c r="C16" s="160"/>
-      <c r="D16" s="227"/>
-      <c r="E16" s="227"/>
-      <c r="F16" s="227"/>
-      <c r="G16" s="227"/>
-      <c r="H16" s="227"/>
-      <c r="I16" s="227"/>
-      <c r="J16" s="227"/>
-      <c r="K16" s="227"/>
-      <c r="L16" s="227"/>
-      <c r="M16" s="227"/>
-      <c r="N16" s="227"/>
-      <c r="O16" s="227"/>
-      <c r="P16" s="227"/>
-      <c r="Q16" s="227"/>
-      <c r="R16" s="227"/>
-      <c r="S16" s="227"/>
-      <c r="T16" s="227"/>
+      <c r="D16" s="226"/>
+      <c r="E16" s="226"/>
+      <c r="F16" s="226"/>
+      <c r="G16" s="226"/>
+      <c r="H16" s="226"/>
+      <c r="I16" s="226"/>
+      <c r="J16" s="226"/>
+      <c r="K16" s="226"/>
+      <c r="L16" s="226"/>
+      <c r="M16" s="226"/>
+      <c r="N16" s="226"/>
+      <c r="O16" s="226"/>
+      <c r="P16" s="226"/>
+      <c r="Q16" s="226"/>
+      <c r="R16" s="226"/>
+      <c r="S16" s="226"/>
+      <c r="T16" s="226"/>
       <c r="U16" s="81"/>
       <c r="V16" s="81"/>
       <c r="W16" s="81"/>
@@ -9753,34 +9759,34 @@
     </row>
     <row r="17" spans="1:29" ht="15.95" customHeight="1">
       <c r="A17" s="81"/>
-      <c r="B17" s="227"/>
-      <c r="C17" s="227"/>
+      <c r="B17" s="226"/>
+      <c r="C17" s="226"/>
       <c r="D17" s="160"/>
-      <c r="E17" s="294" t="s">
+      <c r="E17" s="295" t="s">
         <v>225</v>
       </c>
-      <c r="F17" s="310"/>
-      <c r="G17" s="310"/>
-      <c r="H17" s="310"/>
-      <c r="I17" s="227"/>
+      <c r="F17" s="304"/>
+      <c r="G17" s="304"/>
+      <c r="H17" s="304"/>
+      <c r="I17" s="226"/>
       <c r="J17" s="160" t="s">
         <v>226</v>
       </c>
-      <c r="K17" s="227"/>
-      <c r="L17" s="227"/>
-      <c r="M17" s="227"/>
-      <c r="N17" s="294" t="s">
+      <c r="K17" s="226"/>
+      <c r="L17" s="226"/>
+      <c r="M17" s="226"/>
+      <c r="N17" s="295" t="s">
         <v>227</v>
       </c>
-      <c r="O17" s="294"/>
-      <c r="P17" s="294"/>
-      <c r="Q17" s="227"/>
+      <c r="O17" s="295"/>
+      <c r="P17" s="295"/>
+      <c r="Q17" s="226"/>
       <c r="R17" s="160" t="s">
         <v>228</v>
       </c>
       <c r="S17" s="160"/>
-      <c r="T17" s="227"/>
-      <c r="U17" s="227"/>
+      <c r="T17" s="226"/>
+      <c r="U17" s="226"/>
       <c r="V17" s="81"/>
       <c r="W17" s="160" t="s">
         <v>229</v>
@@ -9840,35 +9846,35 @@
         <v>240</v>
       </c>
       <c r="Y18" s="259"/>
-      <c r="Z18" s="221"/>
-      <c r="AA18" s="298" t="s">
+      <c r="Z18" s="222"/>
+      <c r="AA18" s="299" t="s">
         <v>241</v>
       </c>
-      <c r="AB18" s="298"/>
-      <c r="AC18" s="298"/>
+      <c r="AB18" s="299"/>
+      <c r="AC18" s="299"/>
     </row>
     <row r="19" spans="1:29" ht="15.95" customHeight="1">
       <c r="A19" s="81"/>
-      <c r="B19" s="227"/>
-      <c r="C19" s="227"/>
-      <c r="D19" s="227"/>
-      <c r="E19" s="227"/>
-      <c r="F19" s="227"/>
-      <c r="G19" s="227"/>
+      <c r="B19" s="226"/>
+      <c r="C19" s="226"/>
+      <c r="D19" s="226"/>
+      <c r="E19" s="226"/>
+      <c r="F19" s="226"/>
+      <c r="G19" s="226"/>
       <c r="H19" s="160" t="s">
         <v>242</v>
       </c>
       <c r="I19" s="160"/>
-      <c r="J19" s="227"/>
-      <c r="K19" s="227"/>
-      <c r="L19" s="227"/>
-      <c r="M19" s="227"/>
-      <c r="N19" s="227"/>
-      <c r="O19" s="227"/>
-      <c r="P19" s="227"/>
-      <c r="Q19" s="227"/>
-      <c r="R19" s="227"/>
-      <c r="S19" s="227"/>
+      <c r="J19" s="226"/>
+      <c r="K19" s="226"/>
+      <c r="L19" s="226"/>
+      <c r="M19" s="226"/>
+      <c r="N19" s="226"/>
+      <c r="O19" s="226"/>
+      <c r="P19" s="226"/>
+      <c r="Q19" s="226"/>
+      <c r="R19" s="226"/>
+      <c r="S19" s="226"/>
       <c r="T19" s="257"/>
       <c r="U19" s="258"/>
       <c r="V19" s="258"/>
@@ -9897,7 +9903,7 @@
       <c r="H20" s="232" t="s">
         <v>246</v>
       </c>
-      <c r="I20" s="224"/>
+      <c r="I20" s="221"/>
       <c r="J20" s="259" t="s">
         <v>247</v>
       </c>
@@ -9936,14 +9942,14 @@
       <c r="D21" s="81"/>
       <c r="E21" s="257"/>
       <c r="F21" s="257"/>
-      <c r="G21" s="227"/>
-      <c r="H21" s="227"/>
-      <c r="I21" s="227"/>
-      <c r="J21" s="227"/>
-      <c r="K21" s="227"/>
-      <c r="L21" s="227"/>
-      <c r="M21" s="227"/>
-      <c r="N21" s="227"/>
+      <c r="G21" s="226"/>
+      <c r="H21" s="226"/>
+      <c r="I21" s="226"/>
+      <c r="J21" s="226"/>
+      <c r="K21" s="226"/>
+      <c r="L21" s="226"/>
+      <c r="M21" s="226"/>
+      <c r="N21" s="226"/>
       <c r="O21" s="257"/>
       <c r="P21" s="258"/>
       <c r="Q21" s="258"/>
@@ -9967,28 +9973,28 @@
       <c r="B22" s="254"/>
       <c r="C22" s="81"/>
       <c r="D22" s="229"/>
-      <c r="E22" s="324" t="s">
+      <c r="E22" s="326" t="s">
         <v>253</v>
       </c>
-      <c r="F22" s="324"/>
-      <c r="G22" s="324"/>
-      <c r="H22" s="324"/>
-      <c r="I22" s="324"/>
+      <c r="F22" s="326"/>
+      <c r="G22" s="326"/>
+      <c r="H22" s="326"/>
+      <c r="I22" s="326"/>
       <c r="J22" s="229"/>
       <c r="K22" s="229"/>
-      <c r="L22" s="224"/>
+      <c r="L22" s="221"/>
       <c r="M22" s="277" t="s">
         <v>254</v>
       </c>
       <c r="N22" s="277"/>
-      <c r="O22" s="305" t="s">
+      <c r="O22" s="322" t="s">
         <v>255</v>
       </c>
-      <c r="P22" s="305"/>
-      <c r="Q22" s="305"/>
-      <c r="R22" s="305"/>
-      <c r="S22" s="305"/>
-      <c r="T22" s="305"/>
+      <c r="P22" s="322"/>
+      <c r="Q22" s="322"/>
+      <c r="R22" s="322"/>
+      <c r="S22" s="322"/>
+      <c r="T22" s="322"/>
       <c r="U22" s="260" t="s">
         <v>256</v>
       </c>
@@ -10059,8 +10065,8 @@
       <c r="K24" s="134" t="s">
         <v>262</v>
       </c>
-      <c r="L24" s="227"/>
-      <c r="M24" s="227"/>
+      <c r="L24" s="226"/>
+      <c r="M24" s="226"/>
       <c r="N24" s="81"/>
       <c r="O24" s="91" t="s">
         <v>263</v>
@@ -10091,21 +10097,21 @@
         <v>266</v>
       </c>
       <c r="D25" s="81"/>
-      <c r="E25" s="327" t="s">
+      <c r="E25" s="329" t="s">
         <v>267</v>
       </c>
-      <c r="F25" s="327"/>
-      <c r="G25" s="327"/>
-      <c r="H25" s="327"/>
-      <c r="I25" s="327"/>
-      <c r="J25" s="227"/>
+      <c r="F25" s="329"/>
+      <c r="G25" s="329"/>
+      <c r="H25" s="329"/>
+      <c r="I25" s="329"/>
+      <c r="J25" s="226"/>
       <c r="K25" s="91" t="s">
         <v>268</v>
       </c>
-      <c r="L25" s="310" t="s">
+      <c r="L25" s="304" t="s">
         <v>269</v>
       </c>
-      <c r="M25" s="310"/>
+      <c r="M25" s="304"/>
       <c r="N25" s="278" t="s">
         <v>270</v>
       </c>
@@ -10114,22 +10120,22 @@
         <v>271</v>
       </c>
       <c r="Q25" s="81"/>
-      <c r="R25" s="302" t="s">
+      <c r="R25" s="320" t="s">
         <v>272</v>
       </c>
-      <c r="S25" s="302"/>
+      <c r="S25" s="320"/>
       <c r="T25" s="81"/>
       <c r="U25" s="91"/>
-      <c r="V25" s="301" t="s">
+      <c r="V25" s="319" t="s">
         <v>273</v>
       </c>
-      <c r="W25" s="301"/>
-      <c r="X25" s="301"/>
-      <c r="Y25" s="301"/>
-      <c r="Z25" s="301"/>
-      <c r="AA25" s="301"/>
-      <c r="AB25" s="301"/>
-      <c r="AC25" s="301"/>
+      <c r="W25" s="319"/>
+      <c r="X25" s="319"/>
+      <c r="Y25" s="319"/>
+      <c r="Z25" s="319"/>
+      <c r="AA25" s="319"/>
+      <c r="AB25" s="319"/>
+      <c r="AC25" s="319"/>
     </row>
     <row r="26" spans="1:29" ht="15.95" customHeight="1">
       <c r="A26" s="233"/>
@@ -10193,7 +10199,7 @@
       <c r="I27" s="261"/>
       <c r="J27" s="261"/>
       <c r="K27" s="261"/>
-      <c r="L27" s="224"/>
+      <c r="L27" s="221"/>
       <c r="M27" s="259" t="s">
         <v>276</v>
       </c>
@@ -10203,25 +10209,25 @@
       <c r="Q27" s="261"/>
       <c r="R27" s="261"/>
       <c r="S27" s="261"/>
-      <c r="T27" s="224"/>
-      <c r="U27" s="322" t="s">
+      <c r="T27" s="221"/>
+      <c r="U27" s="324" t="s">
         <v>277</v>
       </c>
-      <c r="V27" s="322"/>
-      <c r="W27" s="322"/>
-      <c r="X27" s="289"/>
-      <c r="Y27" s="289"/>
-      <c r="Z27" s="289"/>
-      <c r="AA27" s="289"/>
-      <c r="AB27" s="289"/>
-      <c r="AC27" s="289"/>
+      <c r="V27" s="324"/>
+      <c r="W27" s="324"/>
+      <c r="X27" s="290"/>
+      <c r="Y27" s="290"/>
+      <c r="Z27" s="290"/>
+      <c r="AA27" s="290"/>
+      <c r="AB27" s="290"/>
+      <c r="AC27" s="290"/>
     </row>
     <row r="28" spans="1:29" ht="15.95" customHeight="1">
       <c r="A28" s="81"/>
       <c r="B28" s="137"/>
-      <c r="C28" s="227"/>
+      <c r="C28" s="226"/>
       <c r="D28" s="138"/>
-      <c r="E28" s="227"/>
+      <c r="E28" s="226"/>
       <c r="F28" s="81"/>
       <c r="G28" s="81"/>
       <c r="H28" s="81"/>
@@ -10233,19 +10239,19 @@
       <c r="N28" s="178"/>
       <c r="O28" s="178"/>
       <c r="P28" s="81"/>
-      <c r="Q28" s="227"/>
-      <c r="R28" s="227"/>
-      <c r="S28" s="227"/>
-      <c r="T28" s="227"/>
-      <c r="U28" s="227"/>
-      <c r="V28" s="227"/>
-      <c r="W28" s="227"/>
-      <c r="X28" s="227"/>
-      <c r="Y28" s="227"/>
-      <c r="Z28" s="227"/>
-      <c r="AA28" s="227"/>
-      <c r="AB28" s="227"/>
-      <c r="AC28" s="227"/>
+      <c r="Q28" s="226"/>
+      <c r="R28" s="226"/>
+      <c r="S28" s="226"/>
+      <c r="T28" s="226"/>
+      <c r="U28" s="226"/>
+      <c r="V28" s="226"/>
+      <c r="W28" s="226"/>
+      <c r="X28" s="226"/>
+      <c r="Y28" s="226"/>
+      <c r="Z28" s="226"/>
+      <c r="AA28" s="226"/>
+      <c r="AB28" s="226"/>
+      <c r="AC28" s="226"/>
     </row>
     <row r="29" spans="1:29" ht="15.95" customHeight="1">
       <c r="A29" s="254" t="s">
@@ -10282,10 +10288,10 @@
     </row>
     <row r="30" spans="1:29" ht="15.95" customHeight="1">
       <c r="A30" s="81"/>
-      <c r="B30" s="227"/>
-      <c r="C30" s="227"/>
-      <c r="D30" s="227"/>
-      <c r="E30" s="227"/>
+      <c r="B30" s="226"/>
+      <c r="C30" s="226"/>
+      <c r="D30" s="226"/>
+      <c r="E30" s="226"/>
       <c r="F30" s="257" t="s">
         <v>279</v>
       </c>
@@ -10294,12 +10300,12 @@
       <c r="I30" s="257"/>
       <c r="J30" s="257"/>
       <c r="K30" s="257"/>
-      <c r="L30" s="227"/>
-      <c r="M30" s="227" t="s">
+      <c r="L30" s="226"/>
+      <c r="M30" s="226" t="s">
         <v>280</v>
       </c>
-      <c r="N30" s="227"/>
-      <c r="O30" s="227" t="s">
+      <c r="N30" s="226"/>
+      <c r="O30" s="226" t="s">
         <v>281</v>
       </c>
       <c r="P30" s="180" t="s">
@@ -10334,16 +10340,20 @@
         <v>284</v>
       </c>
       <c r="G31" s="163"/>
-      <c r="H31" s="182"/>
+      <c r="H31" s="182" t="s">
+        <v>285</v>
+      </c>
       <c r="I31" s="163"/>
-      <c r="J31" s="329"/>
-      <c r="K31" s="329"/>
+      <c r="J31" s="331" t="s">
+        <v>286</v>
+      </c>
+      <c r="K31" s="331"/>
       <c r="L31" s="283" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M31" s="283"/>
       <c r="N31" s="283"/>
-      <c r="O31" s="331"/>
+      <c r="O31" s="315"/>
       <c r="P31" s="265"/>
       <c r="Q31" s="265"/>
       <c r="R31" s="265"/>
@@ -10369,21 +10379,21 @@
       <c r="D32" s="268"/>
       <c r="E32" s="268"/>
       <c r="F32" s="183" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G32" s="163"/>
       <c r="H32" s="184" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I32" s="163"/>
       <c r="J32" s="271" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K32" s="271"/>
       <c r="L32" s="284"/>
       <c r="M32" s="284"/>
       <c r="N32" s="284"/>
-      <c r="O32" s="332"/>
+      <c r="O32" s="316"/>
       <c r="P32" s="265"/>
       <c r="Q32" s="265"/>
       <c r="R32" s="265"/>
@@ -10432,7 +10442,7 @@
       </c>
       <c r="L33" s="187"/>
       <c r="M33" s="188" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N33" s="189"/>
       <c r="O33" s="190"/>
@@ -10487,17 +10497,17 @@
       </c>
       <c r="X34" s="279"/>
       <c r="Y34" s="279"/>
-      <c r="Z34" s="306" t="e">
+      <c r="Z34" s="289" t="e">
         <f>IF(_SMSe=0," ",IF(_RSe&gt;60,"R="," "))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AA34" s="306"/>
-      <c r="AB34" s="328" t="e">
+      <c r="AA34" s="289"/>
+      <c r="AB34" s="330" t="e">
         <f>IF(_SMSe=0," ",IF(_RSe&gt;60,'Corrections Calculations'!K54," "))</f>
         <v>#VALUE!</v>
       </c>
-      <c r="AC34" s="328"/>
-      <c r="AD34" s="328"/>
+      <c r="AC34" s="330"/>
+      <c r="AD34" s="330"/>
     </row>
     <row r="35" spans="1:30" ht="15.95" customHeight="1">
       <c r="A35" s="267" t="e">
@@ -10532,7 +10542,7 @@
       </c>
       <c r="L35" s="187"/>
       <c r="M35" s="188" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N35" s="189"/>
       <c r="O35" s="190"/>
@@ -10562,29 +10572,29 @@
       <c r="D36" s="268"/>
       <c r="E36" s="268"/>
       <c r="F36" s="183" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G36" s="163" t="s">
         <v>195</v>
       </c>
       <c r="H36" s="184" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I36" s="163" t="s">
         <v>195</v>
       </c>
       <c r="J36" s="271" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K36" s="271"/>
       <c r="L36" s="193" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="M36" s="193" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="N36" s="193" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O36" s="170"/>
       <c r="P36" s="265"/>
@@ -10605,26 +10615,30 @@
     </row>
     <row r="37" spans="1:30" ht="15.95" customHeight="1">
       <c r="A37" s="259" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B37" s="268"/>
       <c r="C37" s="268"/>
       <c r="D37" s="268"/>
       <c r="E37" s="268"/>
       <c r="F37" s="183" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="G37" s="163" t="s">
         <v>195</v>
       </c>
-      <c r="H37" s="184"/>
+      <c r="H37" s="184" t="s">
+        <v>285</v>
+      </c>
       <c r="I37" s="163" t="s">
         <v>195</v>
       </c>
-      <c r="J37" s="288"/>
+      <c r="J37" s="288" t="s">
+        <v>286</v>
+      </c>
       <c r="K37" s="288"/>
       <c r="L37" s="280" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M37" s="281"/>
       <c r="N37" s="282"/>
@@ -10647,20 +10661,20 @@
     </row>
     <row r="38" spans="1:30" ht="15.95" customHeight="1">
       <c r="A38" s="81"/>
-      <c r="B38" s="227"/>
-      <c r="C38" s="227"/>
-      <c r="D38" s="227"/>
-      <c r="E38" s="227"/>
+      <c r="B38" s="226"/>
+      <c r="C38" s="226"/>
+      <c r="D38" s="226"/>
+      <c r="E38" s="226"/>
       <c r="F38" s="194" t="s">
-        <v>298</v>
-      </c>
-      <c r="G38" s="227"/>
+        <v>300</v>
+      </c>
+      <c r="G38" s="226"/>
       <c r="H38" s="195" t="s">
         <v>185</v>
       </c>
       <c r="I38" s="195"/>
       <c r="J38" s="266" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K38" s="252"/>
       <c r="L38" s="196">
@@ -10673,21 +10687,21 @@
         <v>0.99729999999999996</v>
       </c>
       <c r="O38" s="139" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="P38" s="199"/>
       <c r="Q38" s="199"/>
-      <c r="R38" s="227"/>
-      <c r="S38" s="227"/>
-      <c r="T38" s="227"/>
-      <c r="U38" s="227"/>
+      <c r="R38" s="226"/>
+      <c r="S38" s="226"/>
+      <c r="T38" s="226"/>
+      <c r="U38" s="226"/>
       <c r="V38" s="81"/>
-      <c r="W38" s="325" t="s">
-        <v>301</v>
-      </c>
-      <c r="X38" s="310"/>
+      <c r="W38" s="327" t="s">
+        <v>303</v>
+      </c>
+      <c r="X38" s="304"/>
       <c r="Y38" s="200" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Z38" s="229"/>
       <c r="AA38" s="234"/>
@@ -10697,26 +10711,26 @@
     </row>
     <row r="39" spans="1:30" ht="15.95" customHeight="1">
       <c r="A39" s="81"/>
-      <c r="B39" s="227"/>
-      <c r="C39" s="227"/>
-      <c r="D39" s="227"/>
-      <c r="E39" s="227"/>
-      <c r="F39" s="227"/>
-      <c r="G39" s="227"/>
+      <c r="B39" s="226"/>
+      <c r="C39" s="226"/>
+      <c r="D39" s="226"/>
+      <c r="E39" s="226"/>
+      <c r="F39" s="226"/>
+      <c r="G39" s="226"/>
       <c r="H39" s="195"/>
       <c r="I39" s="195"/>
       <c r="J39" s="195"/>
       <c r="K39" s="160"/>
       <c r="L39" s="160"/>
-      <c r="M39" s="227"/>
-      <c r="N39" s="227"/>
+      <c r="M39" s="226"/>
+      <c r="N39" s="226"/>
       <c r="O39" s="199"/>
       <c r="P39" s="199"/>
       <c r="Q39" s="199"/>
-      <c r="R39" s="227"/>
-      <c r="S39" s="227"/>
-      <c r="T39" s="227"/>
-      <c r="U39" s="227"/>
+      <c r="R39" s="226"/>
+      <c r="S39" s="226"/>
+      <c r="T39" s="226"/>
+      <c r="U39" s="226"/>
       <c r="V39" s="81"/>
       <c r="W39" s="81"/>
       <c r="X39" s="81"/>
@@ -10729,41 +10743,41 @@
     </row>
     <row r="40" spans="1:30" ht="15.95" customHeight="1">
       <c r="A40" s="170"/>
-      <c r="B40" s="224"/>
+      <c r="B40" s="221"/>
       <c r="C40" s="220"/>
       <c r="D40" s="201" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E40" s="202" t="s">
-        <v>304</v>
-      </c>
-      <c r="F40" s="330" t="s">
-        <v>305</v>
-      </c>
-      <c r="G40" s="330"/>
-      <c r="H40" s="330"/>
-      <c r="I40" s="330"/>
-      <c r="J40" s="330"/>
-      <c r="K40" s="330"/>
-      <c r="L40" s="330"/>
-      <c r="M40" s="330"/>
-      <c r="N40" s="330"/>
-      <c r="O40" s="330"/>
-      <c r="P40" s="330"/>
+        <v>306</v>
+      </c>
+      <c r="F40" s="332" t="s">
+        <v>307</v>
+      </c>
+      <c r="G40" s="332"/>
+      <c r="H40" s="332"/>
+      <c r="I40" s="332"/>
+      <c r="J40" s="332"/>
+      <c r="K40" s="332"/>
+      <c r="L40" s="332"/>
+      <c r="M40" s="332"/>
+      <c r="N40" s="332"/>
+      <c r="O40" s="332"/>
+      <c r="P40" s="332"/>
       <c r="Q40" s="234"/>
       <c r="R40" s="234"/>
       <c r="S40" s="234"/>
       <c r="T40" s="234"/>
       <c r="U40" s="277" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="V40" s="278"/>
       <c r="W40" s="287" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="X40" s="287"/>
       <c r="Y40" s="252" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Z40" s="276"/>
       <c r="AA40" s="276"/>
@@ -10773,28 +10787,28 @@
     </row>
     <row r="41" spans="1:30" ht="15.95" customHeight="1">
       <c r="A41" s="81"/>
-      <c r="B41" s="227"/>
-      <c r="C41" s="227"/>
-      <c r="D41" s="227"/>
+      <c r="B41" s="226"/>
+      <c r="C41" s="226"/>
+      <c r="D41" s="226"/>
       <c r="E41" s="236" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F41" s="236"/>
       <c r="G41" s="234"/>
-      <c r="H41" s="227"/>
-      <c r="I41" s="227"/>
-      <c r="J41" s="227"/>
+      <c r="H41" s="226"/>
+      <c r="I41" s="226"/>
+      <c r="J41" s="226"/>
       <c r="K41" s="255"/>
       <c r="L41" s="256"/>
-      <c r="M41" s="227"/>
-      <c r="N41" s="227"/>
-      <c r="O41" s="227"/>
-      <c r="P41" s="227"/>
-      <c r="Q41" s="227"/>
-      <c r="R41" s="227"/>
-      <c r="S41" s="222"/>
-      <c r="T41" s="227"/>
-      <c r="U41" s="227"/>
+      <c r="M41" s="226"/>
+      <c r="N41" s="226"/>
+      <c r="O41" s="226"/>
+      <c r="P41" s="226"/>
+      <c r="Q41" s="226"/>
+      <c r="R41" s="226"/>
+      <c r="S41" s="223"/>
+      <c r="T41" s="226"/>
+      <c r="U41" s="226"/>
       <c r="V41" s="81"/>
       <c r="W41" s="81"/>
       <c r="X41" s="81"/>
@@ -10807,104 +10821,104 @@
     </row>
     <row r="42" spans="1:30" ht="24" customHeight="1">
       <c r="A42" s="273" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B42" s="273"/>
       <c r="C42" s="273"/>
-      <c r="D42" s="326" t="s">
-        <v>311</v>
-      </c>
-      <c r="E42" s="326"/>
-      <c r="F42" s="326"/>
-      <c r="G42" s="326"/>
-      <c r="H42" s="326"/>
-      <c r="I42" s="326"/>
-      <c r="J42" s="326"/>
-      <c r="K42" s="326"/>
-      <c r="L42" s="326"/>
-      <c r="M42" s="326"/>
-      <c r="N42" s="326"/>
-      <c r="O42" s="326"/>
-      <c r="P42" s="326"/>
-      <c r="Q42" s="326"/>
-      <c r="R42" s="326"/>
-      <c r="S42" s="326"/>
-      <c r="T42" s="326"/>
-      <c r="U42" s="326"/>
-      <c r="V42" s="326"/>
-      <c r="W42" s="326"/>
-      <c r="X42" s="326"/>
-      <c r="Y42" s="326"/>
-      <c r="Z42" s="326"/>
-      <c r="AA42" s="326"/>
-      <c r="AB42" s="326"/>
-      <c r="AC42" s="326"/>
+      <c r="D42" s="328" t="s">
+        <v>313</v>
+      </c>
+      <c r="E42" s="328"/>
+      <c r="F42" s="328"/>
+      <c r="G42" s="328"/>
+      <c r="H42" s="328"/>
+      <c r="I42" s="328"/>
+      <c r="J42" s="328"/>
+      <c r="K42" s="328"/>
+      <c r="L42" s="328"/>
+      <c r="M42" s="328"/>
+      <c r="N42" s="328"/>
+      <c r="O42" s="328"/>
+      <c r="P42" s="328"/>
+      <c r="Q42" s="328"/>
+      <c r="R42" s="328"/>
+      <c r="S42" s="328"/>
+      <c r="T42" s="328"/>
+      <c r="U42" s="328"/>
+      <c r="V42" s="328"/>
+      <c r="W42" s="328"/>
+      <c r="X42" s="328"/>
+      <c r="Y42" s="328"/>
+      <c r="Z42" s="328"/>
+      <c r="AA42" s="328"/>
+      <c r="AB42" s="328"/>
+      <c r="AC42" s="328"/>
       <c r="AD42" s="81"/>
     </row>
     <row r="43" spans="1:30" ht="24" customHeight="1">
       <c r="A43" s="273" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B43" s="273"/>
       <c r="C43" s="273"/>
-      <c r="D43" s="326"/>
-      <c r="E43" s="326"/>
-      <c r="F43" s="326"/>
-      <c r="G43" s="326"/>
-      <c r="H43" s="326"/>
-      <c r="I43" s="326"/>
-      <c r="J43" s="326"/>
-      <c r="K43" s="326"/>
-      <c r="L43" s="326"/>
-      <c r="M43" s="326"/>
-      <c r="N43" s="326"/>
-      <c r="O43" s="326"/>
-      <c r="P43" s="326"/>
-      <c r="Q43" s="326"/>
-      <c r="R43" s="326"/>
-      <c r="S43" s="326"/>
-      <c r="T43" s="326"/>
-      <c r="U43" s="326"/>
-      <c r="V43" s="326"/>
-      <c r="W43" s="326"/>
-      <c r="X43" s="326"/>
-      <c r="Y43" s="326"/>
-      <c r="Z43" s="326"/>
-      <c r="AA43" s="326"/>
-      <c r="AB43" s="326"/>
-      <c r="AC43" s="326"/>
+      <c r="D43" s="328"/>
+      <c r="E43" s="328"/>
+      <c r="F43" s="328"/>
+      <c r="G43" s="328"/>
+      <c r="H43" s="328"/>
+      <c r="I43" s="328"/>
+      <c r="J43" s="328"/>
+      <c r="K43" s="328"/>
+      <c r="L43" s="328"/>
+      <c r="M43" s="328"/>
+      <c r="N43" s="328"/>
+      <c r="O43" s="328"/>
+      <c r="P43" s="328"/>
+      <c r="Q43" s="328"/>
+      <c r="R43" s="328"/>
+      <c r="S43" s="328"/>
+      <c r="T43" s="328"/>
+      <c r="U43" s="328"/>
+      <c r="V43" s="328"/>
+      <c r="W43" s="328"/>
+      <c r="X43" s="328"/>
+      <c r="Y43" s="328"/>
+      <c r="Z43" s="328"/>
+      <c r="AA43" s="328"/>
+      <c r="AB43" s="328"/>
+      <c r="AC43" s="328"/>
       <c r="AD43" s="81"/>
     </row>
     <row r="44" spans="1:30" ht="24" customHeight="1">
       <c r="A44" s="81"/>
       <c r="B44" s="81"/>
       <c r="C44" s="81"/>
-      <c r="D44" s="326"/>
-      <c r="E44" s="326"/>
-      <c r="F44" s="326"/>
-      <c r="G44" s="326"/>
-      <c r="H44" s="326"/>
-      <c r="I44" s="326"/>
-      <c r="J44" s="326"/>
-      <c r="K44" s="326"/>
-      <c r="L44" s="326"/>
-      <c r="M44" s="326"/>
-      <c r="N44" s="326"/>
-      <c r="O44" s="326"/>
-      <c r="P44" s="326"/>
-      <c r="Q44" s="326"/>
-      <c r="R44" s="326"/>
-      <c r="S44" s="326"/>
-      <c r="T44" s="326"/>
-      <c r="U44" s="326"/>
-      <c r="V44" s="326"/>
-      <c r="W44" s="326"/>
-      <c r="X44" s="326"/>
-      <c r="Y44" s="326"/>
-      <c r="Z44" s="326"/>
-      <c r="AA44" s="326"/>
-      <c r="AB44" s="326"/>
-      <c r="AC44" s="326"/>
+      <c r="D44" s="328"/>
+      <c r="E44" s="328"/>
+      <c r="F44" s="328"/>
+      <c r="G44" s="328"/>
+      <c r="H44" s="328"/>
+      <c r="I44" s="328"/>
+      <c r="J44" s="328"/>
+      <c r="K44" s="328"/>
+      <c r="L44" s="328"/>
+      <c r="M44" s="328"/>
+      <c r="N44" s="328"/>
+      <c r="O44" s="328"/>
+      <c r="P44" s="328"/>
+      <c r="Q44" s="328"/>
+      <c r="R44" s="328"/>
+      <c r="S44" s="328"/>
+      <c r="T44" s="328"/>
+      <c r="U44" s="328"/>
+      <c r="V44" s="328"/>
+      <c r="W44" s="328"/>
+      <c r="X44" s="328"/>
+      <c r="Y44" s="328"/>
+      <c r="Z44" s="328"/>
+      <c r="AA44" s="328"/>
+      <c r="AB44" s="328"/>
+      <c r="AC44" s="328"/>
       <c r="AD44" s="81"/>
     </row>
     <row r="45" spans="1:30" ht="24" customHeight="1">
@@ -10912,7 +10926,7 @@
       <c r="B45" s="81"/>
       <c r="C45" s="81"/>
       <c r="D45" s="253" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E45" s="260"/>
       <c r="F45" s="260"/>
@@ -10945,8 +10959,8 @@
       <c r="A46" s="81"/>
       <c r="B46" s="81"/>
       <c r="C46" s="81"/>
-      <c r="D46" s="323" t="s">
-        <v>314</v>
+      <c r="D46" s="325" t="s">
+        <v>316</v>
       </c>
       <c r="E46" s="253"/>
       <c r="F46" s="253"/>
@@ -11081,6 +11095,15 @@
     <mergeCell ref="P13:R13"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="P9:R9"/>
+    <mergeCell ref="E14:O14"/>
+    <mergeCell ref="V25:AC25"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="R25:S25"/>
+    <mergeCell ref="E10:O10"/>
+    <mergeCell ref="S7:V7"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="O22:T22"/>
+    <mergeCell ref="S11:AC11"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A3:F3"/>
@@ -11093,14 +11116,6 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="K5:L5"/>
     <mergeCell ref="J2:T2"/>
-    <mergeCell ref="E14:O14"/>
-    <mergeCell ref="V25:AC25"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="E10:O10"/>
-    <mergeCell ref="S7:V7"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="O22:T22"/>
     <mergeCell ref="Z34:AA34"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="J20:K20"/>
@@ -11125,7 +11140,6 @@
     <mergeCell ref="P7:R7"/>
     <mergeCell ref="S9:AC9"/>
     <mergeCell ref="E7:F7"/>
-    <mergeCell ref="S11:AC11"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="E15:R15"/>
     <mergeCell ref="F30:K30"/>
@@ -11233,88 +11247,88 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="156" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B1" s="156"/>
       <c r="C1" s="156"/>
       <c r="D1" s="156"/>
       <c r="E1" s="156"/>
       <c r="F1" s="156" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G1" s="156"/>
       <c r="H1" s="156"/>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="81" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B2" s="90" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C2" s="156"/>
       <c r="D2" s="156"/>
       <c r="E2" s="156"/>
       <c r="F2" s="156" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G2" s="156"/>
       <c r="H2" s="156"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="156" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B3" s="78" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C3" s="156"/>
       <c r="D3" s="156"/>
       <c r="E3" s="156"/>
       <c r="F3" s="156" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G3" s="156"/>
       <c r="H3" s="156"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="156" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B4" s="79" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C4" s="156"/>
       <c r="D4" s="156"/>
       <c r="E4" s="156"/>
       <c r="F4" s="156" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G4" s="156"/>
       <c r="H4" s="156"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="156" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B5" s="79" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C5" s="156"/>
       <c r="D5" s="156"/>
       <c r="E5" s="156"/>
       <c r="F5" s="156" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G5" s="156"/>
       <c r="H5" s="156"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="81" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B6" s="79" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C6" s="156"/>
       <c r="D6" s="156"/>
@@ -11325,26 +11339,26 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="156" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B7" s="79" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C7" s="156"/>
       <c r="D7" s="156"/>
       <c r="E7" s="156"/>
       <c r="F7" s="156" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G7" s="156"/>
       <c r="H7" s="156"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="156" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B8" s="79" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C8" s="156"/>
       <c r="D8" s="156"/>
@@ -11355,50 +11369,50 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="156" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B9" s="79" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C9" s="156" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D9" s="156"/>
       <c r="E9" s="156" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F9" s="156"/>
       <c r="G9" s="156" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H9" s="156" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="156"/>
       <c r="B10" s="79" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C10" s="156" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D10" s="156"/>
       <c r="E10" s="156" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F10" s="156"/>
       <c r="G10" s="156" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H10" s="156" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="156"/>
       <c r="B11" s="79" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C11" s="156"/>
       <c r="D11" s="156"/>
@@ -11409,10 +11423,10 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B12" s="79" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C12" s="156"/>
       <c r="D12" s="156"/>
@@ -11423,10 +11437,10 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B13" s="79" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C13" s="156"/>
       <c r="D13" s="156"/>
@@ -11437,10 +11451,10 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="156" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B14" s="78" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C14" s="156"/>
       <c r="D14" s="156"/>
@@ -11452,7 +11466,7 @@
     <row r="15" spans="1:8">
       <c r="A15" s="156"/>
       <c r="B15" s="79" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C15" s="156"/>
       <c r="D15" s="156"/>
@@ -11464,7 +11478,7 @@
     <row r="16" spans="1:8">
       <c r="A16" s="156"/>
       <c r="B16" s="78" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C16" s="156"/>
       <c r="D16" s="156"/>
@@ -11476,138 +11490,138 @@
     <row r="17" spans="1:8">
       <c r="A17" s="156"/>
       <c r="B17" s="79" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C17" s="156" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D17" s="156"/>
       <c r="E17" s="156"/>
       <c r="F17" s="156" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G17" s="156"/>
       <c r="H17" s="156" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="156"/>
       <c r="B18" s="79" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C18" s="156" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D18" s="156"/>
       <c r="E18" s="156"/>
       <c r="F18" s="156" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G18" s="156"/>
       <c r="H18" s="156" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="156"/>
       <c r="B19" s="80" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C19" s="156"/>
       <c r="D19" s="156"/>
       <c r="E19" s="156"/>
       <c r="F19" s="156" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G19" s="156"/>
       <c r="H19" s="156" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="156" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B20" s="79" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C20" s="156"/>
       <c r="D20" s="156"/>
       <c r="E20" s="156"/>
       <c r="F20" s="156" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G20" s="156"/>
       <c r="H20" s="156"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="156" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B21" s="78" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C21" s="156"/>
       <c r="D21" s="156"/>
       <c r="E21" s="156"/>
       <c r="F21" s="156" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G21" s="156"/>
       <c r="H21" s="156"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="156" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B22" s="78" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C22" s="156"/>
       <c r="D22" s="156"/>
       <c r="E22" s="156"/>
       <c r="F22" s="156" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="G22" s="156"/>
       <c r="H22" s="156"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="156" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B23" s="142" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C23" s="156"/>
       <c r="D23" s="156"/>
       <c r="E23" s="156"/>
       <c r="F23" s="156" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="G23" s="156"/>
       <c r="H23" s="156"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="156" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B24" s="219" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C24" s="156"/>
       <c r="D24" s="156"/>
       <c r="E24" s="156"/>
       <c r="F24" s="156" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G24" s="156"/>
       <c r="H24" s="156"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="156" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B25" s="156"/>
       <c r="C25" s="156"/>
@@ -11619,21 +11633,21 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="156" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B26" s="156"/>
       <c r="C26" s="156"/>
       <c r="D26" s="156"/>
       <c r="E26" s="156"/>
       <c r="F26" s="156" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="G26" s="156"/>
       <c r="H26" s="156"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="156" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B27" s="156"/>
       <c r="C27" s="156">
@@ -11643,7 +11657,7 @@
       <c r="D27" s="156"/>
       <c r="E27" s="156"/>
       <c r="F27" s="156" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G27" s="156"/>
       <c r="H27" s="156"/>
@@ -11658,7 +11672,7 @@
       <c r="D28" s="156"/>
       <c r="E28" s="156"/>
       <c r="F28" s="156" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G28" s="156"/>
       <c r="H28" s="156"/>
@@ -11673,14 +11687,14 @@
       <c r="D29" s="156"/>
       <c r="E29" s="156"/>
       <c r="F29" s="156" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G29" s="156"/>
       <c r="H29" s="156"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="81" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B30" s="156"/>
       <c r="C30" s="156">
@@ -11695,7 +11709,7 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="81" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B31" s="156"/>
       <c r="C31" s="156">
@@ -11710,7 +11724,7 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="81" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B32" s="156"/>
       <c r="C32" s="156">
@@ -11725,7 +11739,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="81" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B33" s="156"/>
       <c r="C33" s="156">
@@ -11735,12 +11749,12 @@
       <c r="D33" s="156"/>
       <c r="E33" s="156"/>
       <c r="F33" s="156" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="81" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B34" s="156"/>
       <c r="C34" s="156">
@@ -11750,12 +11764,12 @@
       <c r="D34" s="156"/>
       <c r="E34" s="156"/>
       <c r="F34" s="156" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="81" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B35" s="156"/>
       <c r="C35" s="156">
@@ -11765,12 +11779,12 @@
       <c r="D35" s="156"/>
       <c r="E35" s="156"/>
       <c r="F35" s="156" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="81" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B36" s="156"/>
       <c r="C36" s="156"/>
@@ -11780,68 +11794,68 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="81" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B37" s="156"/>
       <c r="C37" s="156"/>
       <c r="D37" s="90" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E37" s="156"/>
       <c r="F37" s="156" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="81" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B38" s="156"/>
       <c r="C38" s="156"/>
       <c r="D38" s="90" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E38" s="156"/>
       <c r="F38" s="156" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="81" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B39" s="156"/>
       <c r="C39" s="156"/>
       <c r="D39" s="90" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E39" s="156"/>
       <c r="F39" s="156" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="81" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B40" s="156"/>
       <c r="C40" s="156"/>
       <c r="D40" s="156"/>
       <c r="E40" s="156"/>
       <c r="F40" s="156" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="13.5" thickBot="1">
       <c r="A41" s="81" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B41" s="156"/>
       <c r="C41" s="156"/>
       <c r="D41" s="156"/>
       <c r="E41" s="156"/>
       <c r="F41" s="156" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -11853,12 +11867,12 @@
       <c r="D42" s="156"/>
       <c r="E42" s="156"/>
       <c r="F42" s="156" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="156" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B43" s="13">
         <v>1</v>
@@ -11867,12 +11881,12 @@
       <c r="D43" s="156"/>
       <c r="E43" s="156"/>
       <c r="F43" s="156" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="156" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B44" s="13">
         <v>1</v>
@@ -11884,7 +11898,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="156" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B45" s="13">
         <v>1</v>
@@ -11896,7 +11910,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="156" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B46" s="13">
         <v>1</v>
@@ -11908,7 +11922,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="156" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B47" s="13">
         <v>2</v>
@@ -11920,7 +11934,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="156" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B48" s="13">
         <v>3</v>
@@ -11929,12 +11943,12 @@
       <c r="D48" s="156"/>
       <c r="E48" s="156"/>
       <c r="F48" s="156" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="156" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B49" s="13">
         <v>4</v>
@@ -11943,14 +11957,14 @@
       <c r="D49" s="156"/>
       <c r="E49" s="156"/>
       <c r="F49" s="156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="G49" s="156"/>
       <c r="H49" s="156"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="156" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B50" s="13">
         <v>5</v>
@@ -11959,7 +11973,7 @@
       <c r="D50" s="156"/>
       <c r="E50" s="156"/>
       <c r="F50" s="156" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="G50" s="156"/>
       <c r="H50" s="156"/>
@@ -11967,7 +11981,7 @@
     <row r="51" spans="1:8" ht="13.5" thickBot="1">
       <c r="A51" s="156"/>
       <c r="B51" s="14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C51" s="156"/>
       <c r="D51" s="156"/>
@@ -11978,7 +11992,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="81" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B52" s="156"/>
       <c r="C52" s="156"/>
@@ -11990,7 +12004,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="156" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B53" s="156"/>
       <c r="C53" s="156"/>
@@ -12002,7 +12016,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="156" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B54" s="156"/>
       <c r="C54" s="156"/>
@@ -12014,7 +12028,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="156" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B55" s="156"/>
       <c r="C55" s="156"/>
@@ -12026,7 +12040,7 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="156" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B56" s="156"/>
       <c r="C56" s="156"/>
@@ -12038,7 +12052,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="156" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B57" s="156"/>
       <c r="C57" s="156"/>
@@ -12050,121 +12064,121 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="156" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B58" s="156"/>
       <c r="C58" s="156"/>
       <c r="D58" s="156"/>
       <c r="E58" s="156" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F58" s="156" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G58" s="156" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="H58" s="156"/>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="81" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B60" s="156"/>
       <c r="C60" s="219"/>
       <c r="D60" s="219"/>
       <c r="E60" s="219" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F60" s="219" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G60" s="219"/>
       <c r="H60" s="219"/>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="218" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B61" s="218" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C61" s="156"/>
       <c r="D61" s="156"/>
       <c r="E61" s="219" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F61" s="219" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G61" s="219"/>
       <c r="H61" s="219"/>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="218" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B62" s="156" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C62" s="156"/>
       <c r="D62" s="156"/>
       <c r="E62" s="219" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F62" s="219" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G62" s="219"/>
       <c r="H62" s="219"/>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="218" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B63" s="219" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C63" s="156"/>
       <c r="D63" s="156"/>
       <c r="E63" s="219" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F63" s="219" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="G63" s="219"/>
       <c r="H63" s="219"/>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="218" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B64" s="219" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C64" s="156"/>
       <c r="D64" s="156"/>
       <c r="E64" s="219" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F64" s="218" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G64" s="219"/>
       <c r="H64" s="219"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="218" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B65" s="219" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C65" s="156"/>
       <c r="D65" s="156"/>
       <c r="E65" s="219" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F65" s="219"/>
       <c r="G65" s="219"/>
@@ -12175,12 +12189,12 @@
         <v>261</v>
       </c>
       <c r="B66" s="219" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C66" s="156"/>
       <c r="D66" s="156"/>
       <c r="E66" s="219" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F66" s="156"/>
       <c r="G66" s="156"/>
@@ -12188,10 +12202,10 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="219" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B67" s="219" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C67" s="156"/>
       <c r="D67" s="156"/>
@@ -12203,7 +12217,7 @@
     <row r="68" spans="1:8">
       <c r="A68" s="156"/>
       <c r="B68" s="219" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C68" s="156"/>
       <c r="D68" s="156"/>
@@ -12215,7 +12229,7 @@
     <row r="69" spans="1:8">
       <c r="A69" s="156"/>
       <c r="B69" s="219" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C69" s="156"/>
       <c r="D69" s="156"/>
@@ -12226,10 +12240,10 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="156" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B70" s="219" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C70" s="156"/>
       <c r="D70" s="156"/>
@@ -12240,10 +12254,10 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="156" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B71" s="218" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C71" s="156"/>
       <c r="D71" s="156"/>
@@ -12254,10 +12268,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="156" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B72" s="219" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C72" s="219"/>
       <c r="D72" s="219"/>
@@ -12269,7 +12283,7 @@
     <row r="73" spans="1:8">
       <c r="A73" s="156"/>
       <c r="B73" s="219" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C73" s="219"/>
       <c r="D73" s="219"/>
@@ -12281,7 +12295,7 @@
     <row r="74" spans="1:8">
       <c r="A74" s="156"/>
       <c r="B74" s="219" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C74" s="219"/>
       <c r="D74" s="219"/>
@@ -12293,7 +12307,7 @@
     <row r="75" spans="1:8">
       <c r="A75" s="156"/>
       <c r="B75" s="219" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C75" s="219"/>
       <c r="D75" s="219"/>
@@ -12305,7 +12319,7 @@
     <row r="76" spans="1:8">
       <c r="A76" s="156"/>
       <c r="B76" s="218" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C76" s="219"/>
       <c r="D76" s="219"/>
@@ -12317,7 +12331,7 @@
     <row r="77" spans="1:8">
       <c r="A77" s="156"/>
       <c r="B77" s="219" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C77" s="219"/>
       <c r="D77" s="219"/>
@@ -12329,7 +12343,7 @@
     <row r="78" spans="1:8">
       <c r="A78" s="156"/>
       <c r="B78" s="219" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C78" s="219"/>
       <c r="D78" s="219"/>
@@ -12341,7 +12355,7 @@
     <row r="79" spans="1:8">
       <c r="A79" s="156"/>
       <c r="B79" s="219" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C79" s="219"/>
       <c r="D79" s="219"/>
@@ -12353,7 +12367,7 @@
     <row r="80" spans="1:8">
       <c r="A80" s="156"/>
       <c r="B80" s="219" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C80" s="219"/>
       <c r="D80" s="219"/>
@@ -12364,7 +12378,7 @@
     </row>
     <row r="81" spans="2:5">
       <c r="B81" s="218" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C81" s="219"/>
       <c r="D81" s="219"/>
@@ -12372,7 +12386,7 @@
     </row>
     <row r="82" spans="2:5">
       <c r="B82" s="219" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C82" s="219"/>
       <c r="D82" s="219"/>
@@ -12380,7 +12394,7 @@
     </row>
     <row r="83" spans="2:5">
       <c r="B83" s="219" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C83" s="219"/>
       <c r="D83" s="219"/>
@@ -12388,7 +12402,7 @@
     </row>
     <row r="84" spans="2:5">
       <c r="B84" s="219" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C84" s="156"/>
       <c r="D84" s="156"/>
@@ -12396,7 +12410,7 @@
     </row>
     <row r="85" spans="2:5">
       <c r="B85" s="219" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C85" s="219"/>
       <c r="D85" s="219"/>
@@ -12404,7 +12418,7 @@
     </row>
     <row r="86" spans="2:5">
       <c r="B86" s="219" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C86" s="219"/>
       <c r="D86" s="219"/>
@@ -12418,7 +12432,7 @@
     </row>
     <row r="88" spans="2:5">
       <c r="B88" s="219" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C88" s="219"/>
       <c r="D88" s="219"/>
@@ -12426,7 +12440,7 @@
     </row>
     <row r="89" spans="2:5">
       <c r="B89" s="219" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C89" s="219"/>
       <c r="D89" s="219"/>
@@ -12434,7 +12448,7 @@
     </row>
     <row r="90" spans="2:5">
       <c r="B90" s="219" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C90" s="219"/>
       <c r="D90" s="219"/>
@@ -12442,7 +12456,7 @@
     </row>
     <row r="91" spans="2:5">
       <c r="B91" s="219" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C91" s="219"/>
       <c r="D91" s="219"/>
@@ -12450,7 +12464,7 @@
     </row>
     <row r="92" spans="2:5">
       <c r="B92" s="219" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C92" s="219"/>
       <c r="D92" s="219"/>
@@ -12458,7 +12472,7 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" s="219" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C93" s="219"/>
       <c r="D93" s="219"/>
@@ -12466,7 +12480,7 @@
     </row>
     <row r="94" spans="2:5">
       <c r="B94" s="219" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C94" s="219"/>
       <c r="D94" s="219"/>
@@ -12474,7 +12488,7 @@
     </row>
     <row r="95" spans="2:5">
       <c r="B95" s="219" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C95" s="219"/>
       <c r="D95" s="219"/>
@@ -12482,7 +12496,7 @@
     </row>
     <row r="96" spans="2:5">
       <c r="B96" s="219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C96" s="219"/>
       <c r="D96" s="219"/>
@@ -12490,7 +12504,7 @@
     </row>
     <row r="97" spans="2:5">
       <c r="B97" s="219" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C97" s="219"/>
       <c r="D97" s="219"/>
@@ -12498,7 +12512,7 @@
     </row>
     <row r="98" spans="2:5">
       <c r="B98" s="219" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C98" s="156"/>
       <c r="D98" s="156"/>
@@ -12506,7 +12520,7 @@
     </row>
     <row r="99" spans="2:5">
       <c r="B99" s="219" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C99" s="156"/>
       <c r="D99" s="156"/>
@@ -12514,7 +12528,7 @@
     </row>
     <row r="100" spans="2:5">
       <c r="B100" s="219" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C100" s="156"/>
       <c r="D100" s="156"/>
@@ -12540,7 +12554,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
       <c r="A1" s="253" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B1" s="260"/>
       <c r="C1" s="260"/>
@@ -12558,21 +12572,21 @@
     </row>
     <row r="4" spans="1:14" ht="15.95" customHeight="1">
       <c r="A4" s="260" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B4" s="260"/>
       <c r="C4" s="260"/>
       <c r="D4" s="260"/>
       <c r="E4" s="156"/>
       <c r="F4" s="260" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="G4" s="260"/>
       <c r="H4" s="260"/>
       <c r="I4" s="260"/>
       <c r="J4" s="156"/>
       <c r="K4" s="260" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L4" s="260"/>
       <c r="M4" s="260"/>
@@ -12580,7 +12594,7 @@
     </row>
     <row r="5" spans="1:14" ht="15.95" customHeight="1">
       <c r="A5" s="260" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B5" s="336"/>
       <c r="C5" s="336"/>
@@ -12598,21 +12612,21 @@
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="337" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B6" s="337"/>
       <c r="C6" s="337"/>
       <c r="D6" s="337"/>
       <c r="E6" s="156"/>
       <c r="F6" s="333" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G6" s="333"/>
       <c r="H6" s="333"/>
       <c r="I6" s="333"/>
       <c r="J6" s="156"/>
       <c r="K6" s="333" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L6" s="333"/>
       <c r="M6" s="333"/>
@@ -12620,21 +12634,21 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="337" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B7" s="337"/>
       <c r="C7" s="337"/>
       <c r="D7" s="337"/>
       <c r="E7" s="156"/>
       <c r="F7" s="333" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G7" s="333"/>
       <c r="H7" s="333"/>
       <c r="I7" s="333"/>
       <c r="J7" s="156"/>
       <c r="K7" s="333" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L7" s="333"/>
       <c r="M7" s="333"/>
@@ -12642,21 +12656,21 @@
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="337" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B8" s="337"/>
       <c r="C8" s="337"/>
       <c r="D8" s="337"/>
       <c r="E8" s="156"/>
       <c r="F8" s="333" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G8" s="333"/>
       <c r="H8" s="333"/>
       <c r="I8" s="333"/>
       <c r="J8" s="156"/>
       <c r="K8" s="333" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L8" s="333"/>
       <c r="M8" s="333"/>
@@ -12664,21 +12678,21 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="337" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B9" s="337"/>
       <c r="C9" s="337"/>
       <c r="D9" s="337"/>
       <c r="E9" s="156"/>
       <c r="F9" s="333" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="G9" s="333"/>
       <c r="H9" s="333"/>
       <c r="I9" s="333"/>
       <c r="J9" s="156"/>
       <c r="K9" s="333" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="L9" s="333"/>
       <c r="M9" s="333"/>
@@ -12686,7 +12700,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="337" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B10" s="337"/>
       <c r="C10" s="337"/>
@@ -12698,7 +12712,7 @@
       <c r="I10" s="156"/>
       <c r="J10" s="156"/>
       <c r="K10" s="333" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="L10" s="333"/>
       <c r="M10" s="333"/>
@@ -12716,7 +12730,7 @@
       <c r="I11" s="156"/>
       <c r="J11" s="156"/>
       <c r="K11" s="333" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L11" s="333"/>
       <c r="M11" s="333"/>
@@ -12734,7 +12748,7 @@
       <c r="I12" s="156"/>
       <c r="J12" s="156"/>
       <c r="K12" s="333" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="L12" s="333"/>
       <c r="M12" s="333"/>
@@ -12752,7 +12766,7 @@
       <c r="I13" s="156"/>
       <c r="J13" s="156"/>
       <c r="K13" s="333" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="L13" s="333"/>
       <c r="M13" s="333"/>
@@ -12770,7 +12784,7 @@
       <c r="I14" s="156"/>
       <c r="J14" s="156"/>
       <c r="K14" s="333" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L14" s="333"/>
       <c r="M14" s="333"/>
@@ -12788,7 +12802,7 @@
       <c r="I15" s="156"/>
       <c r="J15" s="156"/>
       <c r="K15" s="333" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L15" s="333"/>
       <c r="M15" s="333"/>
@@ -12806,7 +12820,7 @@
       <c r="I16" s="156"/>
       <c r="J16" s="156"/>
       <c r="K16" s="333" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L16" s="333"/>
       <c r="M16" s="333"/>
@@ -12846,21 +12860,21 @@
     </row>
     <row r="19" spans="1:14" ht="15.95" customHeight="1">
       <c r="A19" s="260" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B19" s="260"/>
       <c r="C19" s="260"/>
       <c r="D19" s="260"/>
       <c r="E19" s="156"/>
       <c r="F19" s="260" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G19" s="260"/>
       <c r="H19" s="260"/>
       <c r="I19" s="260"/>
       <c r="J19" s="156"/>
       <c r="K19" s="260" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L19" s="260"/>
       <c r="M19" s="260"/>
@@ -12873,14 +12887,14 @@
       <c r="D20" s="156"/>
       <c r="E20" s="156"/>
       <c r="F20" s="334" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G20" s="334"/>
       <c r="H20" s="334"/>
       <c r="I20" s="334"/>
       <c r="J20" s="156"/>
       <c r="K20" s="333" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L20" s="333"/>
       <c r="M20" s="333"/>
@@ -12888,21 +12902,21 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="333" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B21" s="333"/>
       <c r="C21" s="333"/>
       <c r="D21" s="333"/>
       <c r="E21" s="156"/>
       <c r="F21" s="334" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="G21" s="334"/>
       <c r="H21" s="334"/>
       <c r="I21" s="334"/>
       <c r="J21" s="156"/>
       <c r="K21" s="333" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L21" s="333"/>
       <c r="M21" s="333"/>
@@ -12910,7 +12924,7 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="333" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B22" s="333"/>
       <c r="C22" s="333"/>
@@ -12922,7 +12936,7 @@
       <c r="I22" s="333"/>
       <c r="J22" s="156"/>
       <c r="K22" s="333" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L22" s="333"/>
       <c r="M22" s="333"/>
@@ -12930,21 +12944,21 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="333" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B23" s="333"/>
       <c r="C23" s="333"/>
       <c r="D23" s="333"/>
       <c r="E23" s="156"/>
       <c r="F23" s="335" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G23" s="335"/>
       <c r="H23" s="335"/>
       <c r="I23" s="335"/>
       <c r="J23" s="156"/>
       <c r="K23" s="333" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L23" s="333"/>
       <c r="M23" s="333"/>
@@ -12952,7 +12966,7 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="333" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B24" s="333"/>
       <c r="C24" s="333"/>
@@ -12964,7 +12978,7 @@
       <c r="I24" s="335"/>
       <c r="J24" s="156"/>
       <c r="K24" s="333" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="L24" s="333"/>
       <c r="M24" s="333"/>
@@ -12972,21 +12986,21 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="333" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B25" s="333"/>
       <c r="C25" s="333"/>
       <c r="D25" s="333"/>
       <c r="E25" s="156"/>
       <c r="F25" s="239" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="G25" s="239"/>
       <c r="H25" s="239"/>
       <c r="I25" s="239"/>
       <c r="J25" s="156"/>
       <c r="K25" s="333" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L25" s="333"/>
       <c r="M25" s="333"/>
@@ -12994,14 +13008,14 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="333" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B26" s="333"/>
       <c r="C26" s="333"/>
       <c r="D26" s="333"/>
       <c r="E26" s="156"/>
       <c r="F26" s="239" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="G26" s="239"/>
       <c r="H26" s="239"/>
@@ -13014,7 +13028,7 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="333" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B27" s="333"/>
       <c r="C27" s="333"/>
@@ -13032,14 +13046,14 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="333" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B28" s="333"/>
       <c r="C28" s="333"/>
       <c r="D28" s="333"/>
       <c r="E28" s="156"/>
       <c r="F28" s="239" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="G28" s="239"/>
       <c r="H28" s="239"/>
@@ -13052,14 +13066,14 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="333" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B29" s="333"/>
       <c r="C29" s="333"/>
       <c r="D29" s="333"/>
       <c r="E29" s="156"/>
       <c r="F29" s="239" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="G29" s="239"/>
       <c r="H29" s="239"/>
@@ -13072,7 +13086,7 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="333" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B30" s="333"/>
       <c r="C30" s="333"/>
@@ -13085,21 +13099,21 @@
       <c r="J30" s="156"/>
       <c r="K30" s="156"/>
       <c r="L30" s="72" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M30" s="156"/>
       <c r="N30" s="156"/>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="333" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B31" s="333"/>
       <c r="C31" s="333"/>
       <c r="D31" s="333"/>
       <c r="E31" s="156"/>
       <c r="F31" s="239" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="G31" s="239"/>
       <c r="H31" s="239"/>
@@ -13107,21 +13121,21 @@
       <c r="J31" s="156"/>
       <c r="K31" s="156"/>
       <c r="L31" s="156" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M31" s="156"/>
       <c r="N31" s="156"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="333" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B32" s="333"/>
       <c r="C32" s="333"/>
       <c r="D32" s="333"/>
       <c r="E32" s="156"/>
       <c r="F32" s="239" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="G32" s="239"/>
       <c r="H32" s="239"/>
@@ -13129,14 +13143,14 @@
       <c r="J32" s="156"/>
       <c r="K32" s="156"/>
       <c r="L32" s="156" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M32" s="156"/>
       <c r="N32" s="156"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="333" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B33" s="333"/>
       <c r="C33" s="333"/>
@@ -13149,19 +13163,19 @@
       <c r="J33" s="156"/>
       <c r="K33" s="156"/>
       <c r="L33" s="156" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="333" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B34" s="333"/>
       <c r="C34" s="333"/>
       <c r="D34" s="333"/>
       <c r="E34" s="156"/>
       <c r="F34" s="239" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="G34" s="239"/>
       <c r="H34" s="239"/>
@@ -13172,14 +13186,14 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="333" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B35" s="333"/>
       <c r="C35" s="333"/>
       <c r="D35" s="333"/>
       <c r="E35" s="156"/>
       <c r="F35" s="239" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G35" s="239"/>
       <c r="H35" s="239"/>
@@ -13190,7 +13204,7 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="333" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B36" s="333"/>
       <c r="C36" s="333"/>
@@ -13206,14 +13220,14 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="333" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B37" s="333"/>
       <c r="C37" s="333"/>
       <c r="D37" s="333"/>
       <c r="E37" s="156"/>
       <c r="F37" s="239" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="G37" s="239"/>
       <c r="H37" s="239"/>
@@ -13224,7 +13238,7 @@
     </row>
     <row r="38" spans="1:12">
       <c r="A38" s="333" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B38" s="333"/>
       <c r="C38" s="333"/>
@@ -13240,14 +13254,14 @@
     </row>
     <row r="39" spans="1:12">
       <c r="A39" s="333" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B39" s="333"/>
       <c r="C39" s="333"/>
       <c r="D39" s="333"/>
       <c r="E39" s="156"/>
       <c r="F39" s="239" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="G39" s="239"/>
       <c r="H39" s="239"/>
@@ -13258,7 +13272,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="333" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B40" s="333"/>
       <c r="C40" s="333"/>
@@ -13274,14 +13288,14 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="333" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B41" s="333"/>
       <c r="C41" s="333"/>
       <c r="D41" s="333"/>
       <c r="E41" s="156"/>
       <c r="F41" s="335" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G41" s="335"/>
       <c r="H41" s="335"/>
@@ -13292,7 +13306,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="333" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B42" s="333"/>
       <c r="C42" s="333"/>
@@ -13308,7 +13322,7 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" s="333" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B43" s="333"/>
       <c r="C43" s="333"/>
@@ -13565,7 +13579,7 @@
   <sheetData>
     <row r="2" spans="1:21" ht="21.75" customHeight="1">
       <c r="A2" s="253" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B2" s="253"/>
       <c r="C2" s="253"/>
@@ -13575,14 +13589,14 @@
       <c r="G2" s="253"/>
       <c r="H2" s="240"/>
       <c r="I2" s="240"/>
-      <c r="J2" s="224"/>
+      <c r="J2" s="221"/>
       <c r="K2" s="220"/>
-      <c r="L2" s="222"/>
-      <c r="M2" s="222"/>
-      <c r="N2" s="222"/>
-      <c r="O2" s="222"/>
-      <c r="P2" s="222"/>
-      <c r="Q2" s="222"/>
+      <c r="L2" s="223"/>
+      <c r="M2" s="223"/>
+      <c r="N2" s="223"/>
+      <c r="O2" s="223"/>
+      <c r="P2" s="223"/>
+      <c r="Q2" s="223"/>
       <c r="R2" s="156"/>
       <c r="S2" s="156"/>
       <c r="T2" s="156"/>
@@ -13614,7 +13628,7 @@
     <row r="5" spans="1:21" ht="26.1" customHeight="1">
       <c r="A5" s="156"/>
       <c r="B5" s="357" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C5" s="336"/>
       <c r="D5" s="336"/>
@@ -13624,7 +13638,7 @@
       <c r="H5" s="249"/>
       <c r="I5" s="156"/>
       <c r="J5" s="365" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="K5" s="365"/>
       <c r="L5" s="365"/>
@@ -13641,14 +13655,14 @@
     <row r="6" spans="1:21" ht="18" customHeight="1">
       <c r="A6" s="156"/>
       <c r="B6" s="350" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C6" s="336"/>
       <c r="D6" s="336" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E6" s="336" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F6" s="349"/>
       <c r="G6" s="249"/>
@@ -13658,10 +13672,10 @@
       <c r="K6" s="47"/>
       <c r="L6" s="47"/>
       <c r="M6" s="67" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="N6" s="67" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="O6" s="47"/>
       <c r="P6" s="47"/>
@@ -13674,34 +13688,34 @@
     <row r="7" spans="1:21" ht="18" customHeight="1">
       <c r="A7" s="156"/>
       <c r="B7" s="242" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C7" s="240" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D7" s="336"/>
       <c r="E7" s="240" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F7" s="247" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G7" s="249"/>
       <c r="H7" s="249"/>
       <c r="I7" s="156"/>
       <c r="J7" s="358" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="K7" s="358"/>
       <c r="L7" s="358"/>
       <c r="M7" s="244" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N7" s="244" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O7" s="360" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P7" s="360"/>
       <c r="Q7" s="360"/>
@@ -13712,13 +13726,13 @@
     </row>
     <row r="8" spans="1:21" ht="14.1" customHeight="1">
       <c r="A8" s="81" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B8" s="242" t="s">
-        <v>497</v>
-      </c>
-      <c r="C8" s="227" t="s">
-        <v>524</v>
+        <v>499</v>
+      </c>
+      <c r="C8" s="226" t="s">
+        <v>526</v>
       </c>
       <c r="D8" s="240">
         <v>2</v>
@@ -13733,18 +13747,18 @@
       <c r="H8" s="50"/>
       <c r="I8" s="156"/>
       <c r="J8" s="358" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="K8" s="358"/>
       <c r="L8" s="358"/>
       <c r="M8" s="68" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="N8" s="71" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="O8" s="245" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P8" s="245"/>
       <c r="Q8" s="245"/>
@@ -13755,13 +13769,13 @@
     </row>
     <row r="9" spans="1:21" ht="14.1" customHeight="1">
       <c r="A9" s="81" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B9" s="242" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C9" s="203" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D9" s="240">
         <v>3</v>
@@ -13776,15 +13790,15 @@
       <c r="H9" s="50"/>
       <c r="I9" s="156"/>
       <c r="J9" s="358" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K9" s="358"/>
       <c r="L9" s="358"/>
       <c r="M9" s="69" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N9" s="244" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O9" s="61"/>
       <c r="P9" s="61"/>
@@ -13796,13 +13810,13 @@
     </row>
     <row r="10" spans="1:21" ht="14.1" customHeight="1">
       <c r="A10" s="81" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B10" s="242" t="s">
-        <v>503</v>
-      </c>
-      <c r="C10" s="227" t="s">
-        <v>530</v>
+        <v>505</v>
+      </c>
+      <c r="C10" s="226" t="s">
+        <v>532</v>
       </c>
       <c r="D10" s="240">
         <v>5</v>
@@ -13817,7 +13831,7 @@
       <c r="H10" s="50"/>
       <c r="I10" s="156"/>
       <c r="J10" s="358" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="K10" s="358"/>
       <c r="L10" s="358"/>
@@ -13837,13 +13851,13 @@
     </row>
     <row r="11" spans="1:21" ht="14.1" customHeight="1">
       <c r="A11" s="81" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B11" s="242" t="s">
-        <v>532</v>
-      </c>
-      <c r="C11" s="227" t="s">
-        <v>533</v>
+        <v>534</v>
+      </c>
+      <c r="C11" s="226" t="s">
+        <v>535</v>
       </c>
       <c r="D11" s="240">
         <v>9</v>
@@ -13858,15 +13872,15 @@
       <c r="H11" s="50"/>
       <c r="I11" s="156"/>
       <c r="J11" s="358" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="K11" s="358"/>
       <c r="L11" s="358"/>
       <c r="M11" s="69" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="N11" s="244" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O11" s="61"/>
       <c r="P11" s="61"/>
@@ -13878,13 +13892,13 @@
     </row>
     <row r="12" spans="1:21" ht="14.1" customHeight="1">
       <c r="A12" s="81" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B12" s="242" t="s">
-        <v>535</v>
-      </c>
-      <c r="C12" s="227" t="s">
-        <v>536</v>
+        <v>537</v>
+      </c>
+      <c r="C12" s="226" t="s">
+        <v>538</v>
       </c>
       <c r="D12" s="240">
         <v>17</v>
@@ -13899,7 +13913,7 @@
       <c r="H12" s="50"/>
       <c r="I12" s="156"/>
       <c r="J12" s="358" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="K12" s="358"/>
       <c r="L12" s="358"/>
@@ -13919,13 +13933,13 @@
     </row>
     <row r="13" spans="1:21" ht="14.1" customHeight="1">
       <c r="A13" s="81" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B13" s="242" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C13" s="240" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D13" s="240">
         <v>33</v>
@@ -13940,7 +13954,7 @@
       <c r="H13" s="50"/>
       <c r="I13" s="156"/>
       <c r="J13" s="358" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="K13" s="358"/>
       <c r="L13" s="358"/>
@@ -13960,13 +13974,13 @@
     </row>
     <row r="14" spans="1:21" ht="14.1" customHeight="1">
       <c r="A14" s="81" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B14" s="242" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C14" s="240" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D14" s="240">
         <v>65</v>
@@ -13980,14 +13994,14 @@
       <c r="G14" s="43"/>
       <c r="H14" s="50"/>
       <c r="I14" s="156"/>
-      <c r="J14" s="222"/>
-      <c r="K14" s="222"/>
-      <c r="L14" s="222"/>
-      <c r="M14" s="222"/>
-      <c r="N14" s="222"/>
-      <c r="O14" s="222"/>
-      <c r="P14" s="222"/>
-      <c r="Q14" s="222"/>
+      <c r="J14" s="223"/>
+      <c r="K14" s="223"/>
+      <c r="L14" s="223"/>
+      <c r="M14" s="223"/>
+      <c r="N14" s="223"/>
+      <c r="O14" s="223"/>
+      <c r="P14" s="223"/>
+      <c r="Q14" s="223"/>
       <c r="R14" s="156"/>
       <c r="S14" s="156"/>
       <c r="T14" s="156"/>
@@ -13995,13 +14009,13 @@
     </row>
     <row r="15" spans="1:21" ht="14.1" customHeight="1">
       <c r="A15" s="81" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B15" s="242" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C15" s="240" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D15" s="240">
         <v>129</v>
@@ -14030,13 +14044,13 @@
     </row>
     <row r="16" spans="1:21" ht="14.1" customHeight="1">
       <c r="A16" s="81" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B16" s="242" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C16" s="240" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D16" s="240">
         <v>257</v>
@@ -14065,13 +14079,13 @@
     </row>
     <row r="17" spans="1:17" ht="14.1" customHeight="1">
       <c r="A17" s="81" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="D17" s="32">
         <v>513</v>
@@ -14099,7 +14113,7 @@
       <c r="B18" s="156"/>
       <c r="C18" s="156"/>
       <c r="D18" s="242" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E18" s="156"/>
       <c r="F18" s="156"/>
@@ -14120,7 +14134,7 @@
       <c r="B19" s="156"/>
       <c r="C19" s="156"/>
       <c r="D19" s="240" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E19" s="156"/>
       <c r="F19" s="156"/>
@@ -14139,7 +14153,7 @@
     <row r="20" spans="1:17">
       <c r="A20" s="156"/>
       <c r="B20" s="357" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C20" s="336"/>
       <c r="D20" s="336"/>
@@ -14148,26 +14162,26 @@
       <c r="G20" s="156"/>
       <c r="H20" s="156"/>
       <c r="I20" s="156"/>
-      <c r="J20" s="222"/>
-      <c r="K20" s="222"/>
-      <c r="L20" s="222"/>
-      <c r="M20" s="222"/>
-      <c r="N20" s="222"/>
-      <c r="O20" s="222"/>
-      <c r="P20" s="222"/>
-      <c r="Q20" s="222"/>
+      <c r="J20" s="223"/>
+      <c r="K20" s="223"/>
+      <c r="L20" s="223"/>
+      <c r="M20" s="223"/>
+      <c r="N20" s="223"/>
+      <c r="O20" s="223"/>
+      <c r="P20" s="223"/>
+      <c r="Q20" s="223"/>
     </row>
     <row r="21" spans="1:17" ht="26.1" customHeight="1">
       <c r="A21" s="156"/>
       <c r="B21" s="350" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C21" s="336"/>
       <c r="D21" s="336" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E21" s="336" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F21" s="349"/>
       <c r="G21" s="240"/>
@@ -14185,23 +14199,23 @@
     <row r="22" spans="1:17" ht="18" customHeight="1">
       <c r="A22" s="156"/>
       <c r="B22" s="242" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="C22" s="240" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="D22" s="336"/>
       <c r="E22" s="240" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F22" s="247" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G22" s="350"/>
       <c r="H22" s="336"/>
       <c r="I22" s="156"/>
       <c r="J22" s="359" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="K22" s="352"/>
       <c r="L22" s="352"/>
@@ -14214,10 +14228,10 @@
     <row r="23" spans="1:17" ht="18" customHeight="1">
       <c r="A23" s="156"/>
       <c r="B23" s="242" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C23" s="240" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D23" s="240">
         <v>1</v>
@@ -14232,13 +14246,13 @@
       <c r="H23" s="240"/>
       <c r="I23" s="156"/>
       <c r="J23" s="352" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K23" s="356"/>
       <c r="L23" s="356"/>
       <c r="M23" s="155"/>
       <c r="N23" s="352" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O23" s="352"/>
       <c r="P23" s="352"/>
@@ -14247,10 +14261,10 @@
     <row r="24" spans="1:17" ht="14.1" customHeight="1">
       <c r="A24" s="156"/>
       <c r="B24" s="242" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C24" s="240" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D24" s="240">
         <v>2</v>
@@ -14267,13 +14281,13 @@
       <c r="H24" s="240"/>
       <c r="I24" s="156"/>
       <c r="J24" s="352" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="K24" s="356"/>
       <c r="L24" s="356"/>
       <c r="M24" s="155"/>
       <c r="N24" s="352" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="O24" s="352"/>
       <c r="P24" s="352"/>
@@ -14282,10 +14296,10 @@
     <row r="25" spans="1:17" ht="14.1" customHeight="1">
       <c r="A25" s="156"/>
       <c r="B25" s="242" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C25" s="240" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D25" s="240">
         <v>4</v>
@@ -14301,13 +14315,13 @@
       <c r="H25" s="240"/>
       <c r="I25" s="156"/>
       <c r="J25" s="352" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="K25" s="356"/>
       <c r="L25" s="356"/>
       <c r="M25" s="155"/>
       <c r="N25" s="352" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="O25" s="352"/>
       <c r="P25" s="352"/>
@@ -14316,10 +14330,10 @@
     <row r="26" spans="1:17" ht="14.1" customHeight="1">
       <c r="A26" s="156"/>
       <c r="B26" s="242" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C26" s="240" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D26" s="240">
         <v>8</v>
@@ -14335,13 +14349,13 @@
       <c r="H26" s="240"/>
       <c r="I26" s="156"/>
       <c r="J26" s="352" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="K26" s="352"/>
       <c r="L26" s="352"/>
       <c r="M26" s="155"/>
       <c r="N26" s="352" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O26" s="352"/>
       <c r="P26" s="352"/>
@@ -14350,10 +14364,10 @@
     <row r="27" spans="1:17" ht="14.1" customHeight="1">
       <c r="A27" s="156"/>
       <c r="B27" s="242" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C27" s="240" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D27" s="240">
         <v>16</v>
@@ -14380,10 +14394,10 @@
     <row r="28" spans="1:17" ht="14.1" customHeight="1">
       <c r="A28" s="156"/>
       <c r="B28" s="242" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C28" s="240" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D28" s="240">
         <v>32</v>
@@ -14410,10 +14424,10 @@
     <row r="29" spans="1:17" ht="14.1" customHeight="1">
       <c r="A29" s="156"/>
       <c r="B29" s="242" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C29" s="240" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D29" s="240">
         <v>64</v>
@@ -14440,10 +14454,10 @@
     <row r="30" spans="1:17" ht="14.1" customHeight="1">
       <c r="A30" s="156"/>
       <c r="B30" s="242" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C30" s="240" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D30" s="240">
         <v>128</v>
@@ -14470,10 +14484,10 @@
     <row r="31" spans="1:17" ht="14.1" customHeight="1">
       <c r="A31" s="156"/>
       <c r="B31" s="31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D31" s="32">
         <v>256</v>
@@ -14537,7 +14551,7 @@
     </row>
     <row r="34" spans="2:19">
       <c r="B34" s="344" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C34" s="345"/>
       <c r="D34" s="345"/>
@@ -14559,21 +14573,21 @@
     </row>
     <row r="35" spans="2:19" ht="26.1" customHeight="1">
       <c r="B35" s="350" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C35" s="336"/>
       <c r="D35" s="336" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E35" s="336" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F35" s="349"/>
-      <c r="G35" s="222"/>
-      <c r="H35" s="222"/>
+      <c r="G35" s="223"/>
+      <c r="H35" s="223"/>
       <c r="I35" s="156"/>
       <c r="J35" s="355" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="K35" s="355"/>
       <c r="L35" s="355"/>
@@ -14587,15 +14601,15 @@
     </row>
     <row r="36" spans="2:19" ht="18" customHeight="1">
       <c r="B36" s="242" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C36" s="240"/>
       <c r="D36" s="336"/>
       <c r="E36" s="240" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F36" s="247" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G36" s="350"/>
       <c r="H36" s="336"/>
@@ -14603,7 +14617,7 @@
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
       <c r="L36" s="341" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M36" s="341"/>
       <c r="N36" s="341"/>
@@ -14615,7 +14629,7 @@
     </row>
     <row r="37" spans="2:19" ht="18" customHeight="1">
       <c r="B37" s="242" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C37" s="240"/>
       <c r="D37" s="240">
@@ -14641,7 +14655,7 @@
     </row>
     <row r="38" spans="2:19" ht="14.1" customHeight="1">
       <c r="B38" s="242" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C38" s="240"/>
       <c r="D38" s="240">
@@ -14656,14 +14670,14 @@
       <c r="H38" s="156"/>
       <c r="I38" s="156"/>
       <c r="J38" s="342" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="K38" s="342"/>
       <c r="L38" s="51" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M38" s="354" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N38" s="342"/>
       <c r="O38" s="342"/>
@@ -14674,7 +14688,7 @@
     </row>
     <row r="39" spans="2:19" ht="14.1" customHeight="1">
       <c r="B39" s="242" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C39" s="240"/>
       <c r="D39" s="240">
@@ -14688,7 +14702,7 @@
       <c r="H39" s="156"/>
       <c r="I39" s="156"/>
       <c r="J39" s="351" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="K39" s="351"/>
       <c r="L39" s="361"/>
@@ -14697,14 +14711,14 @@
       <c r="O39" s="42"/>
       <c r="P39" s="42"/>
       <c r="Q39" s="241" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="R39" s="42"/>
       <c r="S39" s="42"/>
     </row>
     <row r="40" spans="2:19" ht="14.1" customHeight="1">
       <c r="B40" s="242" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C40" s="240"/>
       <c r="D40" s="240">
@@ -14718,7 +14732,7 @@
       <c r="H40" s="156"/>
       <c r="I40" s="156"/>
       <c r="J40" s="342" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="K40" s="342"/>
       <c r="L40" s="129" t="str">
@@ -14727,10 +14741,10 @@
       </c>
       <c r="M40" s="42"/>
       <c r="N40" s="204" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O40" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P40" s="58"/>
       <c r="Q40" s="48" t="e">
@@ -14738,13 +14752,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="R40" s="42" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="S40" s="42"/>
     </row>
     <row r="41" spans="2:19" ht="14.1" customHeight="1">
       <c r="B41" s="242" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C41" s="240"/>
       <c r="D41" s="240">
@@ -14765,10 +14779,10 @@
       <c r="L41" s="336"/>
       <c r="M41" s="53"/>
       <c r="N41" s="204" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O41" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P41" s="58"/>
       <c r="Q41" s="48" t="e">
@@ -14776,13 +14790,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="R41" s="42" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="S41" s="42"/>
     </row>
     <row r="42" spans="2:19" ht="14.1" customHeight="1">
       <c r="B42" s="242" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C42" s="240"/>
       <c r="D42" s="240">
@@ -14800,10 +14814,10 @@
       <c r="L42" s="42"/>
       <c r="M42" s="53"/>
       <c r="N42" s="204" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O42" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P42" s="58"/>
       <c r="Q42" s="48" t="e">
@@ -14811,13 +14825,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="R42" s="42" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="S42" s="42"/>
     </row>
     <row r="43" spans="2:19" ht="14.1" customHeight="1">
       <c r="B43" s="242" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C43" s="240"/>
       <c r="D43" s="240">
@@ -14843,7 +14857,7 @@
     </row>
     <row r="44" spans="2:19" ht="14.1" customHeight="1">
       <c r="B44" s="242" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C44" s="240"/>
       <c r="D44" s="240">
@@ -14857,7 +14871,7 @@
       <c r="H44" s="156"/>
       <c r="I44" s="156"/>
       <c r="J44" s="342" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K44" s="342"/>
       <c r="L44" s="129" t="str">
@@ -14866,10 +14880,10 @@
       </c>
       <c r="M44" s="52"/>
       <c r="N44" s="204" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O44" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P44" s="58"/>
       <c r="Q44" s="48" t="e">
@@ -14877,13 +14891,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="R44" s="42" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="S44" s="42"/>
     </row>
     <row r="45" spans="2:19" ht="14.1" customHeight="1">
       <c r="B45" s="31" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C45" s="32"/>
       <c r="D45" s="32">
@@ -14904,10 +14918,10 @@
       <c r="L45" s="269"/>
       <c r="M45" s="53"/>
       <c r="N45" s="204" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O45" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P45" s="58"/>
       <c r="Q45" s="48" t="e">
@@ -14915,7 +14929,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R45" s="42" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="S45" s="42"/>
     </row>
@@ -14933,10 +14947,10 @@
       <c r="L46" s="42"/>
       <c r="M46" s="53"/>
       <c r="N46" s="204" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O46" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P46" s="58"/>
       <c r="Q46" s="48" t="e">
@@ -14944,7 +14958,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="R46" s="42" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="S46" s="42"/>
     </row>
@@ -14970,7 +14984,7 @@
     </row>
     <row r="48" spans="2:19">
       <c r="B48" s="345" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="C48" s="345"/>
       <c r="D48" s="345"/>
@@ -14992,21 +15006,21 @@
     </row>
     <row r="49" spans="2:19" ht="26.1" customHeight="1">
       <c r="B49" s="336" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C49" s="336"/>
       <c r="D49" s="336" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E49" s="336" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F49" s="349"/>
-      <c r="G49" s="222"/>
-      <c r="H49" s="222"/>
+      <c r="G49" s="223"/>
+      <c r="H49" s="223"/>
       <c r="I49" s="156"/>
       <c r="J49" s="355" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="K49" s="355"/>
       <c r="L49" s="355"/>
@@ -15023,10 +15037,10 @@
       <c r="C50" s="156"/>
       <c r="D50" s="336"/>
       <c r="E50" s="240" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F50" s="247" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G50" s="350"/>
       <c r="H50" s="336"/>
@@ -15034,7 +15048,7 @@
       <c r="J50" s="42"/>
       <c r="K50" s="42"/>
       <c r="L50" s="341" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="M50" s="341"/>
       <c r="N50" s="341"/>
@@ -15046,7 +15060,7 @@
     </row>
     <row r="51" spans="2:19" ht="18" customHeight="1">
       <c r="B51" s="240" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C51" s="156"/>
       <c r="D51" s="240">
@@ -15074,7 +15088,7 @@
     </row>
     <row r="52" spans="2:19" ht="14.1" customHeight="1">
       <c r="B52" s="240" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C52" s="156"/>
       <c r="D52" s="240">
@@ -15090,14 +15104,14 @@
       <c r="H52" s="156"/>
       <c r="I52" s="156"/>
       <c r="J52" s="342" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="K52" s="342"/>
       <c r="L52" s="51" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="M52" s="354" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="N52" s="342"/>
       <c r="O52" s="342"/>
@@ -15108,7 +15122,7 @@
     </row>
     <row r="53" spans="2:19" ht="14.1" customHeight="1">
       <c r="B53" s="240" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C53" s="156"/>
       <c r="D53" s="240">
@@ -15124,7 +15138,7 @@
       <c r="H53" s="156"/>
       <c r="I53" s="156"/>
       <c r="J53" s="351" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="K53" s="351"/>
       <c r="L53" s="361"/>
@@ -15133,14 +15147,14 @@
       <c r="O53" s="42"/>
       <c r="P53" s="42"/>
       <c r="Q53" s="241" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="R53" s="42"/>
       <c r="S53" s="42"/>
     </row>
     <row r="54" spans="2:19" ht="14.1" customHeight="1">
       <c r="B54" s="35" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C54" s="155"/>
       <c r="D54" s="35">
@@ -15156,7 +15170,7 @@
       <c r="H54" s="81"/>
       <c r="I54" s="156"/>
       <c r="J54" s="342" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="K54" s="342"/>
       <c r="L54" s="129" t="str">
@@ -15165,10 +15179,10 @@
       </c>
       <c r="M54" s="52"/>
       <c r="N54" s="204" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O54" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P54" s="58"/>
       <c r="Q54" s="48" t="e">
@@ -15176,13 +15190,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="R54" s="42" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="S54" s="42"/>
     </row>
     <row r="55" spans="2:19" ht="14.1" customHeight="1">
       <c r="B55" s="240" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C55" s="156"/>
       <c r="D55" s="240">
@@ -15205,10 +15219,10 @@
       <c r="L55" s="336"/>
       <c r="M55" s="53"/>
       <c r="N55" s="204" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O55" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P55" s="58"/>
       <c r="Q55" s="48" t="e">
@@ -15216,13 +15230,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="R55" s="42" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="S55" s="42"/>
     </row>
     <row r="56" spans="2:19" ht="14.1" customHeight="1">
       <c r="B56" s="35" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C56" s="155"/>
       <c r="D56" s="35">
@@ -15242,10 +15256,10 @@
       <c r="L56" s="42"/>
       <c r="M56" s="53"/>
       <c r="N56" s="204" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O56" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P56" s="58"/>
       <c r="Q56" s="48" t="e">
@@ -15253,13 +15267,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="R56" s="42" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="S56" s="42"/>
     </row>
     <row r="57" spans="2:19" ht="14.1" customHeight="1">
       <c r="B57" s="35" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C57" s="155"/>
       <c r="D57" s="35">
@@ -15287,7 +15301,7 @@
     </row>
     <row r="58" spans="2:19" ht="14.1" customHeight="1">
       <c r="B58" s="35" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C58" s="155"/>
       <c r="D58" s="35">
@@ -15303,7 +15317,7 @@
       <c r="H58" s="156"/>
       <c r="I58" s="156"/>
       <c r="J58" s="342" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="K58" s="342"/>
       <c r="L58" s="129" t="str">
@@ -15312,10 +15326,10 @@
       </c>
       <c r="M58" s="52"/>
       <c r="N58" s="204" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O58" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P58" s="58"/>
       <c r="Q58" s="48" t="e">
@@ -15323,13 +15337,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="R58" s="42" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="S58" s="42"/>
     </row>
     <row r="59" spans="2:19" ht="14.1" customHeight="1">
       <c r="B59" s="240" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C59" s="156"/>
       <c r="D59" s="240">
@@ -15352,10 +15366,10 @@
       <c r="L59" s="269"/>
       <c r="M59" s="53"/>
       <c r="N59" s="204" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O59" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P59" s="58"/>
       <c r="Q59" s="48" t="e">
@@ -15363,13 +15377,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="R59" s="42" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="S59" s="42"/>
     </row>
     <row r="60" spans="2:19" ht="14.1" customHeight="1">
       <c r="B60" s="35" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C60" s="155"/>
       <c r="D60" s="35">
@@ -15389,10 +15403,10 @@
       <c r="L60" s="42"/>
       <c r="M60" s="53"/>
       <c r="N60" s="204" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O60" s="58" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P60" s="58"/>
       <c r="Q60" s="48" t="e">
@@ -15400,16 +15414,16 @@
         <v>#VALUE!</v>
       </c>
       <c r="R60" s="42" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="S60" s="42"/>
     </row>
     <row r="61" spans="2:19" ht="14.1" customHeight="1">
       <c r="B61" s="240" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C61" s="156"/>
-      <c r="D61" s="227">
+      <c r="D61" s="226">
         <v>63</v>
       </c>
       <c r="E61" s="28">
@@ -15434,7 +15448,7 @@
     </row>
     <row r="62" spans="2:19" ht="14.1" customHeight="1">
       <c r="B62" s="35" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C62" s="155"/>
       <c r="D62" s="35">
@@ -15462,7 +15476,7 @@
     </row>
     <row r="63" spans="2:19" ht="14.1" customHeight="1">
       <c r="B63" s="32" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C63" s="38"/>
       <c r="D63" s="32">
@@ -15479,7 +15493,7 @@
       <c r="I63" s="156"/>
       <c r="J63" s="49"/>
       <c r="K63" s="256" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L63" s="343"/>
       <c r="M63" s="343"/>
@@ -15512,7 +15526,7 @@
     </row>
     <row r="65" spans="2:35" ht="14.1" customHeight="1">
       <c r="B65" s="347" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C65" s="347"/>
       <c r="D65" s="347"/>
@@ -15523,7 +15537,7 @@
       <c r="I65" s="156"/>
       <c r="J65" s="19"/>
       <c r="K65" s="256" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="L65" s="343"/>
       <c r="M65" s="343"/>
@@ -15552,7 +15566,7 @@
     </row>
     <row r="67" spans="2:35">
       <c r="B67" s="344" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C67" s="345"/>
       <c r="D67" s="345"/>
@@ -15590,21 +15604,21 @@
     </row>
     <row r="68" spans="2:35" ht="26.1" customHeight="1">
       <c r="B68" s="350" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C68" s="336"/>
       <c r="D68" s="336" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E68" s="336" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F68" s="349"/>
-      <c r="G68" s="222"/>
-      <c r="H68" s="222"/>
+      <c r="G68" s="223"/>
+      <c r="H68" s="223"/>
       <c r="I68" s="156"/>
       <c r="J68" s="72" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K68" s="156"/>
       <c r="L68" s="156"/>
@@ -15634,22 +15648,22 @@
     </row>
     <row r="69" spans="2:35" ht="18" customHeight="1">
       <c r="B69" s="242" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C69" s="156"/>
       <c r="D69" s="336"/>
       <c r="E69" s="240" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F69" s="247" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G69" s="55"/>
       <c r="H69" s="54"/>
       <c r="I69" s="54"/>
       <c r="J69" s="75"/>
       <c r="K69" s="75" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="L69" s="77"/>
       <c r="M69" s="76"/>
@@ -15669,7 +15683,7 @@
       <c r="AA69" s="76"/>
       <c r="AB69" s="88"/>
       <c r="AC69" s="362" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AD69" s="363"/>
       <c r="AE69" s="363"/>
@@ -15680,7 +15694,7 @@
     </row>
     <row r="70" spans="2:35" ht="18" customHeight="1">
       <c r="B70" s="242" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C70" s="156"/>
       <c r="D70" s="240">
@@ -15696,79 +15710,79 @@
       <c r="H70" s="46"/>
       <c r="I70" s="54"/>
       <c r="J70" s="75" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="K70" s="87" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L70" s="85" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M70" s="86" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N70" s="86" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O70" s="86" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P70" s="86" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q70" s="85" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="R70" s="86" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="S70" s="85" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="T70" s="86" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="U70" s="86" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="V70" s="86" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="W70" s="86" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="X70" s="86" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Y70" s="86" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Z70" s="86" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AA70" s="86" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AB70" s="89" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AC70" s="109" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AD70" s="109" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AE70" s="110" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AF70" s="110" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG70" s="110" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AH70" s="110" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AI70" s="110" t="s">
         <v>261</v>
@@ -15776,7 +15790,7 @@
     </row>
     <row r="71" spans="2:35" ht="14.1" customHeight="1">
       <c r="B71" s="242" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C71" s="156"/>
       <c r="D71" s="240">
@@ -15792,87 +15806,87 @@
       <c r="H71" s="28"/>
       <c r="I71" s="46"/>
       <c r="J71" s="87" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="K71" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC71" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD71" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AF71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AH71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AI71" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="72" spans="2:35" ht="14.1" customHeight="1">
       <c r="B72" s="242" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C72" s="156"/>
       <c r="D72" s="240">
@@ -15888,87 +15902,87 @@
       <c r="H72" s="28"/>
       <c r="I72" s="156"/>
       <c r="J72" s="87" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K72" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC72" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD72" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AF72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AH72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AI72" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="73" spans="2:35" ht="14.1" customHeight="1">
       <c r="B73" s="39" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C73" s="40"/>
       <c r="D73" s="35">
@@ -15984,87 +15998,87 @@
       <c r="H73" s="28"/>
       <c r="I73" s="156"/>
       <c r="J73" s="83" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="K73" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O73" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Q73" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R73" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S73" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="U73" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="W73" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Y73" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AB73" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI73" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="74" spans="2:35" ht="14.1" customHeight="1">
       <c r="B74" s="242" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C74" s="156"/>
       <c r="D74" s="240">
@@ -16080,87 +16094,87 @@
       <c r="H74" s="29"/>
       <c r="I74" s="156"/>
       <c r="J74" s="84" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="K74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L74" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB74" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC74" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD74" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE74" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF74" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG74" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH74" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI74" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="75" spans="2:35" ht="14.1" customHeight="1">
       <c r="B75" s="39" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C75" s="40"/>
       <c r="D75" s="35">
@@ -16176,87 +16190,87 @@
       <c r="H75" s="28"/>
       <c r="I75" s="156"/>
       <c r="J75" s="84" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L75" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB75" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC75" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD75" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE75" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF75" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG75" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH75" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI75" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="76" spans="2:35" ht="14.1" customHeight="1">
       <c r="B76" s="242" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C76" s="156"/>
       <c r="D76" s="240">
@@ -16272,87 +16286,87 @@
       <c r="H76" s="29"/>
       <c r="I76" s="156"/>
       <c r="J76" s="84" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="K76" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O76" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Q76" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R76" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S76" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="U76" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="W76" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Y76" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AB76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AC76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI76" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="77" spans="2:35" ht="14.1" customHeight="1">
       <c r="B77" s="39" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C77" s="40"/>
       <c r="D77" s="35">
@@ -16368,87 +16382,87 @@
       <c r="H77" s="28"/>
       <c r="I77" s="156"/>
       <c r="J77" s="84" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K77" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O77" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Q77" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R77" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S77" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="U77" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="W77" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Y77" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AB77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AC77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI77" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="78" spans="2:35" ht="14.1" customHeight="1">
       <c r="B78" s="242" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C78" s="156"/>
       <c r="D78" s="240">
@@ -16464,87 +16478,87 @@
       <c r="H78" s="29"/>
       <c r="I78" s="156"/>
       <c r="J78" s="84" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="K78" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O78" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Q78" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R78" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S78" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="U78" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="W78" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Y78" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AB78" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI78" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="79" spans="2:35" ht="14.1" customHeight="1">
       <c r="B79" s="39" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C79" s="40"/>
       <c r="D79" s="35">
@@ -16560,87 +16574,87 @@
       <c r="H79" s="28"/>
       <c r="I79" s="156"/>
       <c r="J79" s="84" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K79" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O79" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Q79" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R79" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S79" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="U79" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="W79" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Y79" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AB79" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI79" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="80" spans="2:35" ht="14.1" customHeight="1">
       <c r="B80" s="242" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C80" s="156"/>
       <c r="D80" s="240">
@@ -16656,87 +16670,87 @@
       <c r="H80" s="29"/>
       <c r="I80" s="156"/>
       <c r="J80" s="84" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="K80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L80" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB80" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC80" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD80" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE80" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF80" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG80" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH80" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI80" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="81" spans="2:35" ht="14.1" customHeight="1">
       <c r="B81" s="39" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C81" s="40"/>
       <c r="D81" s="35">
@@ -16752,87 +16766,87 @@
       <c r="H81" s="28"/>
       <c r="I81" s="156"/>
       <c r="J81" s="84" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="K81" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L81" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M81" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N81" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O81" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P81" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Q81" s="73" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R81" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="S81" s="73" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T81" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="U81" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="V81" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="W81" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="X81" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Y81" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Z81" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA81" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB81" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC81" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD81" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE81" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF81" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG81" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH81" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI81" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="82" spans="2:35" ht="14.1" customHeight="1">
       <c r="B82" s="31" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C82" s="38"/>
       <c r="D82" s="32">
@@ -16848,82 +16862,82 @@
       <c r="H82" s="29"/>
       <c r="I82" s="156"/>
       <c r="J82" s="84" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K82" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L82" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M82" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N82" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O82" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P82" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Q82" s="73" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R82" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="S82" s="73" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T82" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="U82" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="V82" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="W82" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="X82" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Y82" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Z82" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA82" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB82" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC82" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD82" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE82" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF82" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG82" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH82" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI82" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="83" spans="2:35" ht="14.1" customHeight="1">
@@ -16936,87 +16950,87 @@
       <c r="H83" s="28"/>
       <c r="I83" s="156"/>
       <c r="J83" s="121" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K83" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC83" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD83" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE83" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF83" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG83" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH83" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI83" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="84" spans="2:35" ht="14.1" customHeight="1">
       <c r="B84" s="347" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C84" s="347"/>
       <c r="D84" s="347"/>
@@ -17026,82 +17040,82 @@
       <c r="H84" s="246"/>
       <c r="I84" s="156"/>
       <c r="J84" s="84" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="K84" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L84" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M84" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Q84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="R84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="S84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="T84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="U84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="V84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="W84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="X84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Y84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Z84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AB84" s="73" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AC84" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD84" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE84" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF84" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG84" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH84" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI84" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="85" spans="2:35">
@@ -17114,87 +17128,87 @@
       <c r="H85" s="156"/>
       <c r="I85" s="156"/>
       <c r="J85" s="84" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L85" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB85" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC85" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD85" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE85" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF85" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG85" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH85" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI85" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="86" spans="2:35">
       <c r="B86" s="338" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C86" s="339"/>
       <c r="D86" s="339"/>
@@ -17204,176 +17218,176 @@
       <c r="H86" s="156"/>
       <c r="I86" s="156"/>
       <c r="J86" s="84" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="K86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L86" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB86" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC86" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD86" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE86" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF86" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG86" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH86" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI86" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="87" spans="2:35" ht="26.1" customHeight="1">
       <c r="B87" s="350" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C87" s="336"/>
       <c r="D87" s="336" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E87" s="336" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="F87" s="349"/>
       <c r="G87" s="240"/>
       <c r="H87" s="240"/>
       <c r="I87" s="156"/>
       <c r="J87" s="84" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="K87" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC87" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD87" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AF87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AH87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AI87" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="88" spans="2:35" ht="18" customHeight="1">
@@ -17381,96 +17395,96 @@
       <c r="C88" s="156"/>
       <c r="D88" s="336"/>
       <c r="E88" s="240" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="F88" s="247" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G88" s="240"/>
       <c r="H88" s="240"/>
       <c r="I88" s="156"/>
       <c r="J88" s="84" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="K88" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC88" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD88" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AF88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AH88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AI88" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="89" spans="2:35" ht="18" customHeight="1">
       <c r="B89" s="242" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C89" s="240"/>
       <c r="D89" s="240">
@@ -17484,87 +17498,87 @@
       <c r="H89" s="240"/>
       <c r="I89" s="156"/>
       <c r="J89" s="84" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K89" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC89" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD89" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AF89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AH89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AI89" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="90" spans="2:35" ht="14.1" customHeight="1">
       <c r="B90" s="242" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C90" s="240"/>
       <c r="D90" s="240">
@@ -17578,87 +17592,87 @@
       <c r="H90" s="156"/>
       <c r="I90" s="156"/>
       <c r="J90" s="84" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="K90" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC90" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD90" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AF90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AH90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AI90" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="91" spans="2:35" ht="14.1" customHeight="1">
       <c r="B91" s="242" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C91" s="240"/>
       <c r="D91" s="240">
@@ -17672,87 +17686,87 @@
       <c r="H91" s="156"/>
       <c r="I91" s="156"/>
       <c r="J91" s="84" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="K91" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC91" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD91" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AF91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AH91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AI91" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="92" spans="2:35" ht="14.1" customHeight="1">
       <c r="B92" s="242" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C92" s="240"/>
       <c r="D92" s="240">
@@ -17766,87 +17780,87 @@
       <c r="H92" s="156"/>
       <c r="I92" s="156"/>
       <c r="J92" s="84" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L92" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB92" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC92" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD92" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE92" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF92" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG92" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH92" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI92" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="93" spans="2:35" ht="14.1" customHeight="1">
       <c r="B93" s="242" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C93" s="240"/>
       <c r="D93" s="240">
@@ -17860,87 +17874,87 @@
       <c r="H93" s="156"/>
       <c r="I93" s="156"/>
       <c r="J93" s="84" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="K93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M93" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="N93" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="O93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P93" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="Q93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB93" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC93" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD93" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE93" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF93" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG93" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH93" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI93" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="94" spans="2:35" ht="14.1" customHeight="1">
       <c r="B94" s="242" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C94" s="240"/>
       <c r="D94" s="240">
@@ -17954,87 +17968,87 @@
       <c r="H94" s="156"/>
       <c r="I94" s="156"/>
       <c r="J94" s="143" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="K94" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC94" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD94" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE94" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF94" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG94" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AH94" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI94" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="95" spans="2:35" ht="14.1" customHeight="1">
       <c r="B95" s="242" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C95" s="240"/>
       <c r="D95" s="240">
@@ -18048,87 +18062,87 @@
       <c r="H95" s="156"/>
       <c r="I95" s="156"/>
       <c r="J95" s="87" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K95" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC95" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD95" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE95" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AF95" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AG95" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AH95" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AI95" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="96" spans="2:35" ht="14.1" customHeight="1">
       <c r="B96" s="242" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C96" s="240"/>
       <c r="D96" s="240">
@@ -18142,87 +18156,87 @@
       <c r="H96" s="156"/>
       <c r="I96" s="156"/>
       <c r="J96" s="87" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K96" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="M96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="O96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="P96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Q96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="R96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="S96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="U96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="V96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="W96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="X96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Y96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="Z96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AA96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AB96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AC96" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AD96" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AE96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AF96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG96" s="250" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AH96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AI96" s="250" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="97" spans="2:6" ht="14.1" customHeight="1">
       <c r="B97" s="242" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C97" s="240"/>
       <c r="D97" s="240">
@@ -18235,7 +18249,7 @@
     </row>
     <row r="98" spans="2:6" ht="14.1" customHeight="1">
       <c r="B98" s="242" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C98" s="240"/>
       <c r="D98" s="240">
@@ -18248,7 +18262,7 @@
     </row>
     <row r="99" spans="2:6" ht="14.1" customHeight="1">
       <c r="B99" s="242" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C99" s="240"/>
       <c r="D99" s="240">
@@ -18261,7 +18275,7 @@
     </row>
     <row r="100" spans="2:6" ht="14.1" customHeight="1">
       <c r="B100" s="242" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C100" s="240"/>
       <c r="D100" s="240">
@@ -18274,7 +18288,7 @@
     </row>
     <row r="101" spans="2:6" ht="14.1" customHeight="1">
       <c r="B101" s="242" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C101" s="240"/>
       <c r="D101" s="240">
@@ -18287,7 +18301,7 @@
     </row>
     <row r="102" spans="2:6" ht="14.1" customHeight="1">
       <c r="B102" s="242" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C102" s="240"/>
       <c r="D102" s="240">
@@ -18300,7 +18314,7 @@
     </row>
     <row r="103" spans="2:6" ht="14.1" customHeight="1">
       <c r="B103" s="31" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C103" s="32"/>
       <c r="D103" s="32">
@@ -18320,7 +18334,7 @@
     </row>
     <row r="105" spans="2:6" ht="14.1" customHeight="1">
       <c r="B105" s="338" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C105" s="339"/>
       <c r="D105" s="339"/>
@@ -18329,7 +18343,7 @@
     </row>
     <row r="106" spans="2:6" ht="14.1" customHeight="1">
       <c r="B106" s="74" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C106" s="60"/>
       <c r="D106" s="60"/>
@@ -18342,7 +18356,7 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="338" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C107" s="339"/>
       <c r="D107" s="339"/>
@@ -18351,7 +18365,7 @@
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="74" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C108" s="60"/>
       <c r="D108" s="60"/>
@@ -18475,7 +18489,7 @@
   <sheetData>
     <row r="5" spans="1:19">
       <c r="A5" s="81" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B5" s="156"/>
       <c r="C5" s="156"/>
@@ -18498,7 +18512,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="156" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B6" s="156"/>
       <c r="C6" s="156"/>
@@ -18523,17 +18537,17 @@
       <c r="A7" s="156"/>
       <c r="B7" s="156"/>
       <c r="C7" s="367" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D7" s="367"/>
       <c r="E7" s="367" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F7" s="367"/>
       <c r="G7" s="156"/>
       <c r="H7" s="156"/>
       <c r="I7" s="81" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="J7" s="156"/>
       <c r="K7" s="156"/>
@@ -18548,7 +18562,7 @@
     </row>
     <row r="8" spans="1:19" ht="25.5">
       <c r="A8" s="123" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B8" s="94" t="str">
         <f>_CamType</f>
@@ -18593,7 +18607,7 @@
     <row r="10" spans="1:19">
       <c r="A10" s="156"/>
       <c r="B10" s="81" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C10" s="97" t="e">
         <f>INDEX('Corrections Tables'!E8:E17,MATCH(_Exposure,'Corrections Tables'!A8:A17,0),0)</f>
@@ -18628,7 +18642,7 @@
     <row r="11" spans="1:19">
       <c r="A11" s="156"/>
       <c r="B11" s="219" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C11" s="97" t="e">
         <f>INDEX('Corrections Tables'!E8:E17,MATCH(_Exposure,'Corrections Tables'!A8:A17,0),0)</f>
@@ -18663,7 +18677,7 @@
     <row r="12" spans="1:19">
       <c r="A12" s="156"/>
       <c r="B12" s="219" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C12" s="97" t="e">
         <f>INDEX('Corrections Tables'!E23:E31,MATCH(_Exposure,'Corrections Tables'!B23:B31,0),0)</f>
@@ -18698,7 +18712,7 @@
     <row r="13" spans="1:19">
       <c r="A13" s="156"/>
       <c r="B13" s="219" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C13" s="97" t="e">
         <f>INDEX('Corrections Tables'!E23:E31,MATCH(_Exposure,'Corrections Tables'!B23:B31,0),0)</f>
@@ -18733,7 +18747,7 @@
     <row r="14" spans="1:19">
       <c r="A14" s="156"/>
       <c r="B14" s="219" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C14" s="97" t="e">
         <f>INDEX('Corrections Tables'!E37:E45,MATCH(_Exposure,'Corrections Tables'!B37:B45,0),0)</f>
@@ -18768,7 +18782,7 @@
     <row r="15" spans="1:19">
       <c r="A15" s="156"/>
       <c r="B15" s="218" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C15" s="97" t="e">
         <f>INDEX('Corrections Tables'!E51:E63,MATCH(_Exposure,'Corrections Tables'!B51:B63,0),0)</f>
@@ -18803,7 +18817,7 @@
     <row r="16" spans="1:19">
       <c r="A16" s="156"/>
       <c r="B16" s="81" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C16" s="97" t="e">
         <f>INDEX('Corrections Tables'!E70:E82,MATCH(_Exposure,'Corrections Tables'!B70:B82,0),0)</f>
@@ -18837,7 +18851,7 @@
     </row>
     <row r="17" spans="2:19">
       <c r="B17" s="81" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C17" s="97"/>
       <c r="D17" s="97" t="e">
@@ -18865,7 +18879,7 @@
     </row>
     <row r="18" spans="2:19">
       <c r="B18" s="98" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C18" s="97" t="e">
         <f>INDEX('Corrections Tables'!E108,MATCH(_Exposure,'Corrections Tables'!B108,0),0)</f>
@@ -18899,7 +18913,7 @@
     </row>
     <row r="19" spans="2:19">
       <c r="B19" s="219" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C19" s="97" t="e">
         <f>INDEX('Corrections Tables'!E108,MATCH(_Exposure,'Corrections Tables'!B108,0),0)</f>
@@ -18933,7 +18947,7 @@
     </row>
     <row r="20" spans="2:19">
       <c r="B20" s="219" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C20" s="97" t="e">
         <f>INDEX('Corrections Tables'!E108,MATCH(_Exposure,'Corrections Tables'!B108,0),0)</f>
@@ -18967,7 +18981,7 @@
     </row>
     <row r="21" spans="2:19">
       <c r="B21" s="98" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C21" s="97" t="e">
         <f>INDEX('Corrections Tables'!E108,MATCH(_Exposure,'Corrections Tables'!B108,0),0)</f>
@@ -19001,7 +19015,7 @@
     </row>
     <row r="22" spans="2:19">
       <c r="B22" s="98" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C22" s="97" t="e">
         <f>INDEX('Corrections Tables'!E108,MATCH(_Exposure,'Corrections Tables'!B108,0),0)</f>
@@ -19035,7 +19049,7 @@
     </row>
     <row r="23" spans="2:19">
       <c r="B23" s="218" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C23" s="97" t="e">
         <f>INDEX('Corrections Tables'!Q54:Q56,MATCH(_Exposure,'Corrections Tables'!R40:R42,0),0)</f>
@@ -19069,7 +19083,7 @@
     </row>
     <row r="24" spans="2:19">
       <c r="B24" s="218" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C24" s="97" t="e">
         <f>INDEX('Corrections Tables'!E106,MATCH(_Exposure,'Corrections Tables'!B106,0),0)</f>
@@ -19088,7 +19102,7 @@
         <v>#N/A</v>
       </c>
       <c r="G24" s="156" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="H24" s="156"/>
       <c r="I24" s="81"/>
@@ -19105,7 +19119,7 @@
     </row>
     <row r="25" spans="2:19">
       <c r="B25" s="218" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C25" s="97">
         <v>0</v>
@@ -19137,7 +19151,7 @@
     </row>
     <row r="26" spans="2:19">
       <c r="B26" s="218" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C26" s="97">
         <v>0</v>
@@ -19169,7 +19183,7 @@
     </row>
     <row r="27" spans="2:19">
       <c r="B27" s="218" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C27" s="97">
         <v>0</v>
@@ -19201,7 +19215,7 @@
     </row>
     <row r="28" spans="2:19">
       <c r="B28" s="218" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C28" s="97">
         <v>0</v>
@@ -19233,7 +19247,7 @@
     </row>
     <row r="29" spans="2:19">
       <c r="B29" s="84" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C29" s="97">
         <v>0</v>
@@ -19265,7 +19279,7 @@
     </row>
     <row r="30" spans="2:19">
       <c r="B30" s="218" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C30" s="97">
         <v>0</v>
@@ -19297,7 +19311,7 @@
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="218" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C31" s="97">
         <v>0</v>
@@ -19329,7 +19343,7 @@
     </row>
     <row r="32" spans="2:19">
       <c r="B32" s="218" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C32" s="97">
         <v>0</v>
@@ -19361,7 +19375,7 @@
     </row>
     <row r="33" spans="2:23">
       <c r="B33" s="218" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C33" s="97">
         <v>0</v>
@@ -19397,7 +19411,7 @@
     </row>
     <row r="34" spans="2:23">
       <c r="B34" s="218" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C34" s="97">
         <v>0</v>
@@ -19433,7 +19447,7 @@
     </row>
     <row r="35" spans="2:23">
       <c r="B35" s="218" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C35" s="97">
         <v>0</v>
@@ -19474,7 +19488,7 @@
       <c r="E38" s="156"/>
       <c r="F38" s="156"/>
       <c r="G38" s="81" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="H38" s="156"/>
       <c r="I38" s="156"/>
@@ -19486,7 +19500,7 @@
       <c r="O38" s="156"/>
       <c r="P38" s="156"/>
       <c r="Q38" s="156" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="R38" s="156"/>
       <c r="S38" s="156"/>
@@ -19512,7 +19526,7 @@
       <c r="O39" s="156"/>
       <c r="P39" s="156"/>
       <c r="Q39" s="156" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="R39" s="156"/>
       <c r="S39" s="156"/>
@@ -19531,7 +19545,7 @@
       <c r="H40" s="156"/>
       <c r="I40" s="156"/>
       <c r="J40" s="123" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="K40" s="205" t="e">
         <f>K41</f>
@@ -19543,7 +19557,7 @@
       <c r="O40" s="156"/>
       <c r="P40" s="156"/>
       <c r="Q40" s="372" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="R40" s="373"/>
       <c r="S40" s="374"/>
@@ -19562,7 +19576,7 @@
       <c r="H41" s="156"/>
       <c r="I41" s="156"/>
       <c r="J41" s="122" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="K41" s="100" t="e">
         <f>IF(K42+(L46/24/60/60)&lt;0,K42+(L46/24/60/60)+1,K42+(L46/24/60/60))</f>
@@ -19575,11 +19589,11 @@
       <c r="P41" s="156"/>
       <c r="Q41" s="108"/>
       <c r="R41" s="370" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="S41" s="371"/>
       <c r="T41" s="375"/>
-      <c r="U41" s="312"/>
+      <c r="U41" s="306"/>
       <c r="V41" s="366"/>
       <c r="W41" s="366"/>
     </row>
@@ -19593,7 +19607,7 @@
       <c r="H42" s="156"/>
       <c r="I42" s="156"/>
       <c r="J42" s="122" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="K42" s="100" t="e">
         <f>SUM(K43:K45)</f>
@@ -19606,13 +19620,13 @@
       <c r="P42" s="156"/>
       <c r="Q42" s="108"/>
       <c r="R42" s="368" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="S42" s="369"/>
       <c r="T42" s="380"/>
-      <c r="U42" s="302"/>
-      <c r="V42" s="302"/>
-      <c r="W42" s="302"/>
+      <c r="U42" s="320"/>
+      <c r="V42" s="320"/>
+      <c r="W42" s="320"/>
     </row>
     <row r="43" spans="2:23">
       <c r="B43" s="156"/>
@@ -19624,7 +19638,7 @@
       <c r="H43" s="156"/>
       <c r="I43" s="156"/>
       <c r="J43" s="126" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="K43" s="100" t="e">
         <f>I46/24/60/60</f>
@@ -19635,19 +19649,19 @@
         <v>#VALUE!</v>
       </c>
       <c r="M43" s="122" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N43" s="156"/>
       <c r="O43" s="156"/>
       <c r="P43" s="156"/>
       <c r="Q43" s="109" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="R43" s="109" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="S43" s="75" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="T43" s="117"/>
       <c r="U43" s="81"/>
@@ -19664,7 +19678,7 @@
       <c r="H44" s="156"/>
       <c r="I44" s="156"/>
       <c r="J44" s="126" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="K44" s="100" t="e">
         <f>H46/24/60</f>
@@ -19675,13 +19689,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="M44" s="122" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N44" s="156"/>
       <c r="O44" s="156"/>
       <c r="P44" s="156"/>
       <c r="Q44" s="109" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="R44" s="111">
         <v>0</v>
@@ -19704,7 +19718,7 @@
       <c r="H45" s="156"/>
       <c r="I45" s="156"/>
       <c r="J45" s="122" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K45" s="100" t="e">
         <f>G46/24</f>
@@ -19715,13 +19729,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="M45" s="122" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N45" s="156"/>
       <c r="O45" s="156"/>
       <c r="P45" s="156"/>
       <c r="Q45" s="109" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="R45" s="111">
         <v>0</v>
@@ -19765,13 +19779,13 @@
         <v>#N/A</v>
       </c>
       <c r="M46" s="381" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="N46" s="382"/>
       <c r="O46" s="382"/>
       <c r="P46" s="156"/>
       <c r="Q46" s="110" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="R46" s="111">
         <v>0</v>
@@ -19790,32 +19804,32 @@
       <c r="D47" s="156"/>
       <c r="E47" s="156"/>
       <c r="F47" s="206" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="G47" s="207" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="H47" s="207" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="I47" s="207" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="J47" s="208" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="K47" s="209" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="L47" s="208" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="M47" s="106"/>
       <c r="N47" s="156"/>
       <c r="O47" s="156"/>
       <c r="P47" s="156"/>
       <c r="Q47" s="110" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="R47" s="111">
         <v>0.02</v>
@@ -19860,13 +19874,13 @@
         <v>#N/A</v>
       </c>
       <c r="M48" s="381" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="N48" s="382"/>
       <c r="O48" s="382"/>
       <c r="P48" s="156"/>
       <c r="Q48" s="110" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="R48" s="111">
         <v>0</v>
@@ -19885,7 +19899,7 @@
       <c r="H49" s="156"/>
       <c r="I49" s="156"/>
       <c r="J49" s="125" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="K49" s="107" t="e">
         <f>G48/24</f>
@@ -19896,13 +19910,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="M49" s="125" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="N49" s="156"/>
       <c r="O49" s="156"/>
       <c r="P49" s="156"/>
       <c r="Q49" s="110" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="R49" s="111">
         <f>IF(OR(_CamType="QHY 174 GPS",_CamType="Other - Specify in Comments",_CamType="Visual",_CamType="Photometer",_CamType="CCD Drift Scan",_CamType="Flea 3-03S1 with ADVS",_CamType="Flea 3-03S3 with ADVS",_CamType="Flea 3-28S4M with ADVS",_CamType="Grasshopper Express with ADVS",_CamType="G-Star",0),0,-0.02)</f>
@@ -19934,7 +19948,7 @@
       <c r="H50" s="156"/>
       <c r="I50" s="156"/>
       <c r="J50" s="127" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="K50" s="107" t="e">
         <f>H48/24/60</f>
@@ -19945,7 +19959,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="M50" s="125" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N50" s="156"/>
       <c r="O50" s="156"/>
@@ -19983,7 +19997,7 @@
       <c r="H51" s="156"/>
       <c r="I51" s="156"/>
       <c r="J51" s="127" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="K51" s="107" t="e">
         <f>I48/24/60/60</f>
@@ -19994,7 +20008,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="M51" s="125" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="N51" s="156"/>
       <c r="O51" s="156"/>
@@ -20024,7 +20038,7 @@
       <c r="H52" s="156"/>
       <c r="I52" s="156"/>
       <c r="J52" s="125" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="K52" s="107" t="e">
         <f>SUM(K49:K51)</f>
@@ -20060,7 +20074,7 @@
       <c r="H53" s="156"/>
       <c r="I53" s="156"/>
       <c r="J53" s="125" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="K53" s="107" t="e">
         <f>IF(K52+(L48/24/60/60)&lt;0,K52+(L48/24/60/60)+1,K52+(L48/24/60/60))</f>
@@ -20096,7 +20110,7 @@
       <c r="H54" s="156"/>
       <c r="I54" s="156"/>
       <c r="J54" s="124" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="K54" s="210" t="e">
         <f>K53</f>
@@ -20106,7 +20120,7 @@
       <c r="M54" s="156"/>
       <c r="N54" s="156"/>
       <c r="O54" s="156" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="P54" s="156"/>
       <c r="Q54" s="156"/>
@@ -20139,7 +20153,7 @@
       <c r="M55" s="156"/>
       <c r="N55" s="156"/>
       <c r="O55" s="156" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="P55" s="156"/>
       <c r="Q55" s="156"/>
@@ -20164,7 +20178,7 @@
     <row r="56" spans="6:34">
       <c r="F56" s="156"/>
       <c r="G56" s="156" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="H56" s="156"/>
       <c r="I56" s="156"/>
@@ -20174,7 +20188,7 @@
       <c r="M56" s="156"/>
       <c r="N56" s="156"/>
       <c r="O56" s="156" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="P56" s="156"/>
       <c r="Q56" s="211"/>
@@ -20199,7 +20213,7 @@
     <row r="57" spans="6:34" ht="15.75">
       <c r="F57" s="156"/>
       <c r="G57" s="277" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="H57" s="277"/>
       <c r="I57" s="277"/>
@@ -20264,9 +20278,9 @@
       <c r="V58" s="90"/>
       <c r="W58" s="90"/>
       <c r="X58" s="91"/>
-      <c r="Y58" s="328"/>
-      <c r="Z58" s="328"/>
-      <c r="AA58" s="328"/>
+      <c r="Y58" s="330"/>
+      <c r="Z58" s="330"/>
+      <c r="AA58" s="330"/>
       <c r="AB58" s="81"/>
       <c r="AC58" s="92"/>
       <c r="AD58" s="93"/>
@@ -20281,7 +20295,7 @@
     <row r="59" spans="6:34" ht="15.75">
       <c r="F59" s="156"/>
       <c r="G59" s="277" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="H59" s="277"/>
       <c r="I59" s="277"/>
@@ -20334,7 +20348,7 @@
       <c r="M60" s="156"/>
       <c r="N60" s="156"/>
       <c r="O60" s="156" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="P60" s="156"/>
       <c r="Q60" s="156"/>
@@ -20362,7 +20376,7 @@
       <c r="D66" s="156"/>
       <c r="E66" s="156"/>
       <c r="F66" s="81" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="G66" s="156"/>
       <c r="H66" s="156"/>
@@ -20381,7 +20395,7 @@
       <c r="D67" s="156"/>
       <c r="E67" s="156"/>
       <c r="F67" s="365" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G67" s="365"/>
       <c r="H67" s="365"/>
@@ -20403,10 +20417,10 @@
       <c r="G68" s="47"/>
       <c r="H68" s="47"/>
       <c r="I68" s="67" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="J68" s="67" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="K68" s="47"/>
       <c r="L68" s="47"/>
@@ -20421,18 +20435,18 @@
       <c r="D69" s="156"/>
       <c r="E69" s="156"/>
       <c r="F69" s="376" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="G69" s="377"/>
       <c r="H69" s="378"/>
       <c r="I69" s="244" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J69" s="244" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K69" s="379" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L69" s="360"/>
       <c r="M69" s="360"/>
@@ -20446,18 +20460,18 @@
       <c r="D70" s="156"/>
       <c r="E70" s="156"/>
       <c r="F70" s="376" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="G70" s="377"/>
       <c r="H70" s="378"/>
       <c r="I70" s="68" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="J70" s="71" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="K70" s="245" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="L70" s="245"/>
       <c r="M70" s="245"/>
@@ -20471,15 +20485,15 @@
       <c r="D71" s="156"/>
       <c r="E71" s="156"/>
       <c r="F71" s="376" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="G71" s="377"/>
       <c r="H71" s="378"/>
       <c r="I71" s="69" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J71" s="244" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K71" s="61"/>
       <c r="L71" s="61"/>
@@ -20494,7 +20508,7 @@
       <c r="D72" s="22"/>
       <c r="E72" s="22"/>
       <c r="F72" s="376" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="G72" s="377"/>
       <c r="H72" s="378"/>
@@ -20517,15 +20531,15 @@
       <c r="D73" s="22"/>
       <c r="E73" s="22"/>
       <c r="F73" s="376" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="G73" s="377"/>
       <c r="H73" s="378"/>
       <c r="I73" s="69" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="J73" s="244" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="K73" s="61"/>
       <c r="L73" s="61"/>
@@ -20540,7 +20554,7 @@
       <c r="D74" s="22"/>
       <c r="E74" s="22"/>
       <c r="F74" s="376" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="G74" s="377"/>
       <c r="H74" s="378"/>
@@ -20563,7 +20577,7 @@
       <c r="D75" s="22"/>
       <c r="E75" s="22"/>
       <c r="F75" s="376" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="G75" s="377"/>
       <c r="H75" s="378"/>

--- a/occultation-manager/python/NorthAmerica_AstReportForm_V5.6.12r_Template.xlsx
+++ b/occultation-manager/python/NorthAmerica_AstReportForm_V5.6.12r_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29622"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29704"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steve\Documents\_Steve\Astronomy\IOTA\Reports\mpReports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="13_ncr:1_{9EA8FC22-946C-4214-9D68-CC0F7796F0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2AB946FF-F9DD-4E4D-A0B8-9B937D142827}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{9EA8FC22-946C-4214-9D68-CC0F7796F0C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F72B0B1C-3FBE-4601-B942-1CB5E31A490D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -583,7 +583,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="635">
   <si>
     <t>Important Reminders and Tips for the New Report Form (Revised 12-12-2018)</t>
   </si>
@@ -1601,583 +1601,586 @@
     <t>OTE Used:</t>
   </si>
   <si>
+    <t>{{OTE}}</t>
+  </si>
+  <si>
+    <t>Video</t>
+  </si>
+  <si>
+    <t>Exposure</t>
+  </si>
+  <si>
+    <t>Other Detector related info</t>
+  </si>
+  <si>
+    <t>Detector:</t>
+  </si>
+  <si>
+    <t>Model/Type:</t>
+  </si>
+  <si>
+    <t>{{DETECTOR}}</t>
+  </si>
+  <si>
+    <t>Format:</t>
+  </si>
+  <si>
+    <t>{{VIDEO_FORMAT}}</t>
+  </si>
+  <si>
+    <t>Integration:</t>
+  </si>
+  <si>
+    <t>{{INTEGRATION}}</t>
+  </si>
+  <si>
+    <t>Unit: Fields</t>
+  </si>
+  <si>
+    <t>{{OTHER_DETECTOR_RELATED_INFO}}</t>
+  </si>
+  <si>
+    <t>Conditions:</t>
+  </si>
+  <si>
+    <t>Clouds:</t>
+  </si>
+  <si>
+    <t>Stability:</t>
+  </si>
+  <si>
+    <t>Other conditions:</t>
+  </si>
+  <si>
+    <t>Observations:</t>
+  </si>
+  <si>
+    <t>Times</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remarks </t>
+  </si>
+  <si>
+    <t>Started Observing:</t>
+  </si>
+  <si>
+    <t>{{STARTED_OBSERVING_HOURS}}</t>
+  </si>
+  <si>
+    <t>{{STARTED_OBSERVING_MINUTES}}</t>
+  </si>
+  <si>
+    <t>{{STARTED_OBSERVING_SECONDS}}</t>
+  </si>
+  <si>
+    <t>Enter Confidence Level Error Bars In Boxes Below</t>
+  </si>
+  <si>
+    <t>{{AOTA_D_HOURS}}</t>
+  </si>
+  <si>
+    <t>{{AOTA_D_MINUTES}}</t>
+  </si>
+  <si>
+    <t>{{AOTA_D_SECONDS}}</t>
+  </si>
+  <si>
+    <t>{{AOTA_D_ERROR}}</t>
+  </si>
+  <si>
+    <t>{{AOTA_R_ERROR}}</t>
+  </si>
+  <si>
+    <t>{{AOTA_R_HOURS}}</t>
+  </si>
+  <si>
+    <t>{{AOTA_R_MINUTES}}</t>
+  </si>
+  <si>
+    <t>{{AOTA_R_SECONDS}}</t>
+  </si>
+  <si>
+    <t>↑</t>
+  </si>
+  <si>
+    <t>Stopped Observing:</t>
+  </si>
+  <si>
+    <t>{{STOPPED_OBSERVING_HOURS}}</t>
+  </si>
+  <si>
+    <t>Units are in Seconds</t>
+  </si>
+  <si>
+    <t>hh</t>
+  </si>
+  <si>
+    <t>ss.sss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt; 95% confidence level will be reported to IOTA </t>
+  </si>
+  <si>
+    <t>{{WAS_MISS}}</t>
+  </si>
+  <si>
+    <t>Was this a Miss?</t>
+  </si>
+  <si>
+    <t>{{SECOND_STAR}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2nd star</t>
+  </si>
+  <si>
+    <t>Select Yes if this report  is for the  second star of a double.</t>
+  </si>
+  <si>
+    <t>S/N =</t>
+  </si>
+  <si>
+    <t>{{SNR}}</t>
+  </si>
+  <si>
+    <t>(if known)</t>
+  </si>
+  <si>
+    <t>visible?</t>
+  </si>
+  <si>
+    <t>Additional</t>
+  </si>
+  <si>
+    <t>{{COMMENTS}}</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Email report to:  reports@asteroidoccultation.com</t>
+  </si>
+  <si>
+    <t>If available please include a Tangra or Limovie CSV file of the light curve data with the report.</t>
+  </si>
+  <si>
+    <t>TYC       xxxx-xxxxx-x</t>
+  </si>
+  <si>
+    <t>NAD1927</t>
+  </si>
+  <si>
+    <t>HIP  xxxxxx</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>WGS84</t>
+  </si>
+  <si>
+    <t>UCAC2        xxxxxxxx</t>
+  </si>
+  <si>
+    <t>1x</t>
+  </si>
+  <si>
+    <t>EP1950</t>
+  </si>
+  <si>
+    <t>UCAC3     xxx - xxxxxx</t>
+  </si>
+  <si>
+    <t>2x</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
+    <t>UCAC4     xxx - xxxxxx</t>
+  </si>
+  <si>
+    <t>4x</t>
+  </si>
+  <si>
+    <t>GBSN80</t>
+  </si>
+  <si>
+    <t>G-coords hhmmss.s?ddmmss</t>
+  </si>
+  <si>
+    <t>6x</t>
+  </si>
+  <si>
+    <t>URAT1    xxx - xxxxxxx</t>
+  </si>
+  <si>
+    <t>8x</t>
+  </si>
+  <si>
+    <t>1B    xxx - xxxxxxx</t>
+  </si>
+  <si>
+    <t>10x</t>
+  </si>
+  <si>
+    <t>1N    xxx - xxxxxxx</t>
+  </si>
+  <si>
+    <t>12x</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>in</t>
+  </si>
+  <si>
+    <t>14x</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>ft</t>
+  </si>
+  <si>
+    <t>cm</t>
+  </si>
+  <si>
+    <t>16x</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>24x</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>32x</t>
+  </si>
+  <si>
+    <t>Unsure</t>
+  </si>
+  <si>
+    <t>48x</t>
+  </si>
+  <si>
+    <t>64x</t>
+  </si>
+  <si>
+    <t>96x</t>
+  </si>
+  <si>
+    <t>128x</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Visual, PE applied</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>256x</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Visual, standard PE applied</t>
+  </si>
+  <si>
+    <t>Fair</t>
+  </si>
+  <si>
+    <t>512x</t>
+  </si>
+  <si>
+    <t>Visual, no PE applied</t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>GPS - time inserted</t>
+  </si>
+  <si>
+    <t>CCD (specify exp in comments)</t>
+  </si>
+  <si>
+    <t>Video with frame analysis</t>
+  </si>
+  <si>
+    <t>GPS - other linking</t>
+  </si>
+  <si>
+    <t>Flea (specify exp in comments)</t>
+  </si>
+  <si>
+    <t>Video, photo or photoelectric</t>
+  </si>
+  <si>
+    <t>Video + audio time signal</t>
+  </si>
+  <si>
+    <t>Grasshopper (specify exp in comments)</t>
+  </si>
+  <si>
+    <t>Only duration timed</t>
+  </si>
+  <si>
+    <t>Tape Recorder + time signal</t>
+  </si>
+  <si>
+    <t>QHY (specify exp in comments)</t>
+  </si>
+  <si>
+    <t>Drift scan</t>
+  </si>
+  <si>
+    <t>Eye-Ear + time signal</t>
+  </si>
+  <si>
+    <t>Other - List in Comments</t>
+  </si>
+  <si>
+    <t>Preliminary only</t>
+  </si>
+  <si>
+    <t>Stopwatch</t>
+  </si>
+  <si>
+    <t>Radio broadcast - calibrated</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>clouds</t>
+  </si>
+  <si>
+    <t>lights</t>
+  </si>
+  <si>
+    <t>other - list in comments</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>deg mm sec.ss</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>deg min.mmm</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>deg.ddddd</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>Clear</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>Fog</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>maybe</t>
+  </si>
+  <si>
+    <t>Thin cloud &lt; 2</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>Thick cloud &gt; 2</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>Broken cloud</t>
+  </si>
+  <si>
+    <t>Star faint</t>
+  </si>
+  <si>
+    <t>PE applied by observer</t>
+  </si>
+  <si>
+    <t>Averted vision</t>
+  </si>
+  <si>
+    <t>Camera Delay by AOTA applied ---&gt;</t>
+  </si>
+  <si>
+    <t>Camera Delay  by ROTE applied ---&gt;</t>
+  </si>
+  <si>
+    <t>Camera Delay by Occular applied ---&gt;</t>
+  </si>
+  <si>
+    <t>Standard PE applied, 1.0 sec</t>
+  </si>
+  <si>
+    <t>No PE/Delay applied</t>
+  </si>
+  <si>
+    <t>Steady</t>
+  </si>
+  <si>
+    <t>No Camera Delay Applied</t>
+  </si>
+  <si>
+    <t>Slight flickering</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Strong flickering</t>
+  </si>
+  <si>
+    <t>check this table</t>
+  </si>
+  <si>
+    <t>Newtonian</t>
+  </si>
+  <si>
+    <t>SCT including Cass and Mak</t>
+  </si>
+  <si>
+    <t>Refractor</t>
+  </si>
+  <si>
+    <t>Dobsonian</t>
+  </si>
+  <si>
+    <t>binoculars</t>
+  </si>
+  <si>
+    <t>no optical aid</t>
+  </si>
+  <si>
+    <t>other - specify below</t>
+  </si>
+  <si>
+    <t>PAL/CCIR</t>
+  </si>
+  <si>
+    <t>NTSC/EIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>AAV-NTSC</t>
+  </si>
+  <si>
+    <t>Frames</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>CCD Drift Scan</t>
+  </si>
+  <si>
+    <t>AAV-PAL</t>
+  </si>
+  <si>
+    <t>Fields</t>
+  </si>
+  <si>
+    <t>AOTA w/ CamDelay Corrections</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>ADVS</t>
+  </si>
+  <si>
+    <t>Seconds</t>
+  </si>
+  <si>
+    <t>Occular</t>
+  </si>
+  <si>
+    <t>Flea 3-03S1 with ADVS</t>
+  </si>
+  <si>
+    <t>CCD Drift</t>
+  </si>
+  <si>
+    <t>Minutes</t>
+  </si>
+  <si>
+    <t>R-OTE w/ CamDelay Corrections</t>
+  </si>
+  <si>
+    <t>Flea 3-03S3 with ADVS</t>
+  </si>
+  <si>
+    <t>FITS Images</t>
+  </si>
+  <si>
+    <t>R-OTE w/o CamDelay Corrections</t>
+  </si>
+  <si>
+    <t>Flea 3-28S4M with ADVS</t>
+  </si>
+  <si>
     <t>PYOTE</t>
-  </si>
-  <si>
-    <t>Video</t>
-  </si>
-  <si>
-    <t>Exposure</t>
-  </si>
-  <si>
-    <t>Other Detector related info</t>
-  </si>
-  <si>
-    <t>Detector:</t>
-  </si>
-  <si>
-    <t>Model/Type:</t>
-  </si>
-  <si>
-    <t>{{DETECTOR}}</t>
-  </si>
-  <si>
-    <t>Format:</t>
-  </si>
-  <si>
-    <t>{{VIDEO_FORMAT}}</t>
-  </si>
-  <si>
-    <t>Integration:</t>
-  </si>
-  <si>
-    <t>{{INTEGRATION}}</t>
-  </si>
-  <si>
-    <t>{{INTEGRATION_UNITS}}</t>
-  </si>
-  <si>
-    <t>{{OTHER_DETECTOR_RELATED_INFO}}</t>
-  </si>
-  <si>
-    <t>Conditions:</t>
-  </si>
-  <si>
-    <t>Clouds:</t>
-  </si>
-  <si>
-    <t>Stability:</t>
-  </si>
-  <si>
-    <t>Other conditions:</t>
-  </si>
-  <si>
-    <t>Observations:</t>
-  </si>
-  <si>
-    <t>Times</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>PE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remarks </t>
-  </si>
-  <si>
-    <t>Started Observing:</t>
-  </si>
-  <si>
-    <t>{{STARTED_OBSERVING_HOURS}}</t>
-  </si>
-  <si>
-    <t>{{STARTED_OBSERVING_MINUTES}}</t>
-  </si>
-  <si>
-    <t>{{STARTED_OBSERVING_SECONDS}}</t>
-  </si>
-  <si>
-    <t>Enter Confidence Level Error Bars In Boxes Below</t>
-  </si>
-  <si>
-    <t>{{AOTA_D_HOURS}}</t>
-  </si>
-  <si>
-    <t>{{AOTA_D_MINUTES}}</t>
-  </si>
-  <si>
-    <t>{{AOTA_D_SECONDS}}</t>
-  </si>
-  <si>
-    <t>{{AOTA_D_ERROR}}</t>
-  </si>
-  <si>
-    <t>{{AOTA_R_ERROR}}</t>
-  </si>
-  <si>
-    <t>{{AOTA_R_HOURS}}</t>
-  </si>
-  <si>
-    <t>{{AOTA_R_MINUTES}}</t>
-  </si>
-  <si>
-    <t>{{AOTA_R_SECONDS}}</t>
-  </si>
-  <si>
-    <t>↑</t>
-  </si>
-  <si>
-    <t>Stopped Observing:</t>
-  </si>
-  <si>
-    <t>{{STOPPED_OBSERVING_HOURS}}</t>
-  </si>
-  <si>
-    <t>Units are in Seconds</t>
-  </si>
-  <si>
-    <t>hh</t>
-  </si>
-  <si>
-    <t>ss.sss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt; 95% confidence level will be reported to IOTA </t>
-  </si>
-  <si>
-    <t>{{WAS_MISS}}</t>
-  </si>
-  <si>
-    <t>Was this a Miss?</t>
-  </si>
-  <si>
-    <t>{{SECOND_STAR}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2nd star</t>
-  </si>
-  <si>
-    <t>Select Yes if this report  is for the  second star of a double.</t>
-  </si>
-  <si>
-    <t>S/N =</t>
-  </si>
-  <si>
-    <t>{{SNR}}</t>
-  </si>
-  <si>
-    <t>(if known)</t>
-  </si>
-  <si>
-    <t>visible?</t>
-  </si>
-  <si>
-    <t>Additional</t>
-  </si>
-  <si>
-    <t>{{COMMENTS}}</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Email report to:  reports@asteroidoccultation.com</t>
-  </si>
-  <si>
-    <t>If available please include a Tangra or Limovie CSV file of the light curve data with the report.</t>
-  </si>
-  <si>
-    <t>TYC       xxxx-xxxxx-x</t>
-  </si>
-  <si>
-    <t>NAD1927</t>
-  </si>
-  <si>
-    <t>HIP  xxxxxx</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>WGS84</t>
-  </si>
-  <si>
-    <t>UCAC2        xxxxxxxx</t>
-  </si>
-  <si>
-    <t>1x</t>
-  </si>
-  <si>
-    <t>EP1950</t>
-  </si>
-  <si>
-    <t>UCAC3     xxx - xxxxxx</t>
-  </si>
-  <si>
-    <t>2x</t>
-  </si>
-  <si>
-    <t>Tokyo</t>
-  </si>
-  <si>
-    <t>UCAC4     xxx - xxxxxx</t>
-  </si>
-  <si>
-    <t>4x</t>
-  </si>
-  <si>
-    <t>GBSN80</t>
-  </si>
-  <si>
-    <t>G-coords hhmmss.s?ddmmss</t>
-  </si>
-  <si>
-    <t>6x</t>
-  </si>
-  <si>
-    <t>URAT1    xxx - xxxxxxx</t>
-  </si>
-  <si>
-    <t>8x</t>
-  </si>
-  <si>
-    <t>1B    xxx - xxxxxxx</t>
-  </si>
-  <si>
-    <t>10x</t>
-  </si>
-  <si>
-    <t>1N    xxx - xxxxxxx</t>
-  </si>
-  <si>
-    <t>12x</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>in</t>
-  </si>
-  <si>
-    <t>14x</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>ft</t>
-  </si>
-  <si>
-    <t>cm</t>
-  </si>
-  <si>
-    <t>16x</t>
-  </si>
-  <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t>24x</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>32x</t>
-  </si>
-  <si>
-    <t>Unsure</t>
-  </si>
-  <si>
-    <t>48x</t>
-  </si>
-  <si>
-    <t>64x</t>
-  </si>
-  <si>
-    <t>96x</t>
-  </si>
-  <si>
-    <t>128x</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Visual, PE applied</t>
-  </si>
-  <si>
-    <t>Good</t>
-  </si>
-  <si>
-    <t>256x</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>Visual, standard PE applied</t>
-  </si>
-  <si>
-    <t>Fair</t>
-  </si>
-  <si>
-    <t>512x</t>
-  </si>
-  <si>
-    <t>Visual, no PE applied</t>
-  </si>
-  <si>
-    <t>Poor</t>
-  </si>
-  <si>
-    <t>GPS - time inserted</t>
-  </si>
-  <si>
-    <t>CCD (specify exp in comments)</t>
-  </si>
-  <si>
-    <t>Video with frame analysis</t>
-  </si>
-  <si>
-    <t>GPS - other linking</t>
-  </si>
-  <si>
-    <t>Flea (specify exp in comments)</t>
-  </si>
-  <si>
-    <t>Video, photo or photoelectric</t>
-  </si>
-  <si>
-    <t>Video + audio time signal</t>
-  </si>
-  <si>
-    <t>Grasshopper (specify exp in comments)</t>
-  </si>
-  <si>
-    <t>Only duration timed</t>
-  </si>
-  <si>
-    <t>Tape Recorder + time signal</t>
-  </si>
-  <si>
-    <t>QHY (specify exp in comments)</t>
-  </si>
-  <si>
-    <t>Drift scan</t>
-  </si>
-  <si>
-    <t>Eye-Ear + time signal</t>
-  </si>
-  <si>
-    <t>Other - List in Comments</t>
-  </si>
-  <si>
-    <t>Preliminary only</t>
-  </si>
-  <si>
-    <t>Stopwatch</t>
-  </si>
-  <si>
-    <t>Radio broadcast - calibrated</t>
-  </si>
-  <si>
-    <t>wind</t>
-  </si>
-  <si>
-    <t>other</t>
-  </si>
-  <si>
-    <t>clouds</t>
-  </si>
-  <si>
-    <t>lights</t>
-  </si>
-  <si>
-    <t>other - list in comments</t>
-  </si>
-  <si>
-    <t>January</t>
-  </si>
-  <si>
-    <t>February</t>
-  </si>
-  <si>
-    <t>March</t>
-  </si>
-  <si>
-    <t>April</t>
-  </si>
-  <si>
-    <t>deg mm sec.ss</t>
-  </si>
-  <si>
-    <t>May</t>
-  </si>
-  <si>
-    <t>deg min.mmm</t>
-  </si>
-  <si>
-    <t>June</t>
-  </si>
-  <si>
-    <t>deg.ddddd</t>
-  </si>
-  <si>
-    <t>July</t>
-  </si>
-  <si>
-    <t>August</t>
-  </si>
-  <si>
-    <t>Clear</t>
-  </si>
-  <si>
-    <t>September</t>
-  </si>
-  <si>
-    <t>Fog</t>
-  </si>
-  <si>
-    <t>October</t>
-  </si>
-  <si>
-    <t>maybe</t>
-  </si>
-  <si>
-    <t>Thin cloud &lt; 2</t>
-  </si>
-  <si>
-    <t>November</t>
-  </si>
-  <si>
-    <t>Thick cloud &gt; 2</t>
-  </si>
-  <si>
-    <t>December</t>
-  </si>
-  <si>
-    <t>Broken cloud</t>
-  </si>
-  <si>
-    <t>Star faint</t>
-  </si>
-  <si>
-    <t>PE applied by observer</t>
-  </si>
-  <si>
-    <t>Averted vision</t>
-  </si>
-  <si>
-    <t>Camera Delay by AOTA applied ---&gt;</t>
-  </si>
-  <si>
-    <t>Camera Delay  by ROTE applied ---&gt;</t>
-  </si>
-  <si>
-    <t>Camera Delay by Occular applied ---&gt;</t>
-  </si>
-  <si>
-    <t>Standard PE applied, 1.0 sec</t>
-  </si>
-  <si>
-    <t>No PE/Delay applied</t>
-  </si>
-  <si>
-    <t>Steady</t>
-  </si>
-  <si>
-    <t>No Camera Delay Applied</t>
-  </si>
-  <si>
-    <t>Slight flickering</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>Strong flickering</t>
-  </si>
-  <si>
-    <t>check this table</t>
-  </si>
-  <si>
-    <t>Newtonian</t>
-  </si>
-  <si>
-    <t>SCT including Cass and Mak</t>
-  </si>
-  <si>
-    <t>Refractor</t>
-  </si>
-  <si>
-    <t>Dobsonian</t>
-  </si>
-  <si>
-    <t>binoculars</t>
-  </si>
-  <si>
-    <t>no optical aid</t>
-  </si>
-  <si>
-    <t>other - specify below</t>
-  </si>
-  <si>
-    <t>PAL/CCIR</t>
-  </si>
-  <si>
-    <t>NTSC/EIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>AAV-NTSC</t>
-  </si>
-  <si>
-    <t>Frames</t>
-  </si>
-  <si>
-    <t>Manual</t>
-  </si>
-  <si>
-    <t>CCD Drift Scan</t>
-  </si>
-  <si>
-    <t>AAV-PAL</t>
-  </si>
-  <si>
-    <t>Fields</t>
-  </si>
-  <si>
-    <t>AOTA w/ CamDelay Corrections</t>
-  </si>
-  <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
-    <t>ADVS</t>
-  </si>
-  <si>
-    <t>Seconds</t>
-  </si>
-  <si>
-    <t>Occular</t>
-  </si>
-  <si>
-    <t>Flea 3-03S1 with ADVS</t>
-  </si>
-  <si>
-    <t>CCD Drift</t>
-  </si>
-  <si>
-    <t>Minutes</t>
-  </si>
-  <si>
-    <t>R-OTE w/ CamDelay Corrections</t>
-  </si>
-  <si>
-    <t>Flea 3-03S3 with ADVS</t>
-  </si>
-  <si>
-    <t>FITS Images</t>
-  </si>
-  <si>
-    <t>R-OTE w/o CamDelay Corrections</t>
-  </si>
-  <si>
-    <t>Flea 3-28S4M with ADVS</t>
   </si>
   <si>
     <t>Grasshopper Express with ADVS</t>
@@ -4049,11 +4052,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -8686,21 +8689,21 @@
     </row>
     <row r="149" spans="1:16" ht="18">
       <c r="A149" s="156"/>
-      <c r="B149" s="227"/>
-      <c r="C149" s="227"/>
-      <c r="D149" s="227"/>
-      <c r="E149" s="227"/>
-      <c r="F149" s="227"/>
-      <c r="G149" s="227"/>
-      <c r="H149" s="227"/>
-      <c r="I149" s="227"/>
-      <c r="J149" s="227"/>
-      <c r="K149" s="227"/>
-      <c r="L149" s="227"/>
-      <c r="M149" s="227"/>
-      <c r="N149" s="227"/>
-      <c r="O149" s="227"/>
-      <c r="P149" s="227"/>
+      <c r="B149" s="228"/>
+      <c r="C149" s="228"/>
+      <c r="D149" s="228"/>
+      <c r="E149" s="228"/>
+      <c r="F149" s="228"/>
+      <c r="G149" s="228"/>
+      <c r="H149" s="228"/>
+      <c r="I149" s="228"/>
+      <c r="J149" s="228"/>
+      <c r="K149" s="228"/>
+      <c r="L149" s="228"/>
+      <c r="M149" s="228"/>
+      <c r="N149" s="228"/>
+      <c r="O149" s="228"/>
+      <c r="P149" s="228"/>
     </row>
     <row r="150" spans="1:16" ht="18">
       <c r="A150" s="65" t="s">
@@ -9538,7 +9541,7 @@
       <c r="Q10" s="226"/>
       <c r="R10" s="226"/>
       <c r="S10" s="231"/>
-      <c r="T10" s="228"/>
+      <c r="T10" s="227"/>
       <c r="U10" s="231"/>
       <c r="V10" s="231"/>
       <c r="W10" s="231"/>
@@ -9608,7 +9611,7 @@
       <c r="Q12" s="133"/>
       <c r="R12" s="133"/>
       <c r="S12" s="231"/>
-      <c r="T12" s="228"/>
+      <c r="T12" s="227"/>
       <c r="U12" s="231"/>
       <c r="V12" s="231"/>
       <c r="W12" s="231"/>
@@ -11652,7 +11655,7 @@
       <c r="B27" s="156"/>
       <c r="C27" s="156">
         <f ca="1">YEAR(NOW())-3</f>
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D27" s="156"/>
       <c r="E27" s="156"/>
@@ -11667,7 +11670,7 @@
       <c r="B28" s="156"/>
       <c r="C28" s="156">
         <f t="shared" ref="C28:C35" ca="1" si="0">C27+1</f>
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D28" s="156"/>
       <c r="E28" s="156"/>
@@ -11682,7 +11685,7 @@
       <c r="B29" s="156"/>
       <c r="C29" s="156">
         <f t="shared" ca="1" si="0"/>
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D29" s="156"/>
       <c r="E29" s="156"/>
@@ -11699,7 +11702,7 @@
       <c r="B30" s="156"/>
       <c r="C30" s="156">
         <f t="shared" ca="1" si="0"/>
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D30" s="156"/>
       <c r="E30" s="156"/>
@@ -11714,7 +11717,7 @@
       <c r="B31" s="156"/>
       <c r="C31" s="156">
         <f t="shared" ca="1" si="0"/>
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="D31" s="156"/>
       <c r="E31" s="156"/>
@@ -11729,7 +11732,7 @@
       <c r="B32" s="156"/>
       <c r="C32" s="156">
         <f t="shared" ca="1" si="0"/>
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="D32" s="156"/>
       <c r="E32" s="156"/>
@@ -11744,7 +11747,7 @@
       <c r="B33" s="156"/>
       <c r="C33" s="156">
         <f t="shared" ca="1" si="0"/>
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="D33" s="156"/>
       <c r="E33" s="156"/>
@@ -11759,7 +11762,7 @@
       <c r="B34" s="156"/>
       <c r="C34" s="156">
         <f t="shared" ca="1" si="0"/>
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="D34" s="156"/>
       <c r="E34" s="156"/>
@@ -11774,7 +11777,7 @@
       <c r="B35" s="156"/>
       <c r="C35" s="156">
         <f t="shared" ca="1" si="0"/>
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="D35" s="156"/>
       <c r="E35" s="156"/>
@@ -12186,10 +12189,10 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="218" t="s">
-        <v>261</v>
+        <v>454</v>
       </c>
       <c r="B66" s="219" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C66" s="156"/>
       <c r="D66" s="156"/>
@@ -12202,10 +12205,10 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="219" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B67" s="219" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C67" s="156"/>
       <c r="D67" s="156"/>
@@ -12217,7 +12220,7 @@
     <row r="68" spans="1:8">
       <c r="A68" s="156"/>
       <c r="B68" s="219" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C68" s="156"/>
       <c r="D68" s="156"/>
@@ -12229,7 +12232,7 @@
     <row r="69" spans="1:8">
       <c r="A69" s="156"/>
       <c r="B69" s="219" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C69" s="156"/>
       <c r="D69" s="156"/>
@@ -12240,10 +12243,10 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="156" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B70" s="219" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C70" s="156"/>
       <c r="D70" s="156"/>
@@ -12254,10 +12257,10 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="156" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B71" s="218" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C71" s="156"/>
       <c r="D71" s="156"/>
@@ -12268,10 +12271,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="156" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B72" s="219" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C72" s="219"/>
       <c r="D72" s="219"/>
@@ -12283,7 +12286,7 @@
     <row r="73" spans="1:8">
       <c r="A73" s="156"/>
       <c r="B73" s="219" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C73" s="219"/>
       <c r="D73" s="219"/>
@@ -12295,7 +12298,7 @@
     <row r="74" spans="1:8">
       <c r="A74" s="156"/>
       <c r="B74" s="219" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C74" s="219"/>
       <c r="D74" s="219"/>
@@ -12307,7 +12310,7 @@
     <row r="75" spans="1:8">
       <c r="A75" s="156"/>
       <c r="B75" s="219" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C75" s="219"/>
       <c r="D75" s="219"/>
@@ -12319,7 +12322,7 @@
     <row r="76" spans="1:8">
       <c r="A76" s="156"/>
       <c r="B76" s="218" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C76" s="219"/>
       <c r="D76" s="219"/>
@@ -12331,7 +12334,7 @@
     <row r="77" spans="1:8">
       <c r="A77" s="156"/>
       <c r="B77" s="219" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C77" s="219"/>
       <c r="D77" s="219"/>
@@ -12343,7 +12346,7 @@
     <row r="78" spans="1:8">
       <c r="A78" s="156"/>
       <c r="B78" s="219" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C78" s="219"/>
       <c r="D78" s="219"/>
@@ -12355,7 +12358,7 @@
     <row r="79" spans="1:8">
       <c r="A79" s="156"/>
       <c r="B79" s="219" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C79" s="219"/>
       <c r="D79" s="219"/>
@@ -12367,7 +12370,7 @@
     <row r="80" spans="1:8">
       <c r="A80" s="156"/>
       <c r="B80" s="219" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C80" s="219"/>
       <c r="D80" s="219"/>
@@ -12378,7 +12381,7 @@
     </row>
     <row r="81" spans="2:5">
       <c r="B81" s="218" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C81" s="219"/>
       <c r="D81" s="219"/>
@@ -12386,7 +12389,7 @@
     </row>
     <row r="82" spans="2:5">
       <c r="B82" s="219" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C82" s="219"/>
       <c r="D82" s="219"/>
@@ -12394,7 +12397,7 @@
     </row>
     <row r="83" spans="2:5">
       <c r="B83" s="219" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C83" s="219"/>
       <c r="D83" s="219"/>
@@ -12402,7 +12405,7 @@
     </row>
     <row r="84" spans="2:5">
       <c r="B84" s="219" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C84" s="156"/>
       <c r="D84" s="156"/>
@@ -12410,7 +12413,7 @@
     </row>
     <row r="85" spans="2:5">
       <c r="B85" s="219" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C85" s="219"/>
       <c r="D85" s="219"/>
@@ -12440,7 +12443,7 @@
     </row>
     <row r="89" spans="2:5">
       <c r="B89" s="219" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C89" s="219"/>
       <c r="D89" s="219"/>
@@ -12456,7 +12459,7 @@
     </row>
     <row r="91" spans="2:5">
       <c r="B91" s="219" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C91" s="219"/>
       <c r="D91" s="219"/>
@@ -12464,7 +12467,7 @@
     </row>
     <row r="92" spans="2:5">
       <c r="B92" s="219" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C92" s="219"/>
       <c r="D92" s="219"/>
@@ -12472,7 +12475,7 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" s="219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C93" s="219"/>
       <c r="D93" s="219"/>
@@ -12480,7 +12483,7 @@
     </row>
     <row r="94" spans="2:5">
       <c r="B94" s="219" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C94" s="219"/>
       <c r="D94" s="219"/>
@@ -12488,7 +12491,7 @@
     </row>
     <row r="95" spans="2:5">
       <c r="B95" s="219" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C95" s="219"/>
       <c r="D95" s="219"/>
@@ -12496,7 +12499,7 @@
     </row>
     <row r="96" spans="2:5">
       <c r="B96" s="219" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C96" s="219"/>
       <c r="D96" s="219"/>
@@ -12504,7 +12507,7 @@
     </row>
     <row r="97" spans="2:5">
       <c r="B97" s="219" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C97" s="219"/>
       <c r="D97" s="219"/>
@@ -12520,7 +12523,7 @@
     </row>
     <row r="99" spans="2:5">
       <c r="B99" s="219" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C99" s="156"/>
       <c r="D99" s="156"/>
@@ -12528,7 +12531,7 @@
     </row>
     <row r="100" spans="2:5">
       <c r="B100" s="219" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C100" s="156"/>
       <c r="D100" s="156"/>
@@ -12554,7 +12557,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="24" customHeight="1">
       <c r="A1" s="253" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B1" s="260"/>
       <c r="C1" s="260"/>
@@ -12572,21 +12575,21 @@
     </row>
     <row r="4" spans="1:14" ht="15.95" customHeight="1">
       <c r="A4" s="260" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B4" s="260"/>
       <c r="C4" s="260"/>
       <c r="D4" s="260"/>
       <c r="E4" s="156"/>
       <c r="F4" s="260" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G4" s="260"/>
       <c r="H4" s="260"/>
       <c r="I4" s="260"/>
       <c r="J4" s="156"/>
       <c r="K4" s="260" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L4" s="260"/>
       <c r="M4" s="260"/>
@@ -12594,7 +12597,7 @@
     </row>
     <row r="5" spans="1:14" ht="15.95" customHeight="1">
       <c r="A5" s="260" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B5" s="336"/>
       <c r="C5" s="336"/>
@@ -12634,7 +12637,7 @@
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="337" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B7" s="337"/>
       <c r="C7" s="337"/>
@@ -12648,7 +12651,7 @@
       <c r="I7" s="333"/>
       <c r="J7" s="156"/>
       <c r="K7" s="333" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L7" s="333"/>
       <c r="M7" s="333"/>
@@ -12670,7 +12673,7 @@
       <c r="I8" s="333"/>
       <c r="J8" s="156"/>
       <c r="K8" s="333" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L8" s="333"/>
       <c r="M8" s="333"/>
@@ -12678,21 +12681,21 @@
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="337" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B9" s="337"/>
       <c r="C9" s="337"/>
       <c r="D9" s="337"/>
       <c r="E9" s="156"/>
       <c r="F9" s="333" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="G9" s="333"/>
       <c r="H9" s="333"/>
       <c r="I9" s="333"/>
       <c r="J9" s="156"/>
       <c r="K9" s="333" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L9" s="333"/>
       <c r="M9" s="333"/>
@@ -12700,7 +12703,7 @@
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="337" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B10" s="337"/>
       <c r="C10" s="337"/>
@@ -12712,7 +12715,7 @@
       <c r="I10" s="156"/>
       <c r="J10" s="156"/>
       <c r="K10" s="333" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="L10" s="333"/>
       <c r="M10" s="333"/>
@@ -12730,7 +12733,7 @@
       <c r="I11" s="156"/>
       <c r="J11" s="156"/>
       <c r="K11" s="333" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L11" s="333"/>
       <c r="M11" s="333"/>
@@ -12748,7 +12751,7 @@
       <c r="I12" s="156"/>
       <c r="J12" s="156"/>
       <c r="K12" s="333" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L12" s="333"/>
       <c r="M12" s="333"/>
@@ -12766,7 +12769,7 @@
       <c r="I13" s="156"/>
       <c r="J13" s="156"/>
       <c r="K13" s="333" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L13" s="333"/>
       <c r="M13" s="333"/>
@@ -12802,7 +12805,7 @@
       <c r="I15" s="156"/>
       <c r="J15" s="156"/>
       <c r="K15" s="333" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L15" s="333"/>
       <c r="M15" s="333"/>
@@ -12820,7 +12823,7 @@
       <c r="I16" s="156"/>
       <c r="J16" s="156"/>
       <c r="K16" s="333" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L16" s="333"/>
       <c r="M16" s="333"/>
@@ -12860,21 +12863,21 @@
     </row>
     <row r="19" spans="1:14" ht="15.95" customHeight="1">
       <c r="A19" s="260" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B19" s="260"/>
       <c r="C19" s="260"/>
       <c r="D19" s="260"/>
       <c r="E19" s="156"/>
       <c r="F19" s="260" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G19" s="260"/>
       <c r="H19" s="260"/>
       <c r="I19" s="260"/>
       <c r="J19" s="156"/>
       <c r="K19" s="260" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L19" s="260"/>
       <c r="M19" s="260"/>
@@ -12887,7 +12890,7 @@
       <c r="D20" s="156"/>
       <c r="E20" s="156"/>
       <c r="F20" s="334" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="G20" s="334"/>
       <c r="H20" s="334"/>
@@ -12902,14 +12905,14 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" s="333" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B21" s="333"/>
       <c r="C21" s="333"/>
       <c r="D21" s="333"/>
       <c r="E21" s="156"/>
       <c r="F21" s="334" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="G21" s="334"/>
       <c r="H21" s="334"/>
@@ -12924,7 +12927,7 @@
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="333" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B22" s="333"/>
       <c r="C22" s="333"/>
@@ -12944,14 +12947,14 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="333" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B23" s="333"/>
       <c r="C23" s="333"/>
       <c r="D23" s="333"/>
       <c r="E23" s="156"/>
       <c r="F23" s="335" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G23" s="335"/>
       <c r="H23" s="335"/>
@@ -12966,7 +12969,7 @@
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="333" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B24" s="333"/>
       <c r="C24" s="333"/>
@@ -12986,14 +12989,14 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="333" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B25" s="333"/>
       <c r="C25" s="333"/>
       <c r="D25" s="333"/>
       <c r="E25" s="156"/>
       <c r="F25" s="239" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G25" s="239"/>
       <c r="H25" s="239"/>
@@ -13008,14 +13011,14 @@
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="333" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B26" s="333"/>
       <c r="C26" s="333"/>
       <c r="D26" s="333"/>
       <c r="E26" s="156"/>
       <c r="F26" s="239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G26" s="239"/>
       <c r="H26" s="239"/>
@@ -13028,7 +13031,7 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="333" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B27" s="333"/>
       <c r="C27" s="333"/>
@@ -13046,14 +13049,14 @@
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="333" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B28" s="333"/>
       <c r="C28" s="333"/>
       <c r="D28" s="333"/>
       <c r="E28" s="156"/>
       <c r="F28" s="239" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G28" s="239"/>
       <c r="H28" s="239"/>
@@ -13066,14 +13069,14 @@
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="333" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B29" s="333"/>
       <c r="C29" s="333"/>
       <c r="D29" s="333"/>
       <c r="E29" s="156"/>
       <c r="F29" s="239" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="G29" s="239"/>
       <c r="H29" s="239"/>
@@ -13086,7 +13089,7 @@
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="333" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B30" s="333"/>
       <c r="C30" s="333"/>
@@ -13099,21 +13102,21 @@
       <c r="J30" s="156"/>
       <c r="K30" s="156"/>
       <c r="L30" s="72" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M30" s="156"/>
       <c r="N30" s="156"/>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="333" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B31" s="333"/>
       <c r="C31" s="333"/>
       <c r="D31" s="333"/>
       <c r="E31" s="156"/>
       <c r="F31" s="239" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="G31" s="239"/>
       <c r="H31" s="239"/>
@@ -13121,21 +13124,21 @@
       <c r="J31" s="156"/>
       <c r="K31" s="156"/>
       <c r="L31" s="156" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M31" s="156"/>
       <c r="N31" s="156"/>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="333" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B32" s="333"/>
       <c r="C32" s="333"/>
       <c r="D32" s="333"/>
       <c r="E32" s="156"/>
       <c r="F32" s="239" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G32" s="239"/>
       <c r="H32" s="239"/>
@@ -13143,14 +13146,14 @@
       <c r="J32" s="156"/>
       <c r="K32" s="156"/>
       <c r="L32" s="156" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M32" s="156"/>
       <c r="N32" s="156"/>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="333" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B33" s="333"/>
       <c r="C33" s="333"/>
@@ -13163,19 +13166,19 @@
       <c r="J33" s="156"/>
       <c r="K33" s="156"/>
       <c r="L33" s="156" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" s="333" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B34" s="333"/>
       <c r="C34" s="333"/>
       <c r="D34" s="333"/>
       <c r="E34" s="156"/>
       <c r="F34" s="239" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="G34" s="239"/>
       <c r="H34" s="239"/>
@@ -13186,14 +13189,14 @@
     </row>
     <row r="35" spans="1:12">
       <c r="A35" s="333" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B35" s="333"/>
       <c r="C35" s="333"/>
       <c r="D35" s="333"/>
       <c r="E35" s="156"/>
       <c r="F35" s="239" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G35" s="239"/>
       <c r="H35" s="239"/>
@@ -13204,7 +13207,7 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" s="333" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B36" s="333"/>
       <c r="C36" s="333"/>
@@ -13227,7 +13230,7 @@
       <c r="D37" s="333"/>
       <c r="E37" s="156"/>
       <c r="F37" s="239" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="G37" s="239"/>
       <c r="H37" s="239"/>
@@ -13261,7 +13264,7 @@
       <c r="D39" s="333"/>
       <c r="E39" s="156"/>
       <c r="F39" s="239" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="G39" s="239"/>
       <c r="H39" s="239"/>
@@ -13272,7 +13275,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="333" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B40" s="333"/>
       <c r="C40" s="333"/>
@@ -13288,14 +13291,14 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" s="333" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B41" s="333"/>
       <c r="C41" s="333"/>
       <c r="D41" s="333"/>
       <c r="E41" s="156"/>
       <c r="F41" s="335" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G41" s="335"/>
       <c r="H41" s="335"/>
@@ -13306,7 +13309,7 @@
     </row>
     <row r="42" spans="1:12">
       <c r="A42" s="333" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B42" s="333"/>
       <c r="C42" s="333"/>
@@ -13579,7 +13582,7 @@
   <sheetData>
     <row r="2" spans="1:21" ht="21.75" customHeight="1">
       <c r="A2" s="253" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B2" s="253"/>
       <c r="C2" s="253"/>
@@ -13628,7 +13631,7 @@
     <row r="5" spans="1:21" ht="26.1" customHeight="1">
       <c r="A5" s="156"/>
       <c r="B5" s="357" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C5" s="336"/>
       <c r="D5" s="336"/>
@@ -13638,7 +13641,7 @@
       <c r="H5" s="249"/>
       <c r="I5" s="156"/>
       <c r="J5" s="365" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="K5" s="365"/>
       <c r="L5" s="365"/>
@@ -13655,14 +13658,14 @@
     <row r="6" spans="1:21" ht="18" customHeight="1">
       <c r="A6" s="156"/>
       <c r="B6" s="350" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C6" s="336"/>
       <c r="D6" s="336" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E6" s="336" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F6" s="349"/>
       <c r="G6" s="249"/>
@@ -13672,10 +13675,10 @@
       <c r="K6" s="47"/>
       <c r="L6" s="47"/>
       <c r="M6" s="67" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N6" s="67" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O6" s="47"/>
       <c r="P6" s="47"/>
@@ -13688,34 +13691,34 @@
     <row r="7" spans="1:21" ht="18" customHeight="1">
       <c r="A7" s="156"/>
       <c r="B7" s="242" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C7" s="240" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D7" s="336"/>
       <c r="E7" s="240" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F7" s="247" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G7" s="249"/>
       <c r="H7" s="249"/>
       <c r="I7" s="156"/>
       <c r="J7" s="358" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="K7" s="358"/>
       <c r="L7" s="358"/>
       <c r="M7" s="244" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N7" s="244" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O7" s="360" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P7" s="360"/>
       <c r="Q7" s="360"/>
@@ -13729,10 +13732,10 @@
         <v>323</v>
       </c>
       <c r="B8" s="242" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C8" s="226" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D8" s="240">
         <v>2</v>
@@ -13747,18 +13750,18 @@
       <c r="H8" s="50"/>
       <c r="I8" s="156"/>
       <c r="J8" s="358" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="K8" s="358"/>
       <c r="L8" s="358"/>
       <c r="M8" s="68" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N8" s="71" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O8" s="245" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P8" s="245"/>
       <c r="Q8" s="245"/>
@@ -13772,10 +13775,10 @@
         <v>326</v>
       </c>
       <c r="B9" s="242" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C9" s="203" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D9" s="240">
         <v>3</v>
@@ -13790,15 +13793,15 @@
       <c r="H9" s="50"/>
       <c r="I9" s="156"/>
       <c r="J9" s="358" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="K9" s="358"/>
       <c r="L9" s="358"/>
       <c r="M9" s="69" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N9" s="244" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O9" s="61"/>
       <c r="P9" s="61"/>
@@ -13813,10 +13816,10 @@
         <v>329</v>
       </c>
       <c r="B10" s="242" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C10" s="226" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D10" s="240">
         <v>5</v>
@@ -13831,7 +13834,7 @@
       <c r="H10" s="50"/>
       <c r="I10" s="156"/>
       <c r="J10" s="358" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="K10" s="358"/>
       <c r="L10" s="358"/>
@@ -13854,10 +13857,10 @@
         <v>334</v>
       </c>
       <c r="B11" s="242" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C11" s="226" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D11" s="240">
         <v>9</v>
@@ -13872,15 +13875,15 @@
       <c r="H11" s="50"/>
       <c r="I11" s="156"/>
       <c r="J11" s="358" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="K11" s="358"/>
       <c r="L11" s="358"/>
       <c r="M11" s="69" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N11" s="244" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O11" s="61"/>
       <c r="P11" s="61"/>
@@ -13895,10 +13898,10 @@
         <v>348</v>
       </c>
       <c r="B12" s="242" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C12" s="226" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D12" s="240">
         <v>17</v>
@@ -13913,7 +13916,7 @@
       <c r="H12" s="50"/>
       <c r="I12" s="156"/>
       <c r="J12" s="358" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="K12" s="358"/>
       <c r="L12" s="358"/>
@@ -13936,10 +13939,10 @@
         <v>352</v>
       </c>
       <c r="B13" s="242" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C13" s="240" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D13" s="240">
         <v>33</v>
@@ -13954,7 +13957,7 @@
       <c r="H13" s="50"/>
       <c r="I13" s="156"/>
       <c r="J13" s="358" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K13" s="358"/>
       <c r="L13" s="358"/>
@@ -13977,10 +13980,10 @@
         <v>355</v>
       </c>
       <c r="B14" s="242" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C14" s="240" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D14" s="240">
         <v>65</v>
@@ -14012,10 +14015,10 @@
         <v>357</v>
       </c>
       <c r="B15" s="242" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C15" s="240" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D15" s="240">
         <v>129</v>
@@ -14047,10 +14050,10 @@
         <v>361</v>
       </c>
       <c r="B16" s="242" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C16" s="240" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D16" s="240">
         <v>257</v>
@@ -14082,10 +14085,10 @@
         <v>365</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D17" s="32">
         <v>513</v>
@@ -14113,7 +14116,7 @@
       <c r="B18" s="156"/>
       <c r="C18" s="156"/>
       <c r="D18" s="242" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E18" s="156"/>
       <c r="F18" s="156"/>
@@ -14134,7 +14137,7 @@
       <c r="B19" s="156"/>
       <c r="C19" s="156"/>
       <c r="D19" s="240" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E19" s="156"/>
       <c r="F19" s="156"/>
@@ -14153,7 +14156,7 @@
     <row r="20" spans="1:17">
       <c r="A20" s="156"/>
       <c r="B20" s="357" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C20" s="336"/>
       <c r="D20" s="336"/>
@@ -14174,14 +14177,14 @@
     <row r="21" spans="1:17" ht="26.1" customHeight="1">
       <c r="A21" s="156"/>
       <c r="B21" s="350" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C21" s="336"/>
       <c r="D21" s="336" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E21" s="336" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F21" s="349"/>
       <c r="G21" s="240"/>
@@ -14199,23 +14202,23 @@
     <row r="22" spans="1:17" ht="18" customHeight="1">
       <c r="A22" s="156"/>
       <c r="B22" s="242" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C22" s="240" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D22" s="336"/>
       <c r="E22" s="240" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F22" s="247" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G22" s="350"/>
       <c r="H22" s="336"/>
       <c r="I22" s="156"/>
       <c r="J22" s="359" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K22" s="352"/>
       <c r="L22" s="352"/>
@@ -14246,13 +14249,13 @@
       <c r="H23" s="240"/>
       <c r="I23" s="156"/>
       <c r="J23" s="352" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="K23" s="356"/>
       <c r="L23" s="356"/>
       <c r="M23" s="155"/>
       <c r="N23" s="352" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O23" s="352"/>
       <c r="P23" s="352"/>
@@ -14281,13 +14284,13 @@
       <c r="H24" s="240"/>
       <c r="I24" s="156"/>
       <c r="J24" s="352" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="K24" s="356"/>
       <c r="L24" s="356"/>
       <c r="M24" s="155"/>
       <c r="N24" s="352" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O24" s="352"/>
       <c r="P24" s="352"/>
@@ -14315,13 +14318,13 @@
       <c r="H25" s="240"/>
       <c r="I25" s="156"/>
       <c r="J25" s="352" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="K25" s="356"/>
       <c r="L25" s="356"/>
       <c r="M25" s="155"/>
       <c r="N25" s="352" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="O25" s="352"/>
       <c r="P25" s="352"/>
@@ -14349,13 +14352,13 @@
       <c r="H26" s="240"/>
       <c r="I26" s="156"/>
       <c r="J26" s="352" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="K26" s="352"/>
       <c r="L26" s="352"/>
       <c r="M26" s="155"/>
       <c r="N26" s="352" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O26" s="352"/>
       <c r="P26" s="352"/>
@@ -14551,7 +14554,7 @@
     </row>
     <row r="34" spans="2:19">
       <c r="B34" s="344" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C34" s="345"/>
       <c r="D34" s="345"/>
@@ -14573,21 +14576,21 @@
     </row>
     <row r="35" spans="2:19" ht="26.1" customHeight="1">
       <c r="B35" s="350" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C35" s="336"/>
       <c r="D35" s="336" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E35" s="336" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F35" s="349"/>
       <c r="G35" s="223"/>
       <c r="H35" s="223"/>
       <c r="I35" s="156"/>
       <c r="J35" s="355" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K35" s="355"/>
       <c r="L35" s="355"/>
@@ -14601,15 +14604,15 @@
     </row>
     <row r="36" spans="2:19" ht="18" customHeight="1">
       <c r="B36" s="242" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C36" s="240"/>
       <c r="D36" s="336"/>
       <c r="E36" s="240" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F36" s="247" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G36" s="350"/>
       <c r="H36" s="336"/>
@@ -14617,7 +14620,7 @@
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
       <c r="L36" s="341" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M36" s="341"/>
       <c r="N36" s="341"/>
@@ -14670,14 +14673,14 @@
       <c r="H38" s="156"/>
       <c r="I38" s="156"/>
       <c r="J38" s="342" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K38" s="342"/>
       <c r="L38" s="51" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M38" s="354" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N38" s="342"/>
       <c r="O38" s="342"/>
@@ -14702,7 +14705,7 @@
       <c r="H39" s="156"/>
       <c r="I39" s="156"/>
       <c r="J39" s="351" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="K39" s="351"/>
       <c r="L39" s="361"/>
@@ -14711,7 +14714,7 @@
       <c r="O39" s="42"/>
       <c r="P39" s="42"/>
       <c r="Q39" s="241" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="R39" s="42"/>
       <c r="S39" s="42"/>
@@ -14732,7 +14735,7 @@
       <c r="H40" s="156"/>
       <c r="I40" s="156"/>
       <c r="J40" s="342" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K40" s="342"/>
       <c r="L40" s="129" t="str">
@@ -14741,10 +14744,10 @@
       </c>
       <c r="M40" s="42"/>
       <c r="N40" s="204" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O40" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P40" s="58"/>
       <c r="Q40" s="48" t="e">
@@ -14779,10 +14782,10 @@
       <c r="L41" s="336"/>
       <c r="M41" s="53"/>
       <c r="N41" s="204" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O41" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P41" s="58"/>
       <c r="Q41" s="48" t="e">
@@ -14814,10 +14817,10 @@
       <c r="L42" s="42"/>
       <c r="M42" s="53"/>
       <c r="N42" s="204" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O42" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P42" s="58"/>
       <c r="Q42" s="48" t="e">
@@ -14871,7 +14874,7 @@
       <c r="H44" s="156"/>
       <c r="I44" s="156"/>
       <c r="J44" s="342" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="K44" s="342"/>
       <c r="L44" s="129" t="str">
@@ -14880,10 +14883,10 @@
       </c>
       <c r="M44" s="52"/>
       <c r="N44" s="204" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O44" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P44" s="58"/>
       <c r="Q44" s="48" t="e">
@@ -14918,10 +14921,10 @@
       <c r="L45" s="269"/>
       <c r="M45" s="53"/>
       <c r="N45" s="204" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O45" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P45" s="58"/>
       <c r="Q45" s="48" t="e">
@@ -14947,10 +14950,10 @@
       <c r="L46" s="42"/>
       <c r="M46" s="53"/>
       <c r="N46" s="204" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O46" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P46" s="58"/>
       <c r="Q46" s="48" t="e">
@@ -14984,7 +14987,7 @@
     </row>
     <row r="48" spans="2:19">
       <c r="B48" s="345" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C48" s="345"/>
       <c r="D48" s="345"/>
@@ -15006,21 +15009,21 @@
     </row>
     <row r="49" spans="2:19" ht="26.1" customHeight="1">
       <c r="B49" s="336" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C49" s="336"/>
       <c r="D49" s="336" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E49" s="336" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F49" s="349"/>
       <c r="G49" s="223"/>
       <c r="H49" s="223"/>
       <c r="I49" s="156"/>
       <c r="J49" s="355" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="K49" s="355"/>
       <c r="L49" s="355"/>
@@ -15037,10 +15040,10 @@
       <c r="C50" s="156"/>
       <c r="D50" s="336"/>
       <c r="E50" s="240" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F50" s="247" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G50" s="350"/>
       <c r="H50" s="336"/>
@@ -15048,7 +15051,7 @@
       <c r="J50" s="42"/>
       <c r="K50" s="42"/>
       <c r="L50" s="341" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M50" s="341"/>
       <c r="N50" s="341"/>
@@ -15104,14 +15107,14 @@
       <c r="H52" s="156"/>
       <c r="I52" s="156"/>
       <c r="J52" s="342" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="K52" s="342"/>
       <c r="L52" s="51" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M52" s="354" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="N52" s="342"/>
       <c r="O52" s="342"/>
@@ -15138,7 +15141,7 @@
       <c r="H53" s="156"/>
       <c r="I53" s="156"/>
       <c r="J53" s="351" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="K53" s="351"/>
       <c r="L53" s="361"/>
@@ -15147,7 +15150,7 @@
       <c r="O53" s="42"/>
       <c r="P53" s="42"/>
       <c r="Q53" s="241" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="R53" s="42"/>
       <c r="S53" s="42"/>
@@ -15170,7 +15173,7 @@
       <c r="H54" s="81"/>
       <c r="I54" s="156"/>
       <c r="J54" s="342" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="K54" s="342"/>
       <c r="L54" s="129" t="str">
@@ -15179,10 +15182,10 @@
       </c>
       <c r="M54" s="52"/>
       <c r="N54" s="204" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O54" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P54" s="58"/>
       <c r="Q54" s="48" t="e">
@@ -15219,10 +15222,10 @@
       <c r="L55" s="336"/>
       <c r="M55" s="53"/>
       <c r="N55" s="204" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O55" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P55" s="58"/>
       <c r="Q55" s="48" t="e">
@@ -15256,10 +15259,10 @@
       <c r="L56" s="42"/>
       <c r="M56" s="53"/>
       <c r="N56" s="204" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O56" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P56" s="58"/>
       <c r="Q56" s="48" t="e">
@@ -15317,7 +15320,7 @@
       <c r="H58" s="156"/>
       <c r="I58" s="156"/>
       <c r="J58" s="342" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="K58" s="342"/>
       <c r="L58" s="129" t="str">
@@ -15326,10 +15329,10 @@
       </c>
       <c r="M58" s="52"/>
       <c r="N58" s="204" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O58" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P58" s="58"/>
       <c r="Q58" s="48" t="e">
@@ -15366,10 +15369,10 @@
       <c r="L59" s="269"/>
       <c r="M59" s="53"/>
       <c r="N59" s="204" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O59" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P59" s="58"/>
       <c r="Q59" s="48" t="e">
@@ -15403,10 +15406,10 @@
       <c r="L60" s="42"/>
       <c r="M60" s="53"/>
       <c r="N60" s="204" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O60" s="58" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="P60" s="58"/>
       <c r="Q60" s="48" t="e">
@@ -15493,7 +15496,7 @@
       <c r="I63" s="156"/>
       <c r="J63" s="49"/>
       <c r="K63" s="256" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="L63" s="343"/>
       <c r="M63" s="343"/>
@@ -15526,7 +15529,7 @@
     </row>
     <row r="65" spans="2:35" ht="14.1" customHeight="1">
       <c r="B65" s="347" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C65" s="347"/>
       <c r="D65" s="347"/>
@@ -15537,7 +15540,7 @@
       <c r="I65" s="156"/>
       <c r="J65" s="19"/>
       <c r="K65" s="256" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L65" s="343"/>
       <c r="M65" s="343"/>
@@ -15566,7 +15569,7 @@
     </row>
     <row r="67" spans="2:35">
       <c r="B67" s="344" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C67" s="345"/>
       <c r="D67" s="345"/>
@@ -15604,21 +15607,21 @@
     </row>
     <row r="68" spans="2:35" ht="26.1" customHeight="1">
       <c r="B68" s="350" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C68" s="336"/>
       <c r="D68" s="336" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E68" s="336" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F68" s="349"/>
       <c r="G68" s="223"/>
       <c r="H68" s="223"/>
       <c r="I68" s="156"/>
       <c r="J68" s="72" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K68" s="156"/>
       <c r="L68" s="156"/>
@@ -15648,22 +15651,22 @@
     </row>
     <row r="69" spans="2:35" ht="18" customHeight="1">
       <c r="B69" s="242" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C69" s="156"/>
       <c r="D69" s="336"/>
       <c r="E69" s="240" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F69" s="247" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G69" s="55"/>
       <c r="H69" s="54"/>
       <c r="I69" s="54"/>
       <c r="J69" s="75"/>
       <c r="K69" s="75" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="L69" s="77"/>
       <c r="M69" s="76"/>
@@ -15683,7 +15686,7 @@
       <c r="AA69" s="76"/>
       <c r="AB69" s="88"/>
       <c r="AC69" s="362" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AD69" s="363"/>
       <c r="AE69" s="363"/>
@@ -15710,7 +15713,7 @@
       <c r="H70" s="46"/>
       <c r="I70" s="54"/>
       <c r="J70" s="75" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="K70" s="87" t="s">
         <v>320</v>
@@ -15770,7 +15773,7 @@
         <v>437</v>
       </c>
       <c r="AD70" s="109" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AE70" s="110" t="s">
         <v>441</v>
@@ -15785,7 +15788,7 @@
         <v>452</v>
       </c>
       <c r="AI70" s="110" t="s">
-        <v>261</v>
+        <v>454</v>
       </c>
     </row>
     <row r="71" spans="2:35" ht="14.1" customHeight="1">
@@ -15806,82 +15809,82 @@
       <c r="H71" s="28"/>
       <c r="I71" s="46"/>
       <c r="J71" s="87" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="K71" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC71" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD71" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AF71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AH71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AI71" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="72" spans="2:35" ht="14.1" customHeight="1">
@@ -15902,82 +15905,82 @@
       <c r="H72" s="28"/>
       <c r="I72" s="156"/>
       <c r="J72" s="87" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K72" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC72" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD72" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AF72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AH72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AI72" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="73" spans="2:35" ht="14.1" customHeight="1">
@@ -15998,82 +16001,82 @@
       <c r="H73" s="28"/>
       <c r="I73" s="156"/>
       <c r="J73" s="83" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K73" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O73" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Q73" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R73" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S73" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U73" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="W73" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Y73" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AB73" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI73" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="74" spans="2:35" ht="14.1" customHeight="1">
@@ -16094,82 +16097,82 @@
       <c r="H74" s="29"/>
       <c r="I74" s="156"/>
       <c r="J74" s="84" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="K74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L74" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB74" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC74" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD74" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE74" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF74" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG74" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH74" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI74" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="75" spans="2:35" ht="14.1" customHeight="1">
@@ -16190,82 +16193,82 @@
       <c r="H75" s="28"/>
       <c r="I75" s="156"/>
       <c r="J75" s="84" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="K75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L75" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB75" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC75" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD75" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE75" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF75" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG75" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH75" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI75" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="76" spans="2:35" ht="14.1" customHeight="1">
@@ -16286,82 +16289,82 @@
       <c r="H76" s="29"/>
       <c r="I76" s="156"/>
       <c r="J76" s="84" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="K76" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O76" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Q76" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R76" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S76" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U76" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="W76" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Y76" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AB76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AC76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI76" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="77" spans="2:35" ht="14.1" customHeight="1">
@@ -16382,82 +16385,82 @@
       <c r="H77" s="28"/>
       <c r="I77" s="156"/>
       <c r="J77" s="84" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K77" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O77" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Q77" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R77" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S77" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U77" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="W77" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Y77" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AB77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AC77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI77" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="78" spans="2:35" ht="14.1" customHeight="1">
@@ -16478,82 +16481,82 @@
       <c r="H78" s="29"/>
       <c r="I78" s="156"/>
       <c r="J78" s="84" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K78" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O78" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Q78" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R78" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S78" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U78" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="W78" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Y78" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AB78" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI78" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="79" spans="2:35" ht="14.1" customHeight="1">
@@ -16574,82 +16577,82 @@
       <c r="H79" s="28"/>
       <c r="I79" s="156"/>
       <c r="J79" s="84" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="K79" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O79" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Q79" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R79" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S79" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U79" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="W79" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Y79" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AB79" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI79" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="80" spans="2:35" ht="14.1" customHeight="1">
@@ -16670,82 +16673,82 @@
       <c r="H80" s="29"/>
       <c r="I80" s="156"/>
       <c r="J80" s="84" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="K80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L80" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB80" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC80" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD80" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE80" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF80" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG80" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH80" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI80" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="81" spans="2:35" ht="14.1" customHeight="1">
@@ -16766,82 +16769,82 @@
       <c r="H81" s="28"/>
       <c r="I81" s="156"/>
       <c r="J81" s="84" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K81" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L81" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M81" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N81" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O81" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P81" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Q81" s="73" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R81" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="S81" s="73" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T81" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U81" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="V81" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="W81" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="X81" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Y81" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z81" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA81" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB81" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC81" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD81" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE81" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF81" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG81" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH81" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI81" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="82" spans="2:35" ht="14.1" customHeight="1">
@@ -16862,82 +16865,82 @@
       <c r="H82" s="29"/>
       <c r="I82" s="156"/>
       <c r="J82" s="84" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K82" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L82" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M82" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N82" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O82" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P82" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Q82" s="73" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R82" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="S82" s="73" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T82" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U82" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="V82" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="W82" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="X82" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Y82" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z82" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA82" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB82" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC82" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD82" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE82" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF82" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG82" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH82" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI82" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="83" spans="2:35" ht="14.1" customHeight="1">
@@ -16953,84 +16956,84 @@
         <v>438</v>
       </c>
       <c r="K83" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC83" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD83" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE83" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF83" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG83" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH83" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI83" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="84" spans="2:35" ht="14.1" customHeight="1">
       <c r="B84" s="347" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C84" s="347"/>
       <c r="D84" s="347"/>
@@ -17040,82 +17043,82 @@
       <c r="H84" s="246"/>
       <c r="I84" s="156"/>
       <c r="J84" s="84" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K84" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L84" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M84" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Q84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="R84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="S84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="T84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="V84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="W84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="X84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Y84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AA84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AB84" s="73" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AC84" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD84" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE84" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF84" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG84" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH84" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI84" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="85" spans="2:35">
@@ -17128,87 +17131,87 @@
       <c r="H85" s="156"/>
       <c r="I85" s="156"/>
       <c r="J85" s="84" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L85" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB85" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC85" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD85" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE85" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF85" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG85" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH85" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI85" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="86" spans="2:35">
       <c r="B86" s="338" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C86" s="339"/>
       <c r="D86" s="339"/>
@@ -17218,94 +17221,94 @@
       <c r="H86" s="156"/>
       <c r="I86" s="156"/>
       <c r="J86" s="84" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="K86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L86" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB86" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC86" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD86" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE86" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF86" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG86" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH86" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI86" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="87" spans="2:35" ht="26.1" customHeight="1">
       <c r="B87" s="350" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C87" s="336"/>
       <c r="D87" s="336" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E87" s="336" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F87" s="349"/>
       <c r="G87" s="240"/>
@@ -17315,79 +17318,79 @@
         <v>446</v>
       </c>
       <c r="K87" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC87" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD87" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AF87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AH87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AI87" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="88" spans="2:35" ht="18" customHeight="1">
@@ -17395,10 +17398,10 @@
       <c r="C88" s="156"/>
       <c r="D88" s="336"/>
       <c r="E88" s="240" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F88" s="247" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G88" s="240"/>
       <c r="H88" s="240"/>
@@ -17407,79 +17410,79 @@
         <v>450</v>
       </c>
       <c r="K88" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC88" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD88" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AF88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AH88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AI88" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="89" spans="2:35" ht="18" customHeight="1">
@@ -17501,79 +17504,79 @@
         <v>453</v>
       </c>
       <c r="K89" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC89" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD89" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AF89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AH89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AI89" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="90" spans="2:35" ht="14.1" customHeight="1">
@@ -17592,82 +17595,82 @@
       <c r="H90" s="156"/>
       <c r="I90" s="156"/>
       <c r="J90" s="84" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="K90" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC90" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD90" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AF90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AH90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AI90" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="91" spans="2:35" ht="14.1" customHeight="1">
@@ -17686,82 +17689,82 @@
       <c r="H91" s="156"/>
       <c r="I91" s="156"/>
       <c r="J91" s="84" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="K91" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC91" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD91" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AF91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AH91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AI91" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="92" spans="2:35" ht="14.1" customHeight="1">
@@ -17780,82 +17783,82 @@
       <c r="H92" s="156"/>
       <c r="I92" s="156"/>
       <c r="J92" s="84" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="K92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L92" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB92" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC92" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD92" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE92" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF92" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG92" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH92" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI92" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="93" spans="2:35" ht="14.1" customHeight="1">
@@ -17874,82 +17877,82 @@
       <c r="H93" s="156"/>
       <c r="I93" s="156"/>
       <c r="J93" s="84" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="K93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M93" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N93" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="O93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P93" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Q93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB93" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC93" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD93" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE93" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF93" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG93" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH93" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI93" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="94" spans="2:35" ht="14.1" customHeight="1">
@@ -17968,82 +17971,82 @@
       <c r="H94" s="156"/>
       <c r="I94" s="156"/>
       <c r="J94" s="143" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="K94" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC94" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD94" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE94" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF94" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG94" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AH94" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI94" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="95" spans="2:35" ht="14.1" customHeight="1">
@@ -18065,79 +18068,79 @@
         <v>442</v>
       </c>
       <c r="K95" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC95" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD95" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE95" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AF95" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG95" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AH95" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AI95" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="96" spans="2:35" ht="14.1" customHeight="1">
@@ -18159,79 +18162,79 @@
         <v>381</v>
       </c>
       <c r="K96" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="N96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Q96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="R96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="S96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="T96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="U96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="V96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="W96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="X96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Y96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="Z96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AA96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AB96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AC96" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AD96" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AE96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AF96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG96" s="250" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AH96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AI96" s="250" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="97" spans="2:6" ht="14.1" customHeight="1">
@@ -18334,7 +18337,7 @@
     </row>
     <row r="105" spans="2:6" ht="14.1" customHeight="1">
       <c r="B105" s="338" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C105" s="339"/>
       <c r="D105" s="339"/>
@@ -18356,7 +18359,7 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="338" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C107" s="339"/>
       <c r="D107" s="339"/>
@@ -18489,7 +18492,7 @@
   <sheetData>
     <row r="5" spans="1:19">
       <c r="A5" s="81" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B5" s="156"/>
       <c r="C5" s="156"/>
@@ -18512,7 +18515,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="156" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B6" s="156"/>
       <c r="C6" s="156"/>
@@ -18537,17 +18540,17 @@
       <c r="A7" s="156"/>
       <c r="B7" s="156"/>
       <c r="C7" s="367" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D7" s="367"/>
       <c r="E7" s="367" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F7" s="367"/>
       <c r="G7" s="156"/>
       <c r="H7" s="156"/>
       <c r="I7" s="81" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="J7" s="156"/>
       <c r="K7" s="156"/>
@@ -18562,7 +18565,7 @@
     </row>
     <row r="8" spans="1:19" ht="25.5">
       <c r="A8" s="123" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B8" s="94" t="str">
         <f>_CamType</f>
@@ -18592,7 +18595,7 @@
       </c>
       <c r="J8" s="95" t="str">
         <f>_OTA_Used</f>
-        <v>PYOTE</v>
+        <v>{{OTE}}</v>
       </c>
       <c r="K8" s="95"/>
       <c r="L8" s="156"/>
@@ -18607,7 +18610,7 @@
     <row r="10" spans="1:19">
       <c r="A10" s="156"/>
       <c r="B10" s="81" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C10" s="97" t="e">
         <f>INDEX('Corrections Tables'!E8:E17,MATCH(_Exposure,'Corrections Tables'!A8:A17,0),0)</f>
@@ -18642,7 +18645,7 @@
     <row r="11" spans="1:19">
       <c r="A11" s="156"/>
       <c r="B11" s="219" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C11" s="97" t="e">
         <f>INDEX('Corrections Tables'!E8:E17,MATCH(_Exposure,'Corrections Tables'!A8:A17,0),0)</f>
@@ -18677,7 +18680,7 @@
     <row r="12" spans="1:19">
       <c r="A12" s="156"/>
       <c r="B12" s="219" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C12" s="97" t="e">
         <f>INDEX('Corrections Tables'!E23:E31,MATCH(_Exposure,'Corrections Tables'!B23:B31,0),0)</f>
@@ -18712,7 +18715,7 @@
     <row r="13" spans="1:19">
       <c r="A13" s="156"/>
       <c r="B13" s="219" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C13" s="97" t="e">
         <f>INDEX('Corrections Tables'!E23:E31,MATCH(_Exposure,'Corrections Tables'!B23:B31,0),0)</f>
@@ -18747,7 +18750,7 @@
     <row r="14" spans="1:19">
       <c r="A14" s="156"/>
       <c r="B14" s="219" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C14" s="97" t="e">
         <f>INDEX('Corrections Tables'!E37:E45,MATCH(_Exposure,'Corrections Tables'!B37:B45,0),0)</f>
@@ -18782,7 +18785,7 @@
     <row r="15" spans="1:19">
       <c r="A15" s="156"/>
       <c r="B15" s="218" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C15" s="97" t="e">
         <f>INDEX('Corrections Tables'!E51:E63,MATCH(_Exposure,'Corrections Tables'!B51:B63,0),0)</f>
@@ -18817,7 +18820,7 @@
     <row r="16" spans="1:19">
       <c r="A16" s="156"/>
       <c r="B16" s="81" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C16" s="97" t="e">
         <f>INDEX('Corrections Tables'!E70:E82,MATCH(_Exposure,'Corrections Tables'!B70:B82,0),0)</f>
@@ -18851,7 +18854,7 @@
     </row>
     <row r="17" spans="2:19">
       <c r="B17" s="81" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C17" s="97"/>
       <c r="D17" s="97" t="e">
@@ -18879,7 +18882,7 @@
     </row>
     <row r="18" spans="2:19">
       <c r="B18" s="98" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C18" s="97" t="e">
         <f>INDEX('Corrections Tables'!E108,MATCH(_Exposure,'Corrections Tables'!B108,0),0)</f>
@@ -18913,7 +18916,7 @@
     </row>
     <row r="19" spans="2:19">
       <c r="B19" s="219" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C19" s="97" t="e">
         <f>INDEX('Corrections Tables'!E108,MATCH(_Exposure,'Corrections Tables'!B108,0),0)</f>
@@ -18947,7 +18950,7 @@
     </row>
     <row r="20" spans="2:19">
       <c r="B20" s="219" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C20" s="97" t="e">
         <f>INDEX('Corrections Tables'!E108,MATCH(_Exposure,'Corrections Tables'!B108,0),0)</f>
@@ -18981,7 +18984,7 @@
     </row>
     <row r="21" spans="2:19">
       <c r="B21" s="98" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C21" s="97" t="e">
         <f>INDEX('Corrections Tables'!E108,MATCH(_Exposure,'Corrections Tables'!B108,0),0)</f>
@@ -19015,7 +19018,7 @@
     </row>
     <row r="22" spans="2:19">
       <c r="B22" s="98" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C22" s="97" t="e">
         <f>INDEX('Corrections Tables'!E108,MATCH(_Exposure,'Corrections Tables'!B108,0),0)</f>
@@ -19049,7 +19052,7 @@
     </row>
     <row r="23" spans="2:19">
       <c r="B23" s="218" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C23" s="97" t="e">
         <f>INDEX('Corrections Tables'!Q54:Q56,MATCH(_Exposure,'Corrections Tables'!R40:R42,0),0)</f>
@@ -19083,7 +19086,7 @@
     </row>
     <row r="24" spans="2:19">
       <c r="B24" s="218" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C24" s="97" t="e">
         <f>INDEX('Corrections Tables'!E106,MATCH(_Exposure,'Corrections Tables'!B106,0),0)</f>
@@ -19102,7 +19105,7 @@
         <v>#N/A</v>
       </c>
       <c r="G24" s="156" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H24" s="156"/>
       <c r="I24" s="81"/>
@@ -19215,7 +19218,7 @@
     </row>
     <row r="28" spans="2:19">
       <c r="B28" s="218" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C28" s="97">
         <v>0</v>
@@ -19247,7 +19250,7 @@
     </row>
     <row r="29" spans="2:19">
       <c r="B29" s="84" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C29" s="97">
         <v>0</v>
@@ -19279,7 +19282,7 @@
     </row>
     <row r="30" spans="2:19">
       <c r="B30" s="218" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C30" s="97">
         <v>0</v>
@@ -19311,7 +19314,7 @@
     </row>
     <row r="31" spans="2:19">
       <c r="B31" s="218" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C31" s="97">
         <v>0</v>
@@ -19375,7 +19378,7 @@
     </row>
     <row r="33" spans="2:23">
       <c r="B33" s="218" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C33" s="97">
         <v>0</v>
@@ -19447,7 +19450,7 @@
     </row>
     <row r="35" spans="2:23">
       <c r="B35" s="218" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C35" s="97">
         <v>0</v>
@@ -19488,7 +19491,7 @@
       <c r="E38" s="156"/>
       <c r="F38" s="156"/>
       <c r="G38" s="81" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H38" s="156"/>
       <c r="I38" s="156"/>
@@ -19500,7 +19503,7 @@
       <c r="O38" s="156"/>
       <c r="P38" s="156"/>
       <c r="Q38" s="156" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="R38" s="156"/>
       <c r="S38" s="156"/>
@@ -19526,7 +19529,7 @@
       <c r="O39" s="156"/>
       <c r="P39" s="156"/>
       <c r="Q39" s="156" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="R39" s="156"/>
       <c r="S39" s="156"/>
@@ -19545,7 +19548,7 @@
       <c r="H40" s="156"/>
       <c r="I40" s="156"/>
       <c r="J40" s="123" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="K40" s="205" t="e">
         <f>K41</f>
@@ -19557,7 +19560,7 @@
       <c r="O40" s="156"/>
       <c r="P40" s="156"/>
       <c r="Q40" s="372" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="R40" s="373"/>
       <c r="S40" s="374"/>
@@ -19576,7 +19579,7 @@
       <c r="H41" s="156"/>
       <c r="I41" s="156"/>
       <c r="J41" s="122" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="K41" s="100" t="e">
         <f>IF(K42+(L46/24/60/60)&lt;0,K42+(L46/24/60/60)+1,K42+(L46/24/60/60))</f>
@@ -19589,7 +19592,7 @@
       <c r="P41" s="156"/>
       <c r="Q41" s="108"/>
       <c r="R41" s="370" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="S41" s="371"/>
       <c r="T41" s="375"/>
@@ -19607,7 +19610,7 @@
       <c r="H42" s="156"/>
       <c r="I42" s="156"/>
       <c r="J42" s="122" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="K42" s="100" t="e">
         <f>SUM(K43:K45)</f>
@@ -19620,7 +19623,7 @@
       <c r="P42" s="156"/>
       <c r="Q42" s="108"/>
       <c r="R42" s="368" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="S42" s="369"/>
       <c r="T42" s="380"/>
@@ -19638,7 +19641,7 @@
       <c r="H43" s="156"/>
       <c r="I43" s="156"/>
       <c r="J43" s="126" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="K43" s="100" t="e">
         <f>I46/24/60/60</f>
@@ -19649,13 +19652,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="M43" s="122" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N43" s="156"/>
       <c r="O43" s="156"/>
       <c r="P43" s="156"/>
       <c r="Q43" s="109" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="R43" s="109" t="s">
         <v>432</v>
@@ -19678,7 +19681,7 @@
       <c r="H44" s="156"/>
       <c r="I44" s="156"/>
       <c r="J44" s="126" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K44" s="100" t="e">
         <f>H46/24/60</f>
@@ -19689,7 +19692,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="M44" s="122" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N44" s="156"/>
       <c r="O44" s="156"/>
@@ -19718,7 +19721,7 @@
       <c r="H45" s="156"/>
       <c r="I45" s="156"/>
       <c r="J45" s="122" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K45" s="100" t="e">
         <f>G46/24</f>
@@ -19729,13 +19732,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="M45" s="122" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N45" s="156"/>
       <c r="O45" s="156"/>
       <c r="P45" s="156"/>
       <c r="Q45" s="109" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="R45" s="111">
         <v>0</v>
@@ -19770,16 +19773,16 @@
         <f>IF(OR(_VTI_Type="AFT or OFT Flash Tag",_OTA_Used="AOTA w/ CamDelay Corrections",_OTA_Used="R-OTE w/ CamDelay Corrections",_OTA_Used="Manual",_OTA_Used="Other - Specify in Comments"),0,IF(_CamFormat="PAL/CCIR",INDEX(PAL_CORR,MATCH(_CamType,Cor_Camera_List,0)),INDEX(NTSC_CORR,MATCH(_CamType,Cor_Camera_List,0),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="K46" s="130">
+      <c r="K46" s="130" t="e">
         <f>IF(AND(OR(_CamType="RunCam Night Eagle Astro",_CamType="RunCam Night Eagle",_VTI_Type="AFT or OFT Flash Tag"),_OTA_Used&lt;&gt;"Occular"),0,IF(_CamFormat="PAL/CCIR",INDEX(VTIoff_PAL_CCIR,MATCH(_OTA_Used,_OTE_List,0)),INDEX(VTIoff_NTSC_EIA,MATCH(_OTA_Used,_OTE_List,0),0)))</f>
-        <v>-1.67E-2</v>
+        <v>#N/A</v>
       </c>
       <c r="L46" s="130" t="e">
         <f>IF(OR(_CamFormat="AAV-NTSC",_CamFormat="AAV-PAL",_CamFormat="ADVS"),0,J46+K46)</f>
         <v>#N/A</v>
       </c>
       <c r="M46" s="381" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N46" s="382"/>
       <c r="O46" s="382"/>
@@ -19804,25 +19807,25 @@
       <c r="D47" s="156"/>
       <c r="E47" s="156"/>
       <c r="F47" s="206" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="G47" s="207" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H47" s="207" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I47" s="207" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J47" s="208" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K47" s="209" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="L47" s="208" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M47" s="106"/>
       <c r="N47" s="156"/>
@@ -19865,16 +19868,16 @@
         <f>IF(OR(_VTI_Type="AFT or OFT Flash Tag",_OTA_Used="AOTA w/ CamDelay Corrections",_OTA_Used="R-OTE w/ CamDelay Corrections",_OTA_Used="Manual",_OTA_Used="Other - Specify in Comments"),0,IF(_CamFormat="PAL/CCIR",INDEX(PAL_CORR_R,MATCH(_CamType,Cor_Camera_List,0)),INDEX(NTSC_CORR_R,MATCH(_CamType,Cor_Camera_List,0),0)))</f>
         <v>#N/A</v>
       </c>
-      <c r="K48" s="130">
+      <c r="K48" s="130" t="e">
         <f>IF(AND(OR(_CamType="RunCam Night Eagle Astro",_CamType="RunCam Night Eagle",_VTI_Type="AFT or OFT Flash Tag"),_OTA_Used&lt;&gt;"Occular"),0,IF(_CamFormat="PAL/CCIR",INDEX(VTIoff_PAL_CCIR,MATCH(_OTA_Used,_OTE_List,0)),INDEX(VTIoff_NTSC_EIA,MATCH(_OTA_Used,_OTE_List,0),0)))</f>
-        <v>-1.67E-2</v>
+        <v>#N/A</v>
       </c>
       <c r="L48" s="130" t="e">
         <f>IF(OR(_CamFormat="AAV-NTSC",_CamFormat="AAV-PAL",_CamFormat="ADVS"),0,J48+K48)</f>
         <v>#N/A</v>
       </c>
       <c r="M48" s="381" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N48" s="382"/>
       <c r="O48" s="382"/>
@@ -19899,7 +19902,7 @@
       <c r="H49" s="156"/>
       <c r="I49" s="156"/>
       <c r="J49" s="125" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="K49" s="107" t="e">
         <f>G48/24</f>
@@ -19910,7 +19913,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="M49" s="125" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N49" s="156"/>
       <c r="O49" s="156"/>
@@ -19948,7 +19951,7 @@
       <c r="H50" s="156"/>
       <c r="I50" s="156"/>
       <c r="J50" s="127" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="K50" s="107" t="e">
         <f>H48/24/60</f>
@@ -19959,13 +19962,13 @@
         <v>#VALUE!</v>
       </c>
       <c r="M50" s="125" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="N50" s="156"/>
       <c r="O50" s="156"/>
       <c r="P50" s="156"/>
       <c r="Q50" s="112" t="s">
-        <v>261</v>
+        <v>454</v>
       </c>
       <c r="R50" s="111">
         <f>IF(OR(_CamType="QHY 174 GPS",_CamType="Other - Specify in Comments",_CamType="Visual",_CamType="Photometer",_CamType="CCD Drift Scan",_CamType="Flea 3-03S1 with ADVS",_CamType="Flea 3-03S3 with ADVS",_CamType="Flea 3-28S4M with ADVS",_CamType="Grasshopper Express with ADVS",_CamType="G-Star",0),0,-0.02)</f>
@@ -19997,7 +20000,7 @@
       <c r="H51" s="156"/>
       <c r="I51" s="156"/>
       <c r="J51" s="127" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="K51" s="107" t="e">
         <f>I48/24/60/60</f>
@@ -20008,7 +20011,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="M51" s="125" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N51" s="156"/>
       <c r="O51" s="156"/>
@@ -20038,7 +20041,7 @@
       <c r="H52" s="156"/>
       <c r="I52" s="156"/>
       <c r="J52" s="125" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="K52" s="107" t="e">
         <f>SUM(K49:K51)</f>
@@ -20074,7 +20077,7 @@
       <c r="H53" s="156"/>
       <c r="I53" s="156"/>
       <c r="J53" s="125" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K53" s="107" t="e">
         <f>IF(K52+(L48/24/60/60)&lt;0,K52+(L48/24/60/60)+1,K52+(L48/24/60/60))</f>
@@ -20110,7 +20113,7 @@
       <c r="H54" s="156"/>
       <c r="I54" s="156"/>
       <c r="J54" s="124" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K54" s="210" t="e">
         <f>K53</f>
@@ -20120,7 +20123,7 @@
       <c r="M54" s="156"/>
       <c r="N54" s="156"/>
       <c r="O54" s="156" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="P54" s="156"/>
       <c r="Q54" s="156"/>
@@ -20153,7 +20156,7 @@
       <c r="M55" s="156"/>
       <c r="N55" s="156"/>
       <c r="O55" s="156" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P55" s="156"/>
       <c r="Q55" s="156"/>
@@ -20178,7 +20181,7 @@
     <row r="56" spans="6:34">
       <c r="F56" s="156"/>
       <c r="G56" s="156" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H56" s="156"/>
       <c r="I56" s="156"/>
@@ -20188,7 +20191,7 @@
       <c r="M56" s="156"/>
       <c r="N56" s="156"/>
       <c r="O56" s="156" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="P56" s="156"/>
       <c r="Q56" s="211"/>
@@ -20213,7 +20216,7 @@
     <row r="57" spans="6:34" ht="15.75">
       <c r="F57" s="156"/>
       <c r="G57" s="277" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H57" s="277"/>
       <c r="I57" s="277"/>
@@ -20295,7 +20298,7 @@
     <row r="59" spans="6:34" ht="15.75">
       <c r="F59" s="156"/>
       <c r="G59" s="277" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H59" s="277"/>
       <c r="I59" s="277"/>
@@ -20348,7 +20351,7 @@
       <c r="M60" s="156"/>
       <c r="N60" s="156"/>
       <c r="O60" s="156" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P60" s="156"/>
       <c r="Q60" s="156"/>
@@ -20376,7 +20379,7 @@
       <c r="D66" s="156"/>
       <c r="E66" s="156"/>
       <c r="F66" s="81" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G66" s="156"/>
       <c r="H66" s="156"/>
@@ -20395,7 +20398,7 @@
       <c r="D67" s="156"/>
       <c r="E67" s="156"/>
       <c r="F67" s="365" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="G67" s="365"/>
       <c r="H67" s="365"/>
@@ -20417,10 +20420,10 @@
       <c r="G68" s="47"/>
       <c r="H68" s="47"/>
       <c r="I68" s="67" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="J68" s="67" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="K68" s="47"/>
       <c r="L68" s="47"/>
@@ -20435,18 +20438,18 @@
       <c r="D69" s="156"/>
       <c r="E69" s="156"/>
       <c r="F69" s="376" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="G69" s="377"/>
       <c r="H69" s="378"/>
       <c r="I69" s="244" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J69" s="244" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K69" s="379" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L69" s="360"/>
       <c r="M69" s="360"/>
@@ -20460,18 +20463,18 @@
       <c r="D70" s="156"/>
       <c r="E70" s="156"/>
       <c r="F70" s="376" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="G70" s="377"/>
       <c r="H70" s="378"/>
       <c r="I70" s="68" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="J70" s="71" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="K70" s="245" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L70" s="245"/>
       <c r="M70" s="245"/>
@@ -20485,15 +20488,15 @@
       <c r="D71" s="156"/>
       <c r="E71" s="156"/>
       <c r="F71" s="376" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="G71" s="377"/>
       <c r="H71" s="378"/>
       <c r="I71" s="69" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J71" s="244" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K71" s="61"/>
       <c r="L71" s="61"/>
@@ -20508,7 +20511,7 @@
       <c r="D72" s="22"/>
       <c r="E72" s="22"/>
       <c r="F72" s="376" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="G72" s="377"/>
       <c r="H72" s="378"/>
@@ -20531,15 +20534,15 @@
       <c r="D73" s="22"/>
       <c r="E73" s="22"/>
       <c r="F73" s="376" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="G73" s="377"/>
       <c r="H73" s="378"/>
       <c r="I73" s="69" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="J73" s="244" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="K73" s="61"/>
       <c r="L73" s="61"/>
@@ -20554,7 +20557,7 @@
       <c r="D74" s="22"/>
       <c r="E74" s="22"/>
       <c r="F74" s="376" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G74" s="377"/>
       <c r="H74" s="378"/>
@@ -20577,7 +20580,7 @@
       <c r="D75" s="22"/>
       <c r="E75" s="22"/>
       <c r="F75" s="376" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="G75" s="377"/>
       <c r="H75" s="378"/>
